--- a/docs/deliverables/01_요구사항정의서_29기_3팀.xlsx
+++ b/docs/deliverables/01_요구사항정의서_29기_3팀.xlsx
@@ -2,43 +2,18 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" r:id="R038a9c346e6e4314"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" r:id="Rf3747f95cc9b4c0a"/>
   </x:sheets>
 </x:workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:si>
-    <x:t xml:space="preserve">분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">요구사항명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">추가설명</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">비고</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">대분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">중분류</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">요구사항 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">소분류(기능설명)</x:t>
-  </x:si>
-</x:sst>
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="11">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="10"/>
       <x:color rgb="FF000000"/>
@@ -90,8 +65,19 @@
       <x:color theme="1"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF222222"/>
+      <x:name val="Arial"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -103,8 +89,18 @@
         <x:fgColor rgb="FFD9D9D9"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEAF2F8"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF4F6F7"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
-  <x:borders count="25">
+  <x:borders count="26">
     <x:border/>
     <x:border>
       <x:left style="thin">
@@ -337,11 +333,25 @@
         <x:color rgb="FF000000"/>
       </x:bottom>
     </x:border>
+    <x:border>
+      <x:left style="thin">
+        <x:color rgb="FFB7B7B7"/>
+      </x:left>
+      <x:right style="thin">
+        <x:color rgb="FFB7B7B7"/>
+      </x:right>
+      <x:top style="thin">
+        <x:color rgb="FFB7B7B7"/>
+      </x:top>
+      <x:bottom style="thin">
+        <x:color rgb="FFB7B7B7"/>
+      </x:bottom>
+    </x:border>
   </x:borders>
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="1" applyAlignment="1"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="203">
+  <x:cellXfs count="212">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <x:alignment vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -910,6 +920,33 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="top" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="3" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="4" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -961,9 +998,9 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Calibri"/>
-        <a:cs typeface="Calibri"/>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface="Calibri Light"/>
+        <a:cs typeface="Calibri Light"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1070,18 +1107,24 @@
     <x:col min="1" max="4" width="12.630000114440918" customWidth="1"/>
     <x:col min="5" max="6" width="56.130001068115234" customWidth="1"/>
     <x:col min="1" max="1" width="10" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="13" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="17" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="15" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="46" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="62" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="34" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="54" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="20" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="str">
-        <x:v>SensePlace 요구사항 정의서</x:v>
-      </x:c>
+        <x:v>Answervice 요구사항 정의서</x:v>
+      </x:c>
+      <x:c r="B1"/>
+      <x:c r="C1"/>
+      <x:c r="D1"/>
+      <x:c r="E1"/>
+      <x:c r="F1"/>
+      <x:c r="G1"/>
       <x:c r="H1" s="2"/>
       <x:c r="I1" s="2"/>
       <x:c r="J1" s="2"/>
@@ -1104,7 +1147,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="160" t="str">
-        <x:v>호텔 VOC·운영 지원 플랫폼 | SK네트웍스 Family AI 캠프 29기 3팀 | v3.0 | 기준일 2026-07-23 12:07 | 추적 요구사항 62개</x:v>
+        <x:v>DataHub Core 기반 대화형 데이터 분석·자동 리포팅 서비스 | SK네트웍스 Family AI 캠프 29기 3팀 | v1.0 | 기준일 2026-07-30 | 추적 요구사항 75개</x:v>
       </x:c>
       <x:c r="B2" s="160"/>
       <x:c r="C2" s="160"/>
@@ -1133,20 +1176,20 @@
       <x:c r="Z2" s="2"/>
     </x:row>
     <x:row r="3" ht="15.75" customHeight="1">
-      <x:c r="A3" s="3" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="B3" s="4" t="s">
-        <x:v>1</x:v>
+      <x:c r="A3" s="3" t="str">
+        <x:v>분류</x:v>
+      </x:c>
+      <x:c r="B3" s="4" t="str">
+        <x:v>요구사항명</x:v>
       </x:c>
       <x:c r="C3" s="5"/>
       <x:c r="D3" s="5"/>
       <x:c r="E3" s="6"/>
-      <x:c r="F3" s="3" t="s">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="G3" s="3" t="s">
-        <x:v>3</x:v>
+      <x:c r="F3" s="3" t="str">
+        <x:v>추가설명</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="str">
+        <x:v>비고</x:v>
       </x:c>
       <x:c r="H3" s="2"/>
       <x:c r="I3" s="2"/>
@@ -1170,17 +1213,17 @@
     </x:row>
     <x:row r="4" ht="15.75" customHeight="1">
       <x:c r="A4" s="7"/>
-      <x:c r="B4" s="8" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C4" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D4" s="8" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E4" s="8" t="s">
-        <x:v>7</x:v>
+      <x:c r="B4" s="8" t="str">
+        <x:v>대분류</x:v>
+      </x:c>
+      <x:c r="C4" s="8" t="str">
+        <x:v>중분류</x:v>
+      </x:c>
+      <x:c r="D4" s="8" t="str">
+        <x:v>요구사항 ID</x:v>
+      </x:c>
+      <x:c r="E4" s="8" t="str">
+        <x:v>소분류(기능설명)</x:v>
       </x:c>
       <x:c r="F4" s="7"/>
       <x:c r="G4" s="7"/>
@@ -1204,36 +1247,27 @@
       <x:c r="Y4" s="2"/>
       <x:c r="Z4" s="2"/>
     </x:row>
-    <x:row r="5" ht="112" customHeight="1">
-      <x:c r="A5" s="161" t="str">
+    <x:row r="5" ht="72" customHeight="1">
+      <x:c r="A5" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B5" s="161" t="str">
-        <x:v>업무 요구사항</x:v>
-      </x:c>
-      <x:c r="C5" s="133" t="str">
-        <x:v>서비스 목적</x:v>
-      </x:c>
-      <x:c r="D5" s="177" t="str">
-        <x:v>BIZ-001</x:v>
-      </x:c>
-      <x:c r="E5" s="181" t="str">
-        <x:v>시스템은 VOC와 운영지표를 동일 시설·동일 기간 기준으로 교차분석해야 한다.</x:v>
-      </x:c>
-      <x:c r="F5" s="190" t="str">
-        <x:v>정의·상세: 부정 VOC 증가 서비스와 함께 변한 운영지표를 찾아 원인 후보·점검 방향을 제시하는 것이 핵심. 단순 감성분석 아님.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: VOC·운영지표 → 동기간·동시설 정렬·비교 → 증감률·비교기간
-업무 규칙·예외: 상관≠인과 통제.
-수용 기준: Given 시설·기간이 정렬됐을 때 / When 부정 VOC가 증가하면 / Then 동기간 운영지표 변화가 함께 조회된다.</x:v>
-      </x:c>
-      <x:c r="G5" s="190" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(SQL·규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 4~5주차
-산출물: AI 시스템 아키텍처
-참고: 화면: 운영 원인 분석 · 비고: 서비스 핵심 원칙</x:v>
+      <x:c r="B5" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C5" s="207" t="str">
+        <x:v>인증·세션</x:v>
+      </x:c>
+      <x:c r="D5" s="209" t="str">
+        <x:v>REQ-F-001</x:v>
+      </x:c>
+      <x:c r="E5" s="208" t="str">
+        <x:v>사용자는 인증을 거쳐 유효한 역할과 정책 버전을 부여받아야 한다.</x:v>
+      </x:c>
+      <x:c r="F5" s="208" t="str">
+        <x:v>미인증 요청은 로그인으로 이동하고 만료·무효 세션은 안전한 오류와 재인증 동작을 제공한다.</x:v>
+      </x:c>
+      <x:c r="G5" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H5" s="2"/>
       <x:c r="I5" s="2"/>
@@ -1255,35 +1289,27 @@
       <x:c r="Y5" s="2"/>
       <x:c r="Z5" s="2"/>
     </x:row>
-    <x:row r="6" ht="86" customHeight="1">
-      <x:c r="A6" s="162" t="str">
+    <x:row r="6" ht="72" customHeight="1">
+      <x:c r="A6" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B6" s="162" t="str">
-        <x:v>업무 요구사항</x:v>
-      </x:c>
-      <x:c r="C6" s="135" t="str">
-        <x:v>분석 표현</x:v>
-      </x:c>
-      <x:c r="D6" s="178" t="str">
-        <x:v>BIZ-002</x:v>
-      </x:c>
-      <x:c r="E6" s="182" t="str">
-        <x:v>시스템은 분석 결과를 확정 원인이 아닌 원인 후보·연관 지표·우선 점검 항목으로 제공해야 한다.</x:v>
-      </x:c>
-      <x:c r="F6" s="191" t="str">
-        <x:v>정의·상세: AI/LLM은 원인을 확정하지 않는다. '가능성을 우선 점검' 형태로만 표현.
-대상 사용자: 전 사용자
-입력→처리→출력: 교차분석 결과 → 규칙 충족 시 후보 생성 → 원인 후보·연관 지표
-업무 규칙·예외: 인과 확정 표현 금지.
-수용 기준: Given 규칙 충족 결과일 때 / When 문장을 생성하면 / Then 확정 원인 표현 없이 후보로 표기된다.</x:v>
-      </x:c>
-      <x:c r="G6" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-참고: 선행 AI-009 · 화면: 운영 원인 분석</x:v>
+      <x:c r="B6" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C6" s="207" t="str">
+        <x:v>권한</x:v>
+      </x:c>
+      <x:c r="D6" s="209" t="str">
+        <x:v>REQ-F-002</x:v>
+      </x:c>
+      <x:c r="E6" s="208" t="str">
+        <x:v>모든 질문·자산·보고서·감사 동작은 서버의 역할 및 entitlement 검사를 통과해야 한다.</x:v>
+      </x:c>
+      <x:c r="F6" s="208" t="str">
+        <x:v>권한 거부 응답은 요청 역할, 허용 범위, 안전한 사유와 복귀 경로를 제공하며 UI의 메뉴 숨김만으로 권한을 통제하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G6" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H6" s="2"/>
       <x:c r="I6" s="2"/>
@@ -1305,35 +1331,27 @@
       <x:c r="Y6" s="2"/>
       <x:c r="Z6" s="2"/>
     </x:row>
-    <x:row r="7" ht="112" customHeight="1">
-      <x:c r="A7" s="162" t="str">
+    <x:row r="7" ht="72" customHeight="1">
+      <x:c r="A7" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B7" s="162" t="str">
-        <x:v>업무 요구사항</x:v>
-      </x:c>
-      <x:c r="C7" s="136" t="str">
-        <x:v>근거 중심</x:v>
-      </x:c>
-      <x:c r="D7" s="179" t="str">
-        <x:v>BIZ-003</x:v>
-      </x:c>
-      <x:c r="E7" s="183" t="str">
-        <x:v>시스템은 모든 AI 분석 결과에 근거 수치·분석 기간과 허용된 근거를 연결해야 한다.</x:v>
-      </x:c>
-      <x:c r="F7" s="192" t="str">
-        <x:v>정의·상세: 계산값·기간·내부 evidence를 결과와 연결하고 LLM 생성 문장과 계산 결과를 구분한다. VOC 최초 응답에는 평점 근거 수치만 노출하며 리뷰 원문은 FUN-006의 추가 질의 조건을 충족할 때만 표시한다.
-대상 사용자: 전 사용자
-입력→처리→출력: 분석결과·계산값·리뷰 → 결과-근거 연결 → 근거 포함 분석 카드
-업무 규칙·예외: 근거 없는 결과 미표시.
-수용 기준: Given AI 결과가 생성됐을 때 / When 조회하면 / Then 기간·계산값·evidence ID가 연결되고 화면에는 질의 단계에서 허용된 근거만 표시된다.</x:v>
-      </x:c>
-      <x:c r="G7" s="192" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(연결)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-참고: 선행 AI-003,AI-005 · 화면: 근거 리뷰 · 비고: 설명 가능성 핵심</x:v>
+      <x:c r="B7" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C7" s="207" t="str">
+        <x:v>대화</x:v>
+      </x:c>
+      <x:c r="D7" s="209" t="str">
+        <x:v>REQ-F-003</x:v>
+      </x:c>
+      <x:c r="E7" s="208" t="str">
+        <x:v>사용자는 자연어로 분석 질문을 제출하고 대화 단위로 후속 질문을 이어갈 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F7" s="208" t="str">
+        <x:v>요청마다 conversation_id와 request_id를 생성하고 후속 질문은 승인된 이전 문맥만 참조한다.</x:v>
+      </x:c>
+      <x:c r="G7" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H7" s="2"/>
       <x:c r="I7" s="2"/>
@@ -1355,35 +1373,27 @@
       <x:c r="Y7" s="2"/>
       <x:c r="Z7" s="2"/>
     </x:row>
-    <x:row r="8" ht="99" customHeight="1">
-      <x:c r="A8" s="162" t="str">
+    <x:row r="8" ht="72" customHeight="1">
+      <x:c r="A8" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B8" s="162" t="str">
-        <x:v>업무 요구사항</x:v>
-      </x:c>
-      <x:c r="C8" s="137" t="str">
-        <x:v>의사결정 경계</x:v>
-      </x:c>
-      <x:c r="D8" s="180" t="str">
-        <x:v>BIZ-004</x:v>
-      </x:c>
-      <x:c r="E8" s="184" t="str">
-        <x:v>시스템은 대응 방안을 검토 옵션으로만 제공하고 자동 실행하지 않으며 실행은 운영자 승인을 거쳐야 한다.</x:v>
-      </x:c>
-      <x:c r="F8" s="193" t="str">
-        <x:v>정의·상세: 고객 자동응대·보상·인력배치·조치 자동 실행은 범위 외. 에이전트는 추천까지, 실행은 승인 게이트.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 원인 후보·대응 템플릿 → 규칙 매핑 → 검토·선택·메모 옵션
-업무 규칙·예외: 자동 조치 금지.
-수용 기준: Given 대응 옵션이 생성됐을 때 / When 확인하면 / Then 검토·메모만 가능하고 자동 조치는 없다.</x:v>
-      </x:c>
-      <x:c r="G8" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차 Gate
-참고: 선행 FUN-007 · 화면: 운영 원인 분석 · 비고: 안전장치=차별점</x:v>
+      <x:c r="B8" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C8" s="207" t="str">
+        <x:v>대화</x:v>
+      </x:c>
+      <x:c r="D8" s="209" t="str">
+        <x:v>REQ-F-004</x:v>
+      </x:c>
+      <x:c r="E8" s="208" t="str">
+        <x:v>시스템은 질문의 의도·지표·기간·차원·필터를 구조화하고 부족한 조건을 확인해야 한다.</x:v>
+      </x:c>
+      <x:c r="F8" s="208" t="str">
+        <x:v>필수 조건이 모호하면 SQL을 실행하지 않고 수정 가능한 명확화 질문을 반환한다.</x:v>
+      </x:c>
+      <x:c r="G8" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H8" s="2"/>
       <x:c r="I8" s="2"/>
@@ -1405,36 +1415,27 @@
       <x:c r="Y8" s="2"/>
       <x:c r="Z8" s="2"/>
     </x:row>
-    <x:row r="9" ht="112" customHeight="1">
-      <x:c r="A9" s="163" t="str">
+    <x:row r="9" ht="72" customHeight="1">
+      <x:c r="A9" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B9" s="163" t="str">
-        <x:v>업무 요구사항</x:v>
-      </x:c>
-      <x:c r="C9" s="136" t="str">
-        <x:v>데이터 원칙</x:v>
-      </x:c>
-      <x:c r="D9" s="179" t="str">
-        <x:v>BIZ-005</x:v>
-      </x:c>
-      <x:c r="E9" s="185" t="str">
-        <x:v>시스템은 합성 VOC와 합성 운영 데이터 전용 Baseline임을 모든 산출물에 명시해야 한다.</x:v>
-      </x:c>
-      <x:c r="F9" s="192" t="str">
-        <x:v>정의·상세: Baseline과 모델 실험은 규칙·template으로 정답 label을 고정하고 필요 시 LLM으로 문장만 다양화한 합성 VOC와 합성 운영 데이터만 사용한다. 실제 워커힐 내부 데이터와 공개 리뷰 corpus는 사용하지 않는다.
-대상 사용자: 전 사용자, 평가자
-입력→처리→출력: 데이터 출처 메타 → 한계 문구 삽입 → 안내 문구
-업무 규칙·예외: 합성 데이터를 실제처럼 표현 금지.
-수용 기준: Given 리포트 생성 시 / When 출력하면 / Then 데이터 출처·합성 한계 문구가 포함된다.</x:v>
-      </x:c>
-      <x:c r="G9" s="192" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 2주차
-산출물: 수집 데이터 보고서
-참고: 화면: 주간 리포트 · 비고: 가정·자체 정의</x:v>
+      <x:c r="B9" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C9" s="207" t="str">
+        <x:v>라우팅</x:v>
+      </x:c>
+      <x:c r="D9" s="209" t="str">
+        <x:v>REQ-F-005</x:v>
+      </x:c>
+      <x:c r="E9" s="208" t="str">
+        <x:v>Router는 승인된 Template 또는 일반 LLM 경로를 결정해야 한다.</x:v>
+      </x:c>
+      <x:c r="F9" s="208" t="str">
+        <x:v>Template 적중 시 typed parameter binding을 사용하고 문자열 직접 결합을 금지한다.</x:v>
+      </x:c>
+      <x:c r="G9" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H9" s="2"/>
       <x:c r="I9" s="2"/>
@@ -1456,36 +1457,27 @@
       <x:c r="Y9" s="2"/>
       <x:c r="Z9" s="2"/>
     </x:row>
-    <x:row r="10" ht="164" customHeight="1">
-      <x:c r="A10" s="164" t="str">
+    <x:row r="10" ht="72" customHeight="1">
+      <x:c r="A10" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B10" s="164" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C10" s="137" t="str">
-        <x:v>리뷰·VOC</x:v>
-      </x:c>
-      <x:c r="D10" s="180" t="str">
-        <x:v>DAT-001</x:v>
-      </x:c>
-      <x:c r="E10" s="186" t="str">
-        <x:v>시스템은 고객 리뷰 원본을 최소 표준 스키마로 저장해야 한다.</x:v>
-      </x:c>
-      <x:c r="F10" s="193" t="str">
-        <x:v>정의·상세: voc_review_raw는 voc_id, review_text_original, review_date, rating, location, language_code, review_text_ko, translation_version, is_synthetic, dataset/schema version을 저장한다. 번역이 필요 없으면 review_text_ko는 원문과 같게 두고 실제 고객·예약 식별자는 저장하지 않는다.
-대상 사용자: 데이터 담당
-입력→처리→출력: 리뷰 데이터 → 스키마 매핑·적재 → 표준 리뷰 테이블
-업무 규칙·예외: 실제·공개 리뷰 corpus를 사용하지 않으며 원본 행은 학습 label로 덮어쓰지 않는다.
-수용 기준: Given 합성 VOC가 pre-load validation을 통과했을 때 / When 적재하면 / Then 원문·한국어 번역·언어·평점·장소·일자와 version이 같은 voc_id로 저장된다.</x:v>
-      </x:c>
-      <x:c r="G10" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 3주차
-산출물: DB/저장소 설계 문서
-참고: 선행 DAT-007 · 비고: 필수 컬럼은 합성 데이터 스키마 팀 합의 후 확정</x:v>
+      <x:c r="B10" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C10" s="207" t="str">
+        <x:v>처리 상태</x:v>
+      </x:c>
+      <x:c r="D10" s="209" t="str">
+        <x:v>REQ-F-006</x:v>
+      </x:c>
+      <x:c r="E10" s="208" t="str">
+        <x:v>분석 요청의 Controller 처리 상태를 순서대로 조회할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F10" s="208" t="str">
+        <x:v>Router→Context→G1→SQL→G2→Query→G3→Explanation 상태와 안전한 중단 상태를 노출한다.</x:v>
+      </x:c>
+      <x:c r="G10" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H10" s="2"/>
       <x:c r="I10" s="2"/>
@@ -1507,36 +1499,27 @@
       <x:c r="Y10" s="2"/>
       <x:c r="Z10" s="2"/>
     </x:row>
-    <x:row r="11" ht="177" customHeight="1">
-      <x:c r="A11" s="162" t="str">
+    <x:row r="11" ht="72" customHeight="1">
+      <x:c r="A11" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B11" s="162" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C11" s="135" t="str">
-        <x:v>학습 데이터</x:v>
-      </x:c>
-      <x:c r="D11" s="178" t="str">
-        <x:v>DAT-002</x:v>
-      </x:c>
-      <x:c r="E11" s="182" t="str">
-        <x:v>시스템은 원본 리뷰와 분리된 학습용 파생 데이터를 저장해야 한다.</x:v>
-      </x:c>
-      <x:c r="F11" s="191" t="str">
-        <x:v>정의·상세: voc_training_dataset은 voc_id, 학습 입력용 review_text, review_date, rating, location, sentiment_label, label_version, dataset version만 저장한다. sentiment_label은 POSITIVE,NEUTRAL,NEGATIVE 3종이며 원본의 번역·정규화 결과를 참조한다. 학습 목적의 label·split·전처리 버전을 원본 테이블에 추가하지 않는다.
-대상 사용자: 데이터·AI 담당
-입력→처리→출력: 검증된 원본 리뷰 → 번역·정규화·감성 label 부여 → versioned 학습 데이터
-업무 규칙·예외: 원본은 추적·재처리 기준이므로 불변으로 보존하고 학습 데이터는 언제든 재생성 가능한 파생 데이터로 관리한다.
-수용 기준: Given 같은 voc_id의 원본과 학습 행이 있을 때 / When lineage를 검사하면 / Then 원본 변경 없이 학습 입력·감성·label version을 재현할 수 있다.</x:v>
-      </x:c>
-      <x:c r="G11" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 3주차
-산출물: DB/저장소 설계 문서
-참고: 선행 DAT-001</x:v>
+      <x:c r="B11" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C11" s="207" t="str">
+        <x:v>결과</x:v>
+      </x:c>
+      <x:c r="D11" s="209" t="str">
+        <x:v>REQ-F-007</x:v>
+      </x:c>
+      <x:c r="E11" s="208" t="str">
+        <x:v>Gate를 모두 통과한 요청만 표·차트·요약 결과를 반환해야 한다.</x:v>
+      </x:c>
+      <x:c r="F11" s="208" t="str">
+        <x:v>G3 이전 결과는 사용자 설명 또는 성공 Artifact로 저장하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G11" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H11" s="2"/>
       <x:c r="I11" s="2"/>
@@ -1558,36 +1541,27 @@
       <x:c r="Y11" s="2"/>
       <x:c r="Z11" s="2"/>
     </x:row>
-    <x:row r="12" ht="151" customHeight="1">
-      <x:c r="A12" s="162" t="str">
+    <x:row r="12" ht="72" customHeight="1">
+      <x:c r="A12" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B12" s="162" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C12" s="136" t="str">
-        <x:v>운영지표</x:v>
-      </x:c>
-      <x:c r="D12" s="179" t="str">
-        <x:v>DAT-003</x:v>
-      </x:c>
-      <x:c r="E12" s="183" t="str">
-        <x:v>시스템은 매출·예약·투숙·인력 운영 데이터를 단일 테이블로 저장해야 한다.</x:v>
-      </x:c>
-      <x:c r="F12" s="192" t="str">
-        <x:v>정의·상세: hotel_operation_daily 하나에 operation_id, business_date, location, sales_amount, operating_cost, reservation_count, checkin_count, checkout_count, staff_count, dataset/schema version을 둔다. operating_profit은 sales_amount-operating_cost로 조회 시 계산하며 별도 매출·객실·조식·인력 fact를 만들지 않는다.
-대상 사용자: 데이터 담당
-입력→처리→출력: 합성 운영 데이터 → 스키마 매핑·적재 → 운영지표 테이블
-업무 규칙·예외: synthetic 표시·생성규칙·seed·schema_version 기록.
-수용 기준: Given 합성 운영 데이터가 pre-load validation을 통과했을 때 / When 적재하면 / Then 일자·장소 grain의 단일 행으로 저장되고 수익은 저장값과 동일 공식으로 재현된다.</x:v>
-      </x:c>
-      <x:c r="G12" s="194" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 3주차
-산출물: DB/저장소 설계 문서
-참고: 선행 DAT-007 · 비고: 내부 생성 합성 데이터</x:v>
+      <x:c r="B12" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C12" s="207" t="str">
+        <x:v>결과</x:v>
+      </x:c>
+      <x:c r="D12" s="209" t="str">
+        <x:v>REQ-F-008</x:v>
+      </x:c>
+      <x:c r="E12" s="208" t="str">
+        <x:v>결과에는 질문 조건과 해석에 필요한 근거를 함께 표시해야 한다.</x:v>
+      </x:c>
+      <x:c r="F12" s="208" t="str">
+        <x:v>최소 지표, 기간, 필터, as_of, source, DataHub URN, Trino FQN, Context release를 제공한다.</x:v>
+      </x:c>
+      <x:c r="G12" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H12" s="2"/>
       <x:c r="I12" s="2"/>
@@ -1609,36 +1583,27 @@
       <x:c r="Y12" s="2"/>
       <x:c r="Z12" s="2"/>
     </x:row>
-    <x:row r="13" ht="164" customHeight="1">
-      <x:c r="A13" s="162" t="str">
+    <x:row r="13" ht="72" customHeight="1">
+      <x:c r="A13" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B13" s="162" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C13" s="101" t="str">
-        <x:v>분석 결과</x:v>
-      </x:c>
-      <x:c r="D13" s="180" t="str">
-        <x:v>DAT-004</x:v>
-      </x:c>
-      <x:c r="E13" s="186" t="str">
-        <x:v>시스템은 교차분석 결과를 이력으로 저장해야 한다.</x:v>
-      </x:c>
-      <x:c r="F13" s="193" t="str">
-        <x:v>정의·상세: analysis_run에 run·batch·dataset·rule·상태·trigger·version을 저장하고, evidence에 source·관측 시각·evidence kind(관측·지지·반대·부족)·값·단위·version을 연결한다. 원인 후보와 점검 항목은 contract v0의 결과 schema로 저장한다.
-대상 사용자: 분석 담당
-입력→처리→출력: VOC·운영지표 → 교차분석 run·evidence 적재 → versioned 분석 결과
-업무 규칙·예외: 노출되는 관측·후보 문장은 evidence ID 필수이며 반대·부족 근거를 별도 kind로 보존한다.
-수용 기준: Given 교차분석을 수행했을 때 / When 저장하면 / Then dataset·rule·analysis version과 관측·지지·반대·부족 evidence ID가 같은 run에 연결된다.</x:v>
-      </x:c>
-      <x:c r="G13" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 4주차
-산출물: DB/저장소 설계 문서
-참고: 선행 DAT-007 · 비고: 스키마·지표 정의는 경량 시맨틱 카탈로그와 일치시키고 AI-008 결과를 적재</x:v>
+      <x:c r="B13" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C13" s="207" t="str">
+        <x:v>결과</x:v>
+      </x:c>
+      <x:c r="D13" s="209" t="str">
+        <x:v>REQ-F-009</x:v>
+      </x:c>
+      <x:c r="E13" s="208" t="str">
+        <x:v>사용자는 검증된 결과를 Artifact로 저장하고 보고서 편집기로 전달할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F13" s="208" t="str">
+        <x:v>Artifact는 원 요청·결과 checksum·근거·policy/model/context version을 참조하며 임의 숫자 복사를 허용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G13" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H13" s="2"/>
       <x:c r="I13" s="2"/>
@@ -1660,36 +1625,27 @@
       <x:c r="Y13" s="2"/>
       <x:c r="Z13" s="2"/>
     </x:row>
-    <x:row r="14" ht="177" customHeight="1">
-      <x:c r="A14" s="162" t="str">
+    <x:row r="14" ht="72" customHeight="1">
+      <x:c r="A14" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B14" s="162" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C14" s="134" t="str">
-        <x:v>저장 원칙</x:v>
-      </x:c>
-      <x:c r="D14" s="169" t="str">
-        <x:v>DAT-005</x:v>
-      </x:c>
-      <x:c r="E14" s="182" t="str">
-        <x:v>시스템은 원본 리뷰와 학습용 파생 데이터의 lineage를 분리 보존해야 한다.</x:v>
-      </x:c>
-      <x:c r="F14" s="191" t="str">
-        <x:v>정의·상세: versioned source fixture와 voc_review_raw를 원본 계층으로, voc_training_dataset을 번역·정규화·label이 포함된 파생 계층으로 둔다. 둘은 voc_id와 dataset version으로 연결하고 파생 데이터는 재생성할 수 있어야 한다. 개인정보성 공격 fixture는 test 전용이며 DB에 보존하지 않는다.
-대상 사용자: 데이터 담당
-입력→처리→출력: 합성 source fixture → validation·원본 적재 → 번역·정규화·label 파생 → lineage가 있는 학습 데이터
-업무 규칙·예외: validation 통과 source만 lineage fixture에 보존하고 실패 batch는 적재하지 않는다.
-수용 기준: Given 정상 합성 VOC를 정규화했을 때 / When 적재하면 / Then source fixture·voc_review_raw·voc_training_dataset이 같은 voc_id와 각 version으로 연결된다. Given 개인정보성 공격 fixture일 때 / Then DB 저장 0건이 확인된다.</x:v>
-      </x:c>
-      <x:c r="G14" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 3주차
-산출물: 데이터 전처리 결과서
-참고: 선행 DAT-001</x:v>
+      <x:c r="B14" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C14" s="207" t="str">
+        <x:v>오류 처리</x:v>
+      </x:c>
+      <x:c r="D14" s="209" t="str">
+        <x:v>REQ-F-010</x:v>
+      </x:c>
+      <x:c r="E14" s="208" t="str">
+        <x:v>실패 응답은 정규화된 오류 분류와 재시도 가능 여부를 제공해야 한다.</x:v>
+      </x:c>
+      <x:c r="F14" s="208" t="str">
+        <x:v>DB 원문 오류, stack trace, credential, 내부 정책 상세와 모델 CoT는 노출하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G14" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H14" s="2"/>
       <x:c r="I14" s="2"/>
@@ -1711,36 +1667,27 @@
       <x:c r="Y14" s="2"/>
       <x:c r="Z14" s="2"/>
     </x:row>
-    <x:row r="15" ht="125" customHeight="1">
-      <x:c r="A15" s="162" t="str">
+    <x:row r="15" ht="72" customHeight="1">
+      <x:c r="A15" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B15" s="162" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C15" s="141" t="str">
-        <x:v>벡터DB</x:v>
-      </x:c>
-      <x:c r="D15" s="171" t="str">
-        <x:v>DAT-006</x:v>
-      </x:c>
-      <x:c r="E15" s="183" t="str">
-        <x:v>팀은 근거 리뷰 검색을 위한 벡터DB 인덱싱을 독립 실험으로 검증해야 한다.</x:v>
-      </x:c>
-      <x:c r="F15" s="192" t="str">
-        <x:v>정의·상세: 근거 리뷰 검색 전용(수치 계산엔 미사용). 정제 리뷰/근거 문장을 pgvector로 임베딩·인덱싱하고 검색 정확도·속도를 검증한다. 공식 산출물 명칭은 유지하되 GraphDB는 구축하지 않으며 미도입 사유와 향후 적용 조건을 결과서에 기록한다.
-대상 사용자: 백엔드 담당
-입력→처리→출력: 정제 리뷰·임베딩 → 인덱싱 → 벡터 인덱스·검색
-업무 규칙·예외: 수치는 SQL과 카탈로그 정의로 계산하고, 벡터DB는 근거 검색 실험에만 사용한다.
-수용 기준: Given 리뷰가 임베딩됐을 때 / When 주제·키워드로 검색하면 / Then 근거 리뷰가 유사도 순으로 반환된다.</x:v>
-      </x:c>
-      <x:c r="G15" s="194" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:임베딩 검색
-담당: B 백엔드·통합(김재홍)
-실행·검증: 4주차
-산출물: 벡터DB/GraphDB 구축 결과서
-참고: 선행 DAT-001 · 화면: 근거 리뷰 · 비고: 🎓 교육 산출물 제약 · 근거 검색 가치 기준 도입</x:v>
+      <x:c r="B15" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C15" s="207" t="str">
+        <x:v>캐시</x:v>
+      </x:c>
+      <x:c r="D15" s="209" t="str">
+        <x:v>REQ-F-011</x:v>
+      </x:c>
+      <x:c r="E15" s="208" t="str">
+        <x:v>승인된 SQL plan과 shaped result는 권한 및 버전 경계 안에서 재사용할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F15" s="208" t="str">
+        <x:v>cache key에 entitlement, Context/policy/model version, source watermark를 포함하고 Gate를 우회하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G15" s="208" t="str">
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="H15" s="2"/>
       <x:c r="I15" s="2"/>
@@ -1762,36 +1709,27 @@
       <x:c r="Y15" s="2"/>
       <x:c r="Z15" s="2"/>
     </x:row>
-    <x:row r="16" ht="177" customHeight="1">
-      <x:c r="A16" s="162" t="str">
+    <x:row r="16" ht="72" customHeight="1">
+      <x:c r="A16" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B16" s="162" t="str">
-        <x:v>데이터 요구사항</x:v>
-      </x:c>
-      <x:c r="C16" s="101" t="str">
-        <x:v>시맨틱 카탈로그</x:v>
-      </x:c>
-      <x:c r="D16" s="166" t="str">
-        <x:v>DAT-007</x:v>
-      </x:c>
-      <x:c r="E16" s="187" t="str">
-        <x:v>시스템은 지표·용어·허용 차원·조회 범위·권한을 정의한 경량 시맨틱 카탈로그를 관리해야 한다.</x:v>
-      </x:c>
-      <x:c r="F16" s="193" t="str">
-        <x:v>정의·상세: 평점·매출·운영수익 등 지표 공식, 동의어, 조회 가능한 필드·집계 단위·역할 범위를 metric_catalog에 고정한다. Baseline 업무 데이터는 hotel_operation_daily, voc_review_raw, voc_training_dataset, internal_staff, alert_action, hotel_document 6개 핵심 테이블로 제한한다. hotel_document는 document_id, document_type, title, content, version, effective_at, is_active를 저장한다. manifest·job·audit·report 같은 재현·플랫폼 이력은 업무 테이블 수와 분리해 필요한 최소 entity만 유지한다.
-대상 사용자: 분석 담당
-입력→처리→출력: 스키마·지표·권한 정의 → 카탈로그 등록·검토 → 버전이 있는 정의 레지스트리
-업무 규칙·예외: 지표는 정의층으로만 계산(LLM 추측 금지).
-수용 기준: Given 지표 질의 시 / When 조회 계획을 만들면 / Then 카탈로그에 정의된 공식·차원·권한만 사용하고 미정의 항목은 실행하지 않는다.</x:v>
-      </x:c>
-      <x:c r="G16" s="195" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(정의)
-담당: D AI·Agent(윤대성)
-실행·검증: 3주차
-산출물: AI 시스템 아키텍처
-참고: 비고: 정식 온톨로지가 아닌 관계형 스키마 기반의 최소 정의층. 실시간 모니터링은 핵심 테이블의 조회 view이며 별도 원천 테이블이 아니다.</x:v>
+      <x:c r="B16" s="211" t="str">
+        <x:v>기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C16" s="207" t="str">
+        <x:v>내보내기</x:v>
+      </x:c>
+      <x:c r="D16" s="209" t="str">
+        <x:v>REQ-F-012</x:v>
+      </x:c>
+      <x:c r="E16" s="208" t="str">
+        <x:v>권한이 있는 사용자는 승인된 결과 또는 감사 metadata를 내보낼 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F16" s="208" t="str">
+        <x:v>원시 대량 행 대신 Result Shaper 상한을 적용하고 내보내기 동작을 감사 기록으로 남긴다.</x:v>
+      </x:c>
+      <x:c r="G16" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H16" s="2"/>
       <x:c r="I16" s="2"/>
@@ -1813,36 +1751,27 @@
       <x:c r="Y16" s="2"/>
       <x:c r="Z16" s="2"/>
     </x:row>
-    <x:row r="17" ht="125" customHeight="1">
-      <x:c r="A17" s="163" t="str">
+    <x:row r="17" ht="72" customHeight="1">
+      <x:c r="A17" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B17" s="163" t="str">
+      <x:c r="B17" s="211" t="str">
         <x:v>데이터 요구사항</x:v>
       </x:c>
-      <x:c r="C17" s="134" t="str">
-        <x:v>합성 파이프라인</x:v>
-      </x:c>
-      <x:c r="D17" s="169" t="str">
-        <x:v>DAT-008</x:v>
-      </x:c>
-      <x:c r="E17" s="182" t="str">
-        <x:v>시스템은 스키마 정의서→생성→전처리→검증→정답표로 이어지는 합성 데이터 파이프라인을 구축해야 한다.</x:v>
-      </x:c>
-      <x:c r="F17" s="191" t="str">
-        <x:v>정의·상세: ①schema·지표·시간 계약 ②고정 seed 생성 ③scenario 주입 ④pre-load validation ⑤PostgreSQL 적재·batch READY ⑥post-load analytical Gate ⑦정답 manifest·회귀 fixture 구축.
-대상 사용자: 데이터 담당
-입력→처리→출력: 가정·분포 → 생성·주입·정제·검증 → 검증된 데이터셋·정답표
-업무 규칙·예외: 임의 생성이 아니며 명시한 가정·분포에서 생성·검증한다. 고객 이름·전화·이메일·예약번호와 직원 이름·사번 등 식별정보는 생성하지 않는다.
-수용 기준: Given 가정·분포를 정의했을 때 / When 생성·검증하면 / Then 분포·상관·무결성이 가정과 일치하고 정답표가 산출된다.</x:v>
-      </x:c>
-      <x:c r="G17" s="196" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 2~3주차
-산출물: 수집 데이터 보고서·데이터 전처리 결과서
-참고: 선행 DAT-007 · 비고: 합성 당위성 방어</x:v>
+      <x:c r="C17" s="207" t="str">
+        <x:v>합성 데이터</x:v>
+      </x:c>
+      <x:c r="D17" s="209" t="str">
+        <x:v>REQ-D-001</x:v>
+      </x:c>
+      <x:c r="E17" s="208" t="str">
+        <x:v>개발·시험·시연에는 실제 고객 데이터 대신 합성 데이터만 사용해야 한다.</x:v>
+      </x:c>
+      <x:c r="F17" s="208" t="str">
+        <x:v>화면과 증거에 synthetic, deterministic seed, schema version, scenario version을 기록한다.</x:v>
+      </x:c>
+      <x:c r="G17" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H17" s="2"/>
       <x:c r="I17" s="2"/>
@@ -1864,36 +1793,27 @@
       <x:c r="Y17" s="2"/>
       <x:c r="Z17" s="2"/>
     </x:row>
-    <x:row r="18" ht="99" customHeight="1">
-      <x:c r="A18" s="164" t="str">
+    <x:row r="18" ht="72" customHeight="1">
+      <x:c r="A18" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B18" s="164" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C18" s="141" t="str">
-        <x:v>인증</x:v>
-      </x:c>
-      <x:c r="D18" s="171" t="str">
-        <x:v>FUN-001</x:v>
-      </x:c>
-      <x:c r="E18" s="183" t="str">
-        <x:v>사내 사용자는 Django session 기반 계정으로 로그인할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F18" s="192" t="str">
-        <x:v>정의·상세: Django 인증 기반 실제 로그인과 비밀번호 해시 저장을 적용하고 Django session을 사용한다. JWT·SSO는 승인 후 확장이다.
-대상 사용자: 전 사용자
-입력→처리→출력: 계정·비밀번호 → 자격 검증·session 생성 → 역할 범위 적용
-업무 규칙·예외: 5회 실패 시 잠금(가정).
-수용 기준: Given 활성 계정일 때 / When 올바른 자격으로 로그인하면 / Then session이 생성되고 서버가 역할 범위를 강제한다.</x:v>
-      </x:c>
-      <x:c r="G18" s="197" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 3주차 골격·5주차 Gate
-산출물: 웹 애플리케이션
-참고: 화면: 로그인 · 비고: Level 2</x:v>
+      <x:c r="B18" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C18" s="207" t="str">
+        <x:v>소스 구성</x:v>
+      </x:c>
+      <x:c r="D18" s="209" t="str">
+        <x:v>REQ-D-002</x:v>
+      </x:c>
+      <x:c r="E18" s="208" t="str">
+        <x:v>시스템은 기획서에서 정의한 5개 논리 소스와 4종 엔진의 registry를 관리해야 한다.</x:v>
+      </x:c>
+      <x:c r="F18" s="208" t="str">
+        <x:v>logical source, physical engine, owner, schema, ingestion, Trino catalog, 상태를 식별할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="G18" s="208" t="str">
+        <x:v>P1·필수</x:v>
       </x:c>
       <x:c r="H18" s="2"/>
       <x:c r="I18" s="2"/>
@@ -1915,36 +1835,27 @@
       <x:c r="Y18" s="2"/>
       <x:c r="Z18" s="2"/>
     </x:row>
-    <x:row r="19" ht="112" customHeight="1">
-      <x:c r="A19" s="162" t="str">
+    <x:row r="19" ht="72" customHeight="1">
+      <x:c r="A19" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B19" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C19" s="101" t="str">
-        <x:v>권한</x:v>
-      </x:c>
-      <x:c r="D19" s="166" t="str">
-        <x:v>FUN-002</x:v>
-      </x:c>
-      <x:c r="E19" s="187" t="str">
-        <x:v>시스템은 역할 기반으로 메뉴와 데이터 범위를 제한해야 한다.</x:v>
-      </x:c>
-      <x:c r="F19" s="193" t="str">
-        <x:v>정의·상세: HOTEL_MANAGER, FNB_MANAGER, ROOMS_MANAGER 역할별 허용 metric·view 범위를 구분하고 Django가 검증한 scope_snapshot만 FastAPI에 전달한다.
-대상 사용자: 전 사용자
-입력→처리→출력: 사용자 역할 → 역할-권한 매핑 검사 → 허용 메뉴·데이터
-업무 규칙·예외: 비인가 접근 차단.
-수용 기준: Given 권한 없는 사용자일 때 / When 관리자 설정에 접근하면 / Then 거부되고 안내가 표시된다.</x:v>
-      </x:c>
-      <x:c r="G19" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 3주차 골격·5주차 Gate
-산출물: 웹 애플리케이션
-참고: 선행 FUN-001 · 비고: 실제 조직 권한이 아닌 프로젝트 데모 정책</x:v>
+      <x:c r="B19" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C19" s="207" t="str">
+        <x:v>읽기 전용</x:v>
+      </x:c>
+      <x:c r="D19" s="209" t="str">
+        <x:v>REQ-D-003</x:v>
+      </x:c>
+      <x:c r="E19" s="208" t="str">
+        <x:v>원천 데이터 접근 계정과 Trino 조회 경로는 읽기 전용이어야 한다.</x:v>
+      </x:c>
+      <x:c r="F19" s="208" t="str">
+        <x:v>DDL·DML·mutation 시도를 거부하는 자동 검증 증거를 제공한다.</x:v>
+      </x:c>
+      <x:c r="G19" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H19" s="2"/>
       <x:c r="I19" s="2"/>
@@ -1966,36 +1877,27 @@
       <x:c r="Y19" s="2"/>
       <x:c r="Z19" s="2"/>
     </x:row>
-    <x:row r="20" ht="138" customHeight="1">
-      <x:c r="A20" s="162" t="str">
+    <x:row r="20" ht="72" customHeight="1">
+      <x:c r="A20" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B20" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C20" s="134" t="str">
-        <x:v>관리자 파일 업로드</x:v>
-      </x:c>
-      <x:c r="D20" s="169" t="str">
-        <x:v>FUN-003</x:v>
-      </x:c>
-      <x:c r="E20" s="182" t="str">
-        <x:v>팀이 관리자 파일 업로드를 통한 데이터 일괄 적재를 승인한 경우에만 합성 리뷰·운영 파일의 형식과 필수 컬럼을 검증해야 한다.</x:v>
-      </x:c>
-      <x:c r="F20" s="191" t="str">
-        <x:v>정의·상세: Baseline 데이터는 고정 seed 생성기가 내부 적재하므로 사용자 업로드 화면을 만들지 않는다. 팀이 관리자 파일 업로드를 통한 데이터 일괄 적재의 필요성을 승인하면 파일 형식·필수 컬럼 검증과 실패 원인을 정의한다.
-대상 사용자: 시스템 관리자, 데이터 담당
-입력→처리→출력: 관리자가 업로드한 승인 대상 합성 파일 → 형식·컬럼 검증 → 결과·실패 원인
-업무 규칙·예외: 필수 컬럼 누락 시 저장 안 함.
-수용 기준: Given 팀이 관리자 파일 업로드를 통한 데이터 일괄 적재를 범위에 편입했을 때 / When 필수 컬럼이 누락된 파일을 업로드하면 / Then 누락 컬럼명을 표시하고 적재하지 않는다.</x:v>
-      </x:c>
-      <x:c r="G20" s="191" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 승인 후
-산출물: 수집 데이터 보고서
-참고: 선행 DAT-008 · 비고: 현재 Baseline 제외, 필수 컬럼 기준=스키마 정의서</x:v>
+      <x:c r="B20" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C20" s="207" t="str">
+        <x:v>재현성</x:v>
+      </x:c>
+      <x:c r="D20" s="209" t="str">
+        <x:v>REQ-D-004</x:v>
+      </x:c>
+      <x:c r="E20" s="208" t="str">
+        <x:v>합성 데이터 생성은 동일 seed·schema·scenario version에서 결정론적으로 재현되어야 한다.</x:v>
+      </x:c>
+      <x:c r="F20" s="208" t="str">
+        <x:v>재생성 후 대표 fixture의 row count와 checksum을 비교한다.</x:v>
+      </x:c>
+      <x:c r="G20" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H20" s="2"/>
       <x:c r="I20" s="2"/>
@@ -2017,36 +1919,27 @@
       <x:c r="Y20" s="2"/>
       <x:c r="Z20" s="2"/>
     </x:row>
-    <x:row r="21" ht="112" customHeight="1">
-      <x:c r="A21" s="163" t="str">
+    <x:row r="21" ht="72" customHeight="1">
+      <x:c r="A21" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B21" s="163" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C21" s="141" t="str">
-        <x:v>업로드 파일 검증</x:v>
-      </x:c>
-      <x:c r="D21" s="171" t="str">
-        <x:v>FUN-004</x:v>
-      </x:c>
-      <x:c r="E21" s="183" t="str">
-        <x:v>팀이 관리자 파일 업로드를 통한 데이터 일괄 적재를 승인한 경우에만 중복·오류 행을 탐지하고 표시해야 한다.</x:v>
-      </x:c>
-      <x:c r="F21" s="192" t="str">
-        <x:v>정의·상세: 관리자 파일 업로드를 통한 데이터 일괄 적재가 승인될 때만 키 기준 중복·오류 행 탐지와 표시 방식을 정의한다. 생성기 내부 품질 검증은 DAT-008에 포함한다.
-대상 사용자: 시스템 관리자, 데이터 담당
-입력→처리→출력: 관리자가 업로드한 데이터 → 중복·오류 검사 → 중복·오류 행 목록
-업무 규칙·예외: 중복 저장 안 함.
-수용 기준: Given 동일 review_id 존재 시 / When 재업로드하면 / Then 중복 표시하고 저장하지 않는다.</x:v>
-      </x:c>
-      <x:c r="G21" s="192" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 승인 후
-산출물: 데이터 전처리 결과서
-참고: 선행 FUN-003 · 비고: 현재 Baseline 제외</x:v>
+      <x:c r="B21" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C21" s="207" t="str">
+        <x:v>DataHub</x:v>
+      </x:c>
+      <x:c r="D21" s="209" t="str">
+        <x:v>REQ-D-005</x:v>
+      </x:c>
+      <x:c r="E21" s="208" t="str">
+        <x:v>DataHub는 자산 URN, schema, owner, tag, lineage와 ingestion 상태의 기준 시스템이어야 한다.</x:v>
+      </x:c>
+      <x:c r="F21" s="208" t="str">
+        <x:v>앱 DB가 DataHub schema를 독립 복제해 기준 시스템처럼 사용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G21" s="208" t="str">
+        <x:v>P1·필수</x:v>
       </x:c>
       <x:c r="H21" s="2"/>
       <x:c r="I21" s="2"/>
@@ -2068,36 +1961,27 @@
       <x:c r="Y21" s="2"/>
       <x:c r="Z21" s="2"/>
     </x:row>
-    <x:row r="22" ht="151" customHeight="1">
-      <x:c r="A22" s="165" t="str">
+    <x:row r="22" ht="72" customHeight="1">
+      <x:c r="A22" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B22" s="165" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C22" s="101" t="str">
-        <x:v>전처리·번역</x:v>
-      </x:c>
-      <x:c r="D22" s="166" t="str">
-        <x:v>FUN-005</x:v>
-      </x:c>
-      <x:c r="E22" s="187" t="str">
-        <x:v>시스템은 합성 VOC를 정규화·한국어 번역하고 개인정보성 값이 포함되지 않았는지 검증해야 한다.</x:v>
-      </x:c>
-      <x:c r="F22" s="193" t="str">
-        <x:v>정의·상세: HTML·특수문자 정리, 정규화, 완전중복 제거, 언어 식별을 수행한다. 외국어 VOC는 원문을 보존한 채 한국어 번역을 생성하고 번역 버전을 기록한다. 생성 금지한 이름·전화·이메일·예약번호 형식이 발견되면 원문을 임의 치환하지 않고 적재를 거부한다.
-대상 사용자: 데이터 담당
-입력→처리→출력: 합성 리뷰 원문 → 정규화·금지 패턴 검사 → 합성 원문·정제 리뷰·검증 결과
-업무 규칙·예외: 실제 개인정보 입력을 전제로 하지 않는다. 합성 원문 보존은 허용하되 개인정보성 값 검사를 통과한 데이터만 저장한다.
-수용 기준: Given 외국어 합성 VOC일 때 / When 전처리하면 / Then 원문·언어 코드·한국어 번역·번역 버전이 연결된다. Given 생성 금지 패턴이 들어간 합성 테스트 데이터일 때 / Then 해당 batch의 적재가 차단되고 사유가 기록된다.</x:v>
-      </x:c>
-      <x:c r="G22" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 3주차
-산출물: 데이터 전처리 결과서
-참고: 선행 DAT-005,DAT-008 · 비고: SEC-001 연계</x:v>
+      <x:c r="B22" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C22" s="207" t="str">
+        <x:v>Trino</x:v>
+      </x:c>
+      <x:c r="D22" s="209" t="str">
+        <x:v>REQ-D-006</x:v>
+      </x:c>
+      <x:c r="E22" s="208" t="str">
+        <x:v>승인된 분석 SQL은 Trino를 단일 제품 조회 경로로 실행해야 한다.</x:v>
+      </x:c>
+      <x:c r="F22" s="208" t="str">
+        <x:v>앱 내부 federation 또는 DuckDB 제품 경로를 추가하지 않으며 fallback은 별도 승인과 표기를 요구한다.</x:v>
+      </x:c>
+      <x:c r="G22" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H22" s="2"/>
       <x:c r="I22" s="2"/>
@@ -2119,36 +2003,27 @@
       <x:c r="Y22" s="2"/>
       <x:c r="Z22" s="2"/>
     </x:row>
-    <x:row r="23" ht="180" customHeight="1">
-      <x:c r="A23" s="162" t="str">
+    <x:row r="23" ht="72" customHeight="1">
+      <x:c r="A23" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B23" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C23" s="141" t="str">
-        <x:v>대화형 분석</x:v>
-      </x:c>
-      <x:c r="D23" s="171" t="str">
-        <x:v>FUN-006</x:v>
-      </x:c>
-      <x:c r="E23" s="183" t="str">
-        <x:v>시스템은 보장 분석 의도 8종만 검증된 조회로 처리하고 미지원 질문은 SQL을 실행하지 않아야 한다.</x:v>
-      </x:c>
-      <x:c r="F23" s="192" t="str">
-        <x:v>정의·상세: ① 평점 요약 ② 전주·최근 4주 비교 ③ 일별 추이 ④ 장소별 매출 ⑤ 장소별 운영수익 ⑥ 예약·체크인·체크아웃 비교 ⑦ 인력·운영 비교 ⑧ 이상징후 근거 조회를 보장한다. VOC 질문의 최초 응답은 평점 요약만 제공하고, 사용자가 저점 리뷰 근거를 추가로 요청할 때만 voc_review_raw를 join해 기본 최근 분기, 확대 시 최대 최근 반기 내 rating&lt;=3 리뷰를 반환한다. 그보다 오래된 리뷰는 제외한다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 자연어 질문 → 의도 분류·파라미터·조회·규칙 계산 → 분석 카드(과정·결과·근거)
-업무 규칙·예외: 장소·매출·운영수익은 관리자 판단에 필요한 최소 지표만 표시한다. 리뷰 원문은 최초 응답에 포함하지 않고 명시적 추가 질의·권한·기간 조건을 모두 충족해야 조회한다. 미지원 질문은 SQL을 실행하지 않는다.
-수용 기준: Given VOC 최초 질문일 때 / When 처리하면 / Then 평점과 기간·표본만 표시된다. Given 저점 근거 추가 질의일 때 / When 처리하면 / Then 선택 분기 또는 최근 반기 내 3점 이하 리뷰만 표시된다.</x:v>
-      </x:c>
-      <x:c r="G23" s="192" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:query plan 해석+결정론 SQL builder
-담당: D AI·Agent(윤대성) / B 백엔드·통합(김재홍) / A 프론트·UX(송민지)
-실행·검증: 5주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 AI-008,AI-009,AI-010,INT-001 · 비고: 보장세트+가드레일 text-to-SQL</x:v>
+      <x:c r="B23" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C23" s="207" t="str">
+        <x:v>자산 매핑</x:v>
+      </x:c>
+      <x:c r="D23" s="209" t="str">
+        <x:v>REQ-D-007</x:v>
+      </x:c>
+      <x:c r="E23" s="208" t="str">
+        <x:v>실행 가능한 자산은 DataHub URN과 Trino catalog.schema.table을 연결해야 한다.</x:v>
+      </x:c>
+      <x:c r="F23" s="208" t="str">
+        <x:v>active mapping이 없거나 불일치하면 Context Package에 포함하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G23" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H23" s="2"/>
       <x:c r="I23" s="2"/>
@@ -2170,36 +2045,27 @@
       <x:c r="Y23" s="2"/>
       <x:c r="Z23" s="2"/>
     </x:row>
-    <x:row r="24" ht="138" customHeight="1">
-      <x:c r="A24" s="162" t="str">
+    <x:row r="24" ht="72" customHeight="1">
+      <x:c r="A24" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B24" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C24" s="101" t="str">
-        <x:v>대응 옵션</x:v>
-      </x:c>
-      <x:c r="D24" s="166" t="str">
-        <x:v>FUN-007</x:v>
-      </x:c>
-      <x:c r="E24" s="187" t="str">
-        <x:v>시스템은 원인 후보별 대응 옵션을 제시하고 사용자가 검토·메모할 수 있어야 한다(자동 실행 금지).</x:v>
-      </x:c>
-      <x:c r="F24" s="193" t="str">
-        <x:v>정의·상세: 원인 후보와 대응 옵션을 즉시 해결 가능 또는 담당자 확인·현장 조치 필요로 분류한다. 전자는 승인된 매뉴얼에 근거한 정보 안내·단순 설정 확인으로 제한하고, 환불·결제·객실 배정·안전·시설 고장·권한 부족·근거 부족은 후자로 분류해 internal_staff의 담당자에게 alert_action을 생성한다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 원인 후보·매뉴얼 근거 → 해결 가능성 분류·담당자 매핑 → 옵션·알림·조치 여부·메모
-업무 규칙·예외: 자동 실행 금지(BIZ-004).
-수용 기준: Given 원인 후보 생성 시 / When 분류하면 / Then 해결 가능성·담당 부서·근거가 표시되고 담당자 확인이 필요하면 알림·조치 여부·메모 이력이 저장된다.</x:v>
-      </x:c>
-      <x:c r="G24" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차 Gate
-산출물: LLM 활용 소프트웨어
-참고: 선행 AI-009 · 화면: 운영 원인 분석</x:v>
+      <x:c r="B24" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C24" s="207" t="str">
+        <x:v>공통키·JOIN</x:v>
+      </x:c>
+      <x:c r="D24" s="209" t="str">
+        <x:v>REQ-D-008</x:v>
+      </x:c>
+      <x:c r="E24" s="208" t="str">
+        <x:v>교차 소스 JOIN은 승인된 공통키·cardinality·time 계약만 사용해야 한다.</x:v>
+      </x:c>
+      <x:c r="F24" s="208" t="str">
+        <x:v>승인되지 않은 관계 또는 fan-out 위험 관계는 G1/G2에서 차단한다.</x:v>
+      </x:c>
+      <x:c r="G24" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H24" s="2"/>
       <x:c r="I24" s="2"/>
@@ -2221,36 +2087,27 @@
       <x:c r="Y24" s="2"/>
       <x:c r="Z24" s="2"/>
     </x:row>
-    <x:row r="25" ht="112" customHeight="1">
-      <x:c r="A25" s="162" t="str">
+    <x:row r="25" ht="72" customHeight="1">
+      <x:c r="A25" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B25" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C25" s="134" t="str">
-        <x:v>분류 보정</x:v>
-      </x:c>
-      <x:c r="D25" s="169" t="str">
-        <x:v>FUN-008</x:v>
-      </x:c>
-      <x:c r="E25" s="182" t="str">
-        <x:v>팀이 승인한 경우 사용자는 감성·주제 분류 결과를 수정하고 수정 이력을 저장할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F25" s="191" t="str">
-        <x:v>정의·상세: AI 1차 분류 후 사용자가 오분류 수정, 수정자·시점·원본값 보존.
-대상 사용자: 실무자
-입력→처리→출력: 분류 결과 → 수동 수정·이력 기록 → 수정 결과·이력
-업무 규칙·예외: 원본 분류값 보존.
-수용 기준: Given 분류 결과 표시 시 / When 사용자가 수정하면 / Then 변경값과 수정자·시점이 저장된다.</x:v>
-      </x:c>
-      <x:c r="G25" s="191" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: AI:LLM/sLLM 분류 보정
-담당: D AI·Agent(윤대성)
-실행·검증: 승인 후
-산출물: LLM 활용 소프트웨어
-참고: 선행 AI-001,AI-002 · 화면: 근거 리뷰 · 비고: 현재 Baseline 제외</x:v>
+      <x:c r="B25" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C25" s="207" t="str">
+        <x:v>시간 정책</x:v>
+      </x:c>
+      <x:c r="D25" s="209" t="str">
+        <x:v>REQ-D-009</x:v>
+      </x:c>
+      <x:c r="E25" s="208" t="str">
+        <x:v>지표와 조회에는 timezone, 기준 시각, event time, snapshot/SCD 정책을 명시해야 한다.</x:v>
+      </x:c>
+      <x:c r="F25" s="208" t="str">
+        <x:v>결과와 보고서 run은 하나의 as_of와 적용 시간 정책을 표시한다.</x:v>
+      </x:c>
+      <x:c r="G25" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H25" s="2"/>
       <x:c r="I25" s="2"/>
@@ -2272,36 +2129,27 @@
       <x:c r="Y25" s="2"/>
       <x:c r="Z25" s="2"/>
     </x:row>
-    <x:row r="26" ht="112" customHeight="1">
-      <x:c r="A26" s="162" t="str">
+    <x:row r="26" ht="72" customHeight="1">
+      <x:c r="A26" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B26" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C26" s="141" t="str">
-        <x:v>관리자</x:v>
-      </x:c>
-      <x:c r="D26" s="171" t="str">
-        <x:v>FUN-009</x:v>
-      </x:c>
-      <x:c r="E26" s="183" t="str">
-        <x:v>팀이 승인한 경우 시스템 관리자는 VOC 주제 분류체계와 시설 목록을 관리할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F26" s="192" t="str">
-        <x:v>정의·상세: Django admin으로 주제·시설 CRUD 관리(구현 저비용).
-대상 사용자: 시스템 관리자
-입력→처리→출력: 분류체계·시설 → CRUD → 갱신 분류·시설
-업무 규칙·예외: 변경 시 영향 안내.
-수용 기준: Given 관리자 권한일 때 / When 주제·시설을 수정하면 / Then 분석·필터에 반영된다.</x:v>
-      </x:c>
-      <x:c r="G26" s="192" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 승인 후
-산출물: 웹 애플리케이션
-참고: 선행 FUN-002 · 화면: 관리자 설정 · 비고: Django admin</x:v>
+      <x:c r="B26" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C26" s="207" t="str">
+        <x:v>품질</x:v>
+      </x:c>
+      <x:c r="D26" s="209" t="str">
+        <x:v>REQ-D-010</x:v>
+      </x:c>
+      <x:c r="E26" s="208" t="str">
+        <x:v>소스별 필수 컬럼·타입·중복·결측·참조 무결성 규칙을 검증해야 한다.</x:v>
+      </x:c>
+      <x:c r="F26" s="208" t="str">
+        <x:v>검증 실패는 source/asset 상태와 안전한 오류 코드로 기록하고 성공 분석에서 제외한다.</x:v>
+      </x:c>
+      <x:c r="G26" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H26" s="2"/>
       <x:c r="I26" s="2"/>
@@ -2323,36 +2171,27 @@
       <x:c r="Y26" s="2"/>
       <x:c r="Z26" s="2"/>
     </x:row>
-    <x:row r="27" ht="112" customHeight="1">
-      <x:c r="A27" s="162" t="str">
+    <x:row r="27" ht="72" customHeight="1">
+      <x:c r="A27" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B27" s="162" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C27" s="101" t="str">
-        <x:v>다운로드</x:v>
-      </x:c>
-      <x:c r="D27" s="166" t="str">
-        <x:v>FUN-010</x:v>
-      </x:c>
-      <x:c r="E27" s="187" t="str">
-        <x:v>팀이 승인한 경우 사용자는 권한 범위 내에서 분석 결과를 다운로드할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F27" s="193" t="str">
-        <x:v>정의·상세: 역할 권한 따라 결과·리포트 다운로드, 이력 기록.
-대상 사용자: 관리자, 실무자
-입력→처리→출력: 분석 결과 → 권한 검사·생성 → 파일·이력
-업무 규칙·예외: 권한 없는 데이터 차단.
-수용 기준: Given 다운로드 권한 없을 때 / When 시도하면 / Then 차단되고 이력에 기록된다.</x:v>
-      </x:c>
-      <x:c r="G27" s="193" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 승인 후
-산출물: 웹 애플리케이션
-참고: 선행 FUN-002,SEC-003 · 화면: 리포트</x:v>
+      <x:c r="B27" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C27" s="207" t="str">
+        <x:v>개인정보</x:v>
+      </x:c>
+      <x:c r="D27" s="209" t="str">
+        <x:v>REQ-D-011</x:v>
+      </x:c>
+      <x:c r="E27" s="208" t="str">
+        <x:v>개인 식별 가능 데이터는 승인된 masking 및 최소 컬럼 정책을 적용해야 한다.</x:v>
+      </x:c>
+      <x:c r="F27" s="208" t="str">
+        <x:v>원문 PII는 모델 입력·로그·Artifact·화면에 노출하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G27" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H27" s="2"/>
       <x:c r="I27" s="2"/>
@@ -2374,36 +2213,27 @@
       <x:c r="Y27" s="2"/>
       <x:c r="Z27" s="2"/>
     </x:row>
-    <x:row r="28" ht="112" customHeight="1">
-      <x:c r="A28" s="163" t="str">
+    <x:row r="28" ht="72" customHeight="1">
+      <x:c r="A28" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B28" s="163" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C28" s="141" t="str">
-        <x:v>관리자</x:v>
-      </x:c>
-      <x:c r="D28" s="171" t="str">
-        <x:v>FUN-011</x:v>
-      </x:c>
-      <x:c r="E28" s="183" t="str">
-        <x:v>팀이 외부 파일 입력을 승인한 경우 시스템 관리자는 입력 데이터의 컬럼 매핑을 관리할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F28" s="192" t="str">
-        <x:v>정의·상세: 외부 파일 입력을 승인하고 컬럼명이 표준 스키마와 다를 때만 매핑 설정을 검토한다.
-대상 사용자: 시스템 관리자, 데이터 담당
-입력→처리→출력: 원본 컬럼명 → 매핑 규칙 설정·검증 → 표준화 매핑
-업무 규칙·예외: 매핑 누락 컬럼 경고.
-수용 기준: Given 표준과 다른 CSV일 때 / When 매핑하면 / Then 이후 업로드가 표준 스키마로 정규화된다.</x:v>
-      </x:c>
-      <x:c r="G28" s="192" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 승인 후
-산출물: DB/저장소 설계 문서
-참고: 선행 DAT-001 · 화면: 관리자 설정 · 비고: 필수 컬럼은 데이터 조사 후 확정</x:v>
+      <x:c r="B28" s="211" t="str">
+        <x:v>데이터 요구사항</x:v>
+      </x:c>
+      <x:c r="C28" s="207" t="str">
+        <x:v>Result Shaper</x:v>
+      </x:c>
+      <x:c r="D28" s="209" t="str">
+        <x:v>REQ-D-012</x:v>
+      </x:c>
+      <x:c r="E28" s="208" t="str">
+        <x:v>쿼리 결과는 승인된 집계·샘플링·표시 상한을 적용한 뒤 모델과 UI에 전달해야 한다.</x:v>
+      </x:c>
+      <x:c r="F28" s="208" t="str">
+        <x:v>적용된 row/column limit와 sampling evidence를 저장한다.</x:v>
+      </x:c>
+      <x:c r="G28" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H28" s="2"/>
       <x:c r="I28" s="2"/>
@@ -2425,36 +2255,27 @@
       <x:c r="Y28" s="2"/>
       <x:c r="Z28" s="2"/>
     </x:row>
-    <x:row r="29" ht="125" customHeight="1">
-      <x:c r="A29" s="165" t="str">
+    <x:row r="29" ht="72" customHeight="1">
+      <x:c r="A29" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B29" s="165" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C29" s="101" t="str">
-        <x:v>후속 질문</x:v>
-      </x:c>
-      <x:c r="D29" s="166" t="str">
-        <x:v>FUN-012</x:v>
-      </x:c>
-      <x:c r="E29" s="187" t="str">
-        <x:v>팀이 승인한 경우 시스템은 현재 결과와 지원 지표에 맞는 사전 정의 후속 질문·드릴다운을 제안할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F29" s="193" t="str">
-        <x:v>정의·상세: UX 보조 기능으로, 현재 결과의 지표·기간·시설을 기준으로 미리 검증한 질문 template을 제안한다. 정식 온톨로지나 LLM 생성에 의존하지 않는다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 현재 결과·카탈로그·질문 template → 지원 범위 검사 → 후속 질문·드릴다운
-업무 규칙·예외: 답 못 할 질문 추천 금지.
-수용 기준: Given 기능이 승인되고 결과 화면이 표시될 때 / When 후속 질문을 제안하면 / Then 카탈로그와 회귀테스트가 지원하는 template만 노출된다.</x:v>
-      </x:c>
-      <x:c r="G29" s="193" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 비AI(규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 승인 후
-산출물: 웹 애플리케이션
-참고: 선행 DAT-007,FUN-006 · 화면: 분석 에이전트 · 비고: 현재 Baseline 제외, 보조 UX</x:v>
+      <x:c r="B29" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C29" s="207" t="str">
+        <x:v>Context Layer</x:v>
+      </x:c>
+      <x:c r="D29" s="209" t="str">
+        <x:v>REQ-AI-001</x:v>
+      </x:c>
+      <x:c r="E29" s="208" t="str">
+        <x:v>Context Layer는 질문별로 승인된 지표·차원·공통키·JOIN·시간·권한 정보를 결합해야 한다.</x:v>
+      </x:c>
+      <x:c r="F29" s="208" t="str">
+        <x:v>DataHub URN을 참조하는 불변 Context release와 context_package_id를 반환한다.</x:v>
+      </x:c>
+      <x:c r="G29" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H29" s="2"/>
       <x:c r="I29" s="2"/>
@@ -2476,36 +2297,27 @@
       <x:c r="Y29" s="2"/>
       <x:c r="Z29" s="2"/>
     </x:row>
-    <x:row r="30" ht="138" customHeight="1">
-      <x:c r="A30" s="163" t="str">
+    <x:row r="30" ht="72" customHeight="1">
+      <x:c r="A30" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B30" s="163" t="str">
-        <x:v>기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C30" s="134" t="str">
-        <x:v>능동형 트리거</x:v>
-      </x:c>
-      <x:c r="D30" s="169" t="str">
-        <x:v>FUN-013</x:v>
-      </x:c>
-      <x:c r="E30" s="182" t="str">
-        <x:v>시스템은 이상징후를 자동 감지하는 트리거로 사용자 요청 없이 조사를 시작할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F30" s="191" t="str">
-        <x:v>정의·상세: 스케줄/임계값 트리거가 hotel_operation_daily와 voc_review_raw의 최신 데이터를 읽어 이상징후를 조사하고 alert_action에 알림 후보를 기록한다. D 기능을 위해 별도 실시간 원천 테이블을 만들지 않으며, 실제 stream 연동은 Baseline 밖이다.
-대상 사용자: 관리자, 실무자
-입력→처리→출력: 운영·VOC 최신 데이터와 스케줄·임계값 → 이상 감지·자동 조사 → 장소별 상태·최종 갱신 시각·담당 알림
-업무 규칙·예외: 트리거는 조사·알림까지, 조치는 승인.
-수용 기준: Given 임계값 초과 시 / When 트리거가 동작하면 / Then 자동 조사 결과가 능동형 인사이트로 표시된다.</x:v>
-      </x:c>
-      <x:c r="G30" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:에이전트 트리거
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 AI-006,FUN-006 · 화면: 실무자 대시보드 · 비고: 능동형 핵심</x:v>
+      <x:c r="B30" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C30" s="207" t="str">
+        <x:v>Context Layer</x:v>
+      </x:c>
+      <x:c r="D30" s="209" t="str">
+        <x:v>REQ-AI-002</x:v>
+      </x:c>
+      <x:c r="E30" s="208" t="str">
+        <x:v>Context 검색은 권한 필터를 먼저 적용하고 질문과 무관한 자산·컬럼을 제거해야 한다.</x:v>
+      </x:c>
+      <x:c r="F30" s="208" t="str">
+        <x:v>선택 자산과 제외 사유를 재현할 수 있는 ranking·compression metadata를 기록한다.</x:v>
+      </x:c>
+      <x:c r="G30" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H30" s="2"/>
       <x:c r="I30" s="2"/>
@@ -2527,36 +2339,27 @@
       <x:c r="Y30" s="2"/>
       <x:c r="Z30" s="2"/>
     </x:row>
-    <x:row r="31" ht="112" customHeight="1">
-      <x:c r="A31" s="167" t="str">
+    <x:row r="31" ht="72" customHeight="1">
+      <x:c r="A31" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B31" s="167" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C31" s="141" t="str">
-        <x:v>감성 실험</x:v>
-      </x:c>
-      <x:c r="D31" s="171" t="str">
-        <x:v>AI-001</x:v>
-      </x:c>
-      <x:c r="E31" s="183" t="str">
-        <x:v>팀은 합성 VOC 감성 분류 모델을 독립 실험하고 규칙 정답표와 비교해야 한다.</x:v>
-      </x:c>
-      <x:c r="F31" s="192" t="str">
-        <x:v>정의·상세: 합성 생성기의 긍정·중립·부정 정답 label을 기준으로 사전학습 모델·API LLM 등 2개 이상 방법의 정확도·지연을 오프라인 비교한다.
-대상 사용자: AI 담당
-입력→처리→출력: 합성 정제 리뷰·정답 label → 감성 분류 실험 → 성능·오류 비교표
-업무 규칙·예외: Baseline 통계·판정은 생성기 정답 label을 사용하며 모델 실험 결과에 의존하지 않는다.
-수용 기준: Given 고정된 합성 평가셋일 때 / When 두 방법을 평가하면 / Then 동일 지표의 성능·오류 사례·실험 버전이 기록된다.</x:v>
-      </x:c>
-      <x:c r="G31" s="192" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:분류 모델 비교
-담당: D AI·Agent(윤대성)
-실행·검증: 3~4주차
-산출물: ML/DL 학습결과서
-참고: 선행 FUN-005,DAT-008 · 비고: Baseline Gate 제외</x:v>
+      <x:c r="B31" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C31" s="207" t="str">
+        <x:v>G1</x:v>
+      </x:c>
+      <x:c r="D31" s="209" t="str">
+        <x:v>REQ-AI-003</x:v>
+      </x:c>
+      <x:c r="E31" s="208" t="str">
+        <x:v>G1 Context Gate는 지표·자산·JOIN·시간·권한의 완전성과 승인 여부를 검증해야 한다.</x:v>
+      </x:c>
+      <x:c r="F31" s="208" t="str">
+        <x:v>실패 시 SQL 생성을 시작하지 않고 정규화 오류와 수정 가능한 입력을 반환한다.</x:v>
+      </x:c>
+      <x:c r="G31" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H31" s="2"/>
       <x:c r="I31" s="2"/>
@@ -2578,36 +2381,27 @@
       <x:c r="Y31" s="2"/>
       <x:c r="Z31" s="2"/>
     </x:row>
-    <x:row r="32" ht="112" customHeight="1">
-      <x:c r="A32" s="165" t="str">
+    <x:row r="32" ht="72" customHeight="1">
+      <x:c r="A32" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B32" s="165" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C32" s="121" t="str">
-        <x:v>주제 실험</x:v>
-      </x:c>
-      <x:c r="D32" s="168" t="str">
-        <x:v>AI-002</x:v>
-      </x:c>
-      <x:c r="E32" s="188" t="str">
-        <x:v>팀은 합성 VOC 다중 주제 분류 모델을 독립 실험하고 규칙 정답표와 비교해야 한다.</x:v>
-      </x:c>
-      <x:c r="F32" s="198" t="str">
-        <x:v>정의·상세: 합성 생성기의 다중 주제 정답표를 기준으로 청결·소음·조식품질·조식대기·주차·부대시설 등 다중 label 분류 방법을 오프라인 비교한다.
-대상 사용자: AI 담당
-입력→처리→출력: 합성 정제 리뷰·정답 label → 다중 주제 분류 실험 → 성능·오류 비교표
-업무 규칙·예외: Baseline 분석용 주제는 생성 시 부여한 정답 label을 사용한다.
-수용 기준: Given 복수 주제 합성 리뷰일 때 / When 모델을 평가하면 / Then 주제별 성능·오류 사례·실험 버전이 기록된다.</x:v>
-      </x:c>
-      <x:c r="G32" s="198" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:분류 모델 비교
-담당: D AI·Agent(윤대성)
-실행·검증: 3~4주차
-산출물: ML/DL 학습결과서
-참고: 선행 AI-001,DAT-008 · 비고: Baseline Gate 제외</x:v>
+      <x:c r="B32" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C32" s="207" t="str">
+        <x:v>SQL 생성</x:v>
+      </x:c>
+      <x:c r="D32" s="209" t="str">
+        <x:v>REQ-AI-004</x:v>
+      </x:c>
+      <x:c r="E32" s="208" t="str">
+        <x:v>Node 2는 승인된 Context Package 안에서 Trino SQL만 생성해야 한다.</x:v>
+      </x:c>
+      <x:c r="F32" s="208" t="str">
+        <x:v>Node는 권한·실행 허용·Gate 합격을 판정하지 않으며 승인 범위 밖 자산을 추가하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G32" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H32" s="2"/>
       <x:c r="I32" s="2"/>
@@ -2629,36 +2423,27 @@
       <x:c r="Y32" s="2"/>
       <x:c r="Z32" s="2"/>
     </x:row>
-    <x:row r="33" ht="125" customHeight="1">
-      <x:c r="A33" s="162" t="str">
+    <x:row r="33" ht="72" customHeight="1">
+      <x:c r="A33" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B33" s="162" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C33" s="101" t="str">
-        <x:v>근거</x:v>
-      </x:c>
-      <x:c r="D33" s="166" t="str">
-        <x:v>AI-003</x:v>
-      </x:c>
-      <x:c r="E33" s="187" t="str">
-        <x:v>시스템은 각 분석 결과에 합성 원문의 정답 span 근거를 연결해야 한다.</x:v>
-      </x:c>
-      <x:c r="F33" s="193" t="str">
-        <x:v>정의·상세: Baseline은 합성 생성 단계에서 기록한 근거 문장 span을 원문과 연결한다. 선택 실험에서 모델 추출 결과를 비교할 수 있으나 존재하지 않는 문장을 생성하지 않는다.
-대상 사용자: AI 담당
-입력→처리→출력: 합성 리뷰·정답 span·분석 결과 → 원문 일치 검증·연결 → evidence_sentence
-업무 규칙·예외: 존재하지 않는 문장 생성 금지.
-수용 기준: Given 분석 결과를 표시할 때 / When 근거를 연결하면 / Then 원문에 실제 존재하고 정답표와 일치하는 문장만 연결된다.</x:v>
-      </x:c>
-      <x:c r="G33" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(정답 span 연결), 선택적 LLM 비교
-담당: D AI·Agent(윤대성)
-실행·검증: 4~5주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 DAT-008 · 화면: 근거 리뷰 · 비고: BIZ-003 지원</x:v>
+      <x:c r="B33" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C33" s="207" t="str">
+        <x:v>G2</x:v>
+      </x:c>
+      <x:c r="D33" s="209" t="str">
+        <x:v>REQ-AI-005</x:v>
+      </x:c>
+      <x:c r="E33" s="208" t="str">
+        <x:v>G2 SQL Policy Gate는 AST, allowlist, read-only, JOIN, 시간 함수, LIMIT와 EXPLAIN을 검증해야 한다.</x:v>
+      </x:c>
+      <x:c r="F33" s="208" t="str">
+        <x:v>문자열 검사만으로 합격시키지 않고 SQLGlot AST 및 Trino 검증 결과를 기록한다.</x:v>
+      </x:c>
+      <x:c r="G33" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H33" s="2"/>
       <x:c r="I33" s="2"/>
@@ -2680,36 +2465,27 @@
       <x:c r="Y33" s="2"/>
       <x:c r="Z33" s="2"/>
     </x:row>
-    <x:row r="34" ht="112" customHeight="1">
-      <x:c r="A34" s="162" t="str">
+    <x:row r="34" ht="72" customHeight="1">
+      <x:c r="A34" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B34" s="162" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C34" s="141" t="str">
-        <x:v>sLLM</x:v>
-      </x:c>
-      <x:c r="D34" s="171" t="str">
-        <x:v>AI-004</x:v>
-      </x:c>
-      <x:c r="E34" s="183" t="str">
-        <x:v>팀은 합성 VOC로 자체 sLLM을 파인튜닝하고 API LLM 또는 기본 모델과 비교해야 한다.</x:v>
-      </x:c>
-      <x:c r="F34" s="192" t="str">
-        <x:v>정의·상세: 규칙·template으로 label을 고정한 합성 VOC만 사용해 학습 전/후 성능·지연·비용을 비교한다. 공식 교육 산출물용 독립 실험이며 Baseline 런타임 기본은 API LLM이다.
-대상 사용자: AI 담당
-입력→처리→출력: 라벨 데이터셋 → 파인튜닝·비교 → sLLM·성능표
-업무 규칙·예외: 기본 모델 대비 개선 근거 제시.
-수용 기준: Given 데이터셋 준비 시 / When 파인튜닝하면 / Then 학습 전/후 성능이 비교표로 제시된다.</x:v>
-      </x:c>
-      <x:c r="G34" s="192" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:sLLM 파인튜닝
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-산출물: 자체 sLLM 인공지능
-참고: 선행 AI-001,AI-002 · 비고: 🎓 독립 실험·교육 산출물, Baseline Gate 제외</x:v>
+      <x:c r="B34" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C34" s="207" t="str">
+        <x:v>SQL 수정</x:v>
+      </x:c>
+      <x:c r="D34" s="209" t="str">
+        <x:v>REQ-AI-006</x:v>
+      </x:c>
+      <x:c r="E34" s="208" t="str">
+        <x:v>G2 거절 SQL은 승인 범위 안에서 최대 1회 수정할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F34" s="208" t="str">
+        <x:v>수정 후 G2를 다시 통과하지 못하면 종료하며 자유 반복 self-repair를 금지한다.</x:v>
+      </x:c>
+      <x:c r="G34" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H34" s="2"/>
       <x:c r="I34" s="2"/>
@@ -2731,36 +2507,27 @@
       <x:c r="Y34" s="2"/>
       <x:c r="Z34" s="2"/>
     </x:row>
-    <x:row r="35" ht="125" customHeight="1">
-      <x:c r="A35" s="162" t="str">
+    <x:row r="35" ht="72" customHeight="1">
+      <x:c r="A35" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B35" s="162" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C35" s="101" t="str">
-        <x:v>VOC 통계</x:v>
-      </x:c>
-      <x:c r="D35" s="166" t="str">
-        <x:v>AI-005</x:v>
-      </x:c>
-      <x:c r="E35" s="187" t="str">
-        <x:v>시스템은 주제별 부정 VOC 건수·비율과 전주·최근 4주 대비 증감률을 계산해야 한다.</x:v>
-      </x:c>
-      <x:c r="F35" s="193" t="str">
-        <x:v>정의·상세: SQL/Pandas로 전주 및 최근 4주 동일 요일 기준 집계·증감률을 계산하고 최소 표본 미달 시 제한을 표시한다.
-대상 사용자: 분석 담당, 실무자
-입력→처리→출력: 분석 결과 → 집계·증감률(코드) → 주제별 부정률·증감률
-업무 규칙·예외: 표본 미달 시 제한 표시.
-수용 기준: Given 비교 가능한 전주·최근 4주 동일 요일 표본이 있을 때 / When 증감률을 계산하면 / Then 두 비교값과 표본 수가 산출된다. 표본이 부족하면 비교값 대신 제한 사유가 표시된다.</x:v>
-      </x:c>
-      <x:c r="G35" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(SQL·Pandas)
-담당: D AI·Agent(윤대성) / C 데이터·DB(정승)
-실행·검증: 4주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 DAT-002 · 화면: VOC 이상징후 · 비고: 수치는 코드</x:v>
+      <x:c r="B35" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C35" s="207" t="str">
+        <x:v>G3</x:v>
+      </x:c>
+      <x:c r="D35" s="209" t="str">
+        <x:v>REQ-AI-007</x:v>
+      </x:c>
+      <x:c r="E35" s="208" t="str">
+        <x:v>G3 Result Gate는 결과 shape, 빈 값, 정책, 수치 일관성과 설명 가능 여부를 검증해야 한다.</x:v>
+      </x:c>
+      <x:c r="F35" s="208" t="str">
+        <x:v>실패 결과는 성공 설명·Artifact·보고서 블록으로 승격하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G35" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H35" s="2"/>
       <x:c r="I35" s="2"/>
@@ -2782,36 +2549,27 @@
       <x:c r="Y35" s="2"/>
       <x:c r="Z35" s="2"/>
     </x:row>
-    <x:row r="36" ht="112" customHeight="1">
-      <x:c r="A36" s="163" t="str">
+    <x:row r="36" ht="72" customHeight="1">
+      <x:c r="A36" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B36" s="163" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C36" s="141" t="str">
-        <x:v>이상징후</x:v>
-      </x:c>
-      <x:c r="D36" s="171" t="str">
-        <x:v>AI-006</x:v>
-      </x:c>
-      <x:c r="E36" s="183" t="str">
-        <x:v>Baseline은 versioned rule로 VOC·운영 이상징후를 탐지해야 한다.</x:v>
-      </x:c>
-      <x:c r="F36" s="192" t="str">
-        <x:v>정의·상세: Baseline 판정은 팀이 합의한 프로젝트 가정 임계값과 versioned rule만 사용한다. 합성 정답 manifest와 반례로 임계값의 민감도·오탐·미탐을 검증한다.
-대상 사용자: 분석 담당
-입력→처리→출력: 통계·지표 → 품질 Gate→versioned rule → 이상징후·rule version
-업무 규칙·예외: 최소 표본 미달 제한.
-수용 기준: Given 임계값 초과 시 / When 브리핑을 생성하면 / Then 이상징후 카드가 표시된다.</x:v>
-      </x:c>
-      <x:c r="G36" s="192" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(규칙 판정)
-담당: D AI·Agent(윤대성)
-실행·검증: 4~5주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 AI-005 · 비고: 규칙 관리 UI는 OPS-003 보류·승인 후 후보</x:v>
+      <x:c r="B36" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C36" s="207" t="str">
+        <x:v>설명</x:v>
+      </x:c>
+      <x:c r="D36" s="209" t="str">
+        <x:v>REQ-AI-008</x:v>
+      </x:c>
+      <x:c r="E36" s="208" t="str">
+        <x:v>Node 3는 shaped result와 승인 근거만 사용해 결과를 설명해야 한다.</x:v>
+      </x:c>
+      <x:c r="F36" s="208" t="str">
+        <x:v>관측 사실, 해석, 한계와 후속 질문을 구분하고 원시 대량 행이나 CoT를 반환하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G36" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H36" s="2"/>
       <x:c r="I36" s="2"/>
@@ -2833,36 +2591,27 @@
       <x:c r="Y36" s="2"/>
       <x:c r="Z36" s="2"/>
     </x:row>
-    <x:row r="37" ht="125" customHeight="1">
-      <x:c r="A37" s="165" t="str">
+    <x:row r="37" ht="72" customHeight="1">
+      <x:c r="A37" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B37" s="165" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C37" s="101" t="str">
-        <x:v>운영지표</x:v>
-      </x:c>
-      <x:c r="D37" s="166" t="str">
-        <x:v>AI-007</x:v>
-      </x:c>
-      <x:c r="E37" s="187" t="str">
-        <x:v>시스템은 운영지표의 전주·최근 4주 동일 요일 대비 변화를 계산해야 한다.</x:v>
-      </x:c>
-      <x:c r="F37" s="193" t="str">
-        <x:v>정의·상세: 조식 이용객·근무 인원·평균/상위 대기시간·처리량 등 운영지표의 전주 및 최근 4주 동일 요일 대비 증감률을 코드로 계산한다. 객실 점유율은 데이터 항목과 생성 규칙이 팀 승인된 경우에만 사용한다.
-대상 사용자: 분석 담당, 실무자
-입력→처리→출력: 운영지표 → 기간 비교(코드) → 운영지표 증감률
-업무 규칙·예외: 데이터 없는 기간은 제외하고 행사·날씨·성수기 등 미수집 혼동 요인은 unknown으로 표시한다.
-수용 기준: Given 비교 가능한 동일 요일 운영지표일 때 / When 비교하면 / Then 지표별 증감률·표본·비교 기간이 산출된다. 비교 불가 시 값 대신 사유가 표시된다.</x:v>
-      </x:c>
-      <x:c r="G37" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(SQL·Pandas)
-담당: C 데이터·DB(정승) / D AI·Agent(윤대성)
-실행·검증: 4주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 DAT-003 · 화면: 운영 원인 분석</x:v>
+      <x:c r="B37" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C37" s="207" t="str">
+        <x:v>모델 버전</x:v>
+      </x:c>
+      <x:c r="D37" s="209" t="str">
+        <x:v>REQ-AI-009</x:v>
+      </x:c>
+      <x:c r="E37" s="208" t="str">
+        <x:v>모든 AI 요청은 model, prompt, tokenizer/adapter와 policy version을 추적해야 한다.</x:v>
+      </x:c>
+      <x:c r="F37" s="208" t="str">
+        <x:v>request trace에서 사용 버전과 fallback 여부를 재구성할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="G37" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H37" s="2"/>
       <x:c r="I37" s="2"/>
@@ -2884,36 +2633,27 @@
       <x:c r="Y37" s="2"/>
       <x:c r="Z37" s="2"/>
     </x:row>
-    <x:row r="38" ht="125" customHeight="1">
-      <x:c r="A38" s="162" t="str">
+    <x:row r="38" ht="72" customHeight="1">
+      <x:c r="A38" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B38" s="162" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C38" s="141" t="str">
-        <x:v>교차분석</x:v>
-      </x:c>
-      <x:c r="D38" s="171" t="str">
-        <x:v>AI-008</x:v>
-      </x:c>
-      <x:c r="E38" s="183" t="str">
-        <x:v>시스템은 VOC 주제와 관련 운영지표를 매핑해 동기간 변화를 비교해야 한다.</x:v>
-      </x:c>
-      <x:c r="F38" s="192" t="str">
-        <x:v>정의·상세: 부정 VOC 증가 시 함께 변한 운영지표를 동일 시설·기간 기준 비교, 사용 계산값 표시.
-대상 사용자: 분석 담당
-입력→처리→출력: VOC·운영 증감률 → 주제-지표 매핑·비교 → 교차 결과·계산값
-업무 규칙·예외: 상관≠인과. 공통 키(시설·주제·일시) 존재 확인.
-수용 기준: Given 부정 VOC 증가 기간일 때 / When 교차분석하면 / Then 동기간 관련 운영지표 변화가 함께 조회된다.</x:v>
-      </x:c>
-      <x:c r="G38" s="192" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 가정
-AI 활용: 비AI(SQL·규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-산출물: AI 시스템 아키텍처
-참고: 선행 AI-005,AI-007,DAT-007 · 화면: 운영 원인 분석 · 비고: service_area_id·기간·timezone 공통 키 정합 확인</x:v>
+      <x:c r="B38" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C38" s="207" t="str">
+        <x:v>모델 평가</x:v>
+      </x:c>
+      <x:c r="D38" s="209" t="str">
+        <x:v>REQ-AI-010</x:v>
+      </x:c>
+      <x:c r="E38" s="208" t="str">
+        <x:v>모델 후보는 동일 fixture·질문·Context에서 정확도·실행 성공·지연·자원·비용을 비교해야 한다.</x:v>
+      </x:c>
+      <x:c r="F38" s="208" t="str">
+        <x:v>필수 30건 회귀와 승인된 gold 120건을 분리하고 gold를 학습·prompt 조정에 사용하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G38" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H38" s="2"/>
       <x:c r="I38" s="2"/>
@@ -2935,36 +2675,27 @@
       <x:c r="Y38" s="2"/>
       <x:c r="Z38" s="2"/>
     </x:row>
-    <x:row r="39" ht="112" customHeight="1">
-      <x:c r="A39" s="162" t="str">
+    <x:row r="39" ht="72" customHeight="1">
+      <x:c r="A39" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B39" s="162" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C39" s="101" t="str">
-        <x:v>원인 후보</x:v>
-      </x:c>
-      <x:c r="D39" s="166" t="str">
-        <x:v>AI-009</x:v>
-      </x:c>
-      <x:c r="E39" s="187" t="str">
-        <x:v>시스템은 사전 정의 규칙에 따라 원인 후보를 생성해야 한다.</x:v>
-      </x:c>
-      <x:c r="F39" s="193" t="str">
-        <x:v>정의·상세: 예: 조식 부정 VOC↑20% AND 이용객↑15% AND 인원↑&lt;5% AND 대기↑20% → '혼잡시간 인력 미확대 가능성 우선 점검' 후보. 확정 표현 금지.
-대상 사용자: 분석 담당
-입력→처리→출력: 교차 결과 → 규칙 엔진 평가 → 원인 후보·계산값·rule_id
-업무 규칙·예외: 데이터 없으면 후보 미생성.
-수용 기준: Given 운영 데이터 없는 기간 조회 시 / When 분석하면 / Then 후보 미생성·데이터 부족 메시지가 표시된다.</x:v>
-      </x:c>
-      <x:c r="G39" s="193" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(규칙)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 AI-008,OPS-003 · 화면: 운영 원인 분석 · 비고: 규칙 OPS-003</x:v>
+      <x:c r="B39" s="211" t="str">
+        <x:v>AI 요구사항</x:v>
+      </x:c>
+      <x:c r="C39" s="207" t="str">
+        <x:v>채택 Gate</x:v>
+      </x:c>
+      <x:c r="D39" s="209" t="str">
+        <x:v>REQ-AI-011</x:v>
+      </x:c>
+      <x:c r="E39" s="208" t="str">
+        <x:v>fine-tuned 모델은 baseline 대비 승인된 품질·지연·비용 기준을 충족할 때만 채택해야 한다.</x:v>
+      </x:c>
+      <x:c r="F39" s="208" t="str">
+        <x:v>기준 미충족 또는 비용 승인 부재 시 baseline 경로를 유지한다.</x:v>
+      </x:c>
+      <x:c r="G39" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H39" s="2"/>
       <x:c r="I39" s="2"/>
@@ -2986,36 +2717,27 @@
       <x:c r="Y39" s="2"/>
       <x:c r="Z39" s="2"/>
     </x:row>
-    <x:row r="40" ht="177" customHeight="1">
-      <x:c r="A40" s="163" t="str">
+    <x:row r="40" ht="72" customHeight="1">
+      <x:c r="A40" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B40" s="163" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C40" s="141" t="str">
-        <x:v>text-to-SQL</x:v>
-      </x:c>
-      <x:c r="D40" s="171" t="str">
-        <x:v>AI-010</x:v>
-      </x:c>
-      <x:c r="E40" s="183" t="str">
-        <x:v>시스템은 보장 intent의 semantic plan을 결정론적 read-only SQL로 변환·검증·실행하고 조회 근거를 제공해야 한다.</x:v>
-      </x:c>
-      <x:c r="F40" s="192" t="str">
-        <x:v>정의·상세: 질문을 8개 보장 intent와 그 파라미터에 연결해 semantic plan을 만들고, 결정론적 builder가 허용 query template에 값을 바인딩한다. 실행 전 권한·서비스 범위·read-only·allowlist를 검증하며 수치는 DB가 계산한다. LLM은 임의 SQL을 작성하지 않는다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 질문·스키마·카탈로그·권한 → 조회 계획·SQL 생성·검증·실행 → 결과·적용 지표·기간·필터·실행 SQL
-업무 규칙·예외: 미지원 intent, 권한·scope 위반, UNION, SQL 주석, 다중 statement, 금지 함수·catalog 접근, timeout은 모두 미실행한다.
-수용 기준: Given 보장 intent와 유효 파라미터일 때 / When semantic plan을 변환하면 / Then 권한·카탈로그·SQL Guard를 모두 통과한 read-only template SQL만 실행되고 적용 지표·기간·필터·수치·근거가 표시된다. 공격·미지원 입력은 실행 0건과 차단 사유를 evidence로 남긴다.</x:v>
-      </x:c>
-      <x:c r="G40" s="192" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:plan 해석+비AI SQL builder·Guard
-담당: D AI·Agent(윤대성) / B 백엔드·통합(김재홍) / A 프론트·UX(송민지)
-실행·검증: 5주차
-산출물: LLM 활용 소프트웨어
-참고: 선행 DAT-007,FUN-006 · 화면: 분석 에이전트 · 비고: 정식 온톨로지 불필요</x:v>
+      <x:c r="B40" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C40" s="207" t="str">
+        <x:v>정의</x:v>
+      </x:c>
+      <x:c r="D40" s="209" t="str">
+        <x:v>REQ-RPT-001</x:v>
+      </x:c>
+      <x:c r="E40" s="208" t="str">
+        <x:v>보고서 정의와 실행 결과는 독립된 versioned entity로 관리해야 한다.</x:v>
+      </x:c>
+      <x:c r="F40" s="208" t="str">
+        <x:v>definition version은 불변이며 수정 시 새 초안을 생성하고 기존 승인본을 덮어쓰지 않는다.</x:v>
+      </x:c>
+      <x:c r="G40" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H40" s="2"/>
       <x:c r="I40" s="2"/>
@@ -3037,36 +2759,27 @@
       <x:c r="Y40" s="2"/>
       <x:c r="Z40" s="2"/>
     </x:row>
-    <x:row r="41" ht="177" customHeight="1">
-      <x:c r="A41" s="168" t="str">
+    <x:row r="41" ht="72" customHeight="1">
+      <x:c r="A41" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B41" s="168" t="str">
-        <x:v>AI·분석 요구사항</x:v>
-      </x:c>
-      <x:c r="C41" s="105" t="str">
-        <x:v>군집 실험</x:v>
-      </x:c>
-      <x:c r="D41" s="166" t="str">
-        <x:v>AI-011</x:v>
-      </x:c>
-      <x:c r="E41" s="187" t="str">
-        <x:v>팀은 합성 VOC 리뷰 군집을 독립 실험하고 규칙 주제 정답표와 비교해야 한다.</x:v>
-      </x:c>
-      <x:c r="F41" s="193" t="str">
-        <x:v>정의·상세: 개발에 사용하지 않은 hold-out template family·seed에서 KMeans와 HDBSCAN 후보를 비교하고 생성기의 규칙 주제 label과 대조해 군집이 의미 있는 주제를 재현하는지 확인한다. 단일 호텔 데이터에서 별도 가치가 불명확한 시설·시간대 세그먼트 도출은 요구하지 않는다.
-대상 사용자: AI 담당
-입력→처리→출력: 합성 리뷰 임베딩·규칙 주제 label → 군집·비교 → 군집 품질·해석·한계
-업무 규칙·예외: 입력 embedding/model version, 군집 수·noise 비율·silhouette·ARI/NMI 또는 대응 가능한 지표·seed 안정성·해석 근거를 기록한다. 결과는 Baseline 주제 label을 대체하지 않는다.
-수용 기준: Given 개발에 사용하지 않은 template family·seed 평가셋일 때 / When 두 군집 후보를 수행하면 / Then 비교 지표·주제 label 대응·seed 안정성·오류 사례·채택 또는 미사용 결론이 기록된다.</x:v>
-      </x:c>
-      <x:c r="G41" s="193" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:비지도 군집
-담당: D AI·Agent(윤대성)
-실행·검증: 4주차
-산출물: ML/DL 학습결과서
-참고: 선행 AI-002,DAT-006 · 비고: 오프라인 비교만 수행, Baseline Gate 제외</x:v>
+      <x:c r="B41" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C41" s="207" t="str">
+        <x:v>블록</x:v>
+      </x:c>
+      <x:c r="D41" s="209" t="str">
+        <x:v>REQ-RPT-002</x:v>
+      </x:c>
+      <x:c r="E41" s="208" t="str">
+        <x:v>보고서는 12-column grid의 독립 Block Definition들로 구성되어야 한다.</x:v>
+      </x:c>
+      <x:c r="F41" s="208" t="str">
+        <x:v>각 block은 위치·크기·유형·Artifact/query reference·표시 설정을 직렬화한다.</x:v>
+      </x:c>
+      <x:c r="G41" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H41" s="2"/>
       <x:c r="I41" s="2"/>
@@ -3088,36 +2801,27 @@
       <x:c r="Y41" s="2"/>
       <x:c r="Z41" s="2"/>
     </x:row>
-    <x:row r="42" ht="125" customHeight="1">
-      <x:c r="A42" s="170" t="str">
+    <x:row r="42" ht="72" customHeight="1">
+      <x:c r="A42" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B42" s="170" t="str">
-        <x:v>연동 요구사항</x:v>
-      </x:c>
-      <x:c r="C42" s="116" t="str">
-        <x:v>LLM API</x:v>
-      </x:c>
-      <x:c r="D42" s="169" t="str">
-        <x:v>INT-001</x:v>
-      </x:c>
-      <x:c r="E42" s="182" t="str">
-        <x:v>시스템은 LLM API를 연동하고 장애 시 통계 결과는 유지해야 한다.</x:v>
-      </x:c>
-      <x:c r="F42" s="191" t="str">
-        <x:v>정의·상세: LLM은 질문 해석 또는 evidence 기반 설명·보고 문장에 실행당 최대 1회 사용한다. API 오류 시 결정론적 통계와 template 문장을 유지하고 PARTIAL로 반환한다.
-대상 사용자: 백엔드 담당
-입력→처리→출력: 질문·데이터 → API 호출·오류 처리 → 응답·오류 메시지
-업무 규칙·예외: 키는 환경변수로 관리한다. timeout·retry는 시연 환경 측정 후 구현 설계에서 정하고 비용 상한은 팀이 별도 합의한다.
-수용 기준: Given LLM API 실패 시 / When 분석을 조회하면 / Then 계산된 통계·운영지표는 정상 표시된다.</x:v>
-      </x:c>
-      <x:c r="G42" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:LLM
-담당: B 백엔드·통합(김재홍)
-실행·검증: 5주차
-산출물: LLM 활용 소프트웨어
-참고: 화면: 분석 에이전트 · 비고: 가용성 NFR-002 · 키 환경변수는 SEC-002 점검 연계</x:v>
+      <x:c r="B42" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C42" s="207" t="str">
+        <x:v>편집</x:v>
+      </x:c>
+      <x:c r="D42" s="209" t="str">
+        <x:v>REQ-RPT-003</x:v>
+      </x:c>
+      <x:c r="E42" s="208" t="str">
+        <x:v>권한 사용자는 block을 추가·이동·크기 변경·삭제하고 초안으로 저장할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F42" s="208" t="str">
+        <x:v>키보드 대체 조작과 취소 가능한 변경을 제공하며 서버 검증 전 승인 상태로 전환하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G42" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H42" s="2"/>
       <x:c r="I42" s="2"/>
@@ -3139,36 +2843,27 @@
       <x:c r="Y42" s="2"/>
       <x:c r="Z42" s="2"/>
     </x:row>
-    <x:row r="43" ht="112" customHeight="1">
-      <x:c r="A43" s="169" t="str">
+    <x:row r="43" ht="72" customHeight="1">
+      <x:c r="A43" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B43" s="169" t="str">
-        <x:v>연동 요구사항</x:v>
-      </x:c>
-      <x:c r="C43" s="116" t="str">
-        <x:v>벡터DB</x:v>
-      </x:c>
-      <x:c r="D43" s="169" t="str">
-        <x:v>INT-002</x:v>
-      </x:c>
-      <x:c r="E43" s="182" t="str">
-        <x:v>팀은 벡터DB 근거 검색의 품질과 제한을 독립 실험해야 한다.</x:v>
-      </x:c>
-      <x:c r="F43" s="191" t="str">
-        <x:v>정의·상세: 합성 VOC의 pgvector 임베딩 검색 품질을 오프라인 평가한다. 이슈 브리프의 참고 섹션 노출은 별도 승인 사항이며 Baseline 판정·수치·보고 생성은 VectorDB에 의존하지 않는다. GraphDB 비교 실험은 범위에 추가하지 않는다.
-대상 사용자: 백엔드 담당
-입력→처리→출력: 질의 임베딩 → 벡터 검색 → 근거 리뷰
-업무 규칙·예외: 검색 실패 시 통계 유지.
-수용 기준: Given 고정 평가 질의와 벡터 인덱스가 있을 때 / When 근거 검색을 평가하면 / Then 정답 리뷰 재현율·오탐 사례·한계가 기록된다.</x:v>
-      </x:c>
-      <x:c r="G43" s="191" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:임베딩 검색
-담당: B 백엔드·통합(김재홍)
-실행·검증: 4~5주차
-산출물: 벡터DB/GraphDB 구축 결과서
-참고: 선행 DAT-006 · 화면: 근거 리뷰 · 비고: 🎓 교육 산출물 제약</x:v>
+      <x:c r="B43" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C43" s="207" t="str">
+        <x:v>AI 삽입</x:v>
+      </x:c>
+      <x:c r="D43" s="209" t="str">
+        <x:v>REQ-RPT-004</x:v>
+      </x:c>
+      <x:c r="E43" s="208" t="str">
+        <x:v>AI assistant 결과는 출처 미리보기와 사용자 승인 후 새 block으로 삽입해야 한다.</x:v>
+      </x:c>
+      <x:c r="F43" s="208" t="str">
+        <x:v>기존 block 자동 덮어쓰기를 금지하고 교체 시 변경 전·후 요약과 명시적 승인을 요구한다.</x:v>
+      </x:c>
+      <x:c r="G43" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H43" s="2"/>
       <x:c r="I43" s="2"/>
@@ -3190,36 +2885,27 @@
       <x:c r="Y43" s="2"/>
       <x:c r="Z43" s="2"/>
     </x:row>
-    <x:row r="44" ht="125" customHeight="1">
-      <x:c r="A44" s="171" t="str">
+    <x:row r="44" ht="72" customHeight="1">
+      <x:c r="A44" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B44" s="171" t="str">
-        <x:v>연동 요구사항</x:v>
-      </x:c>
-      <x:c r="C44" s="116" t="str">
-        <x:v>외부 전달</x:v>
-      </x:c>
-      <x:c r="D44" s="169" t="str">
-        <x:v>INT-003</x:v>
-      </x:c>
-      <x:c r="E44" s="182" t="str">
-        <x:v>팀이 대상 채널과 필요성을 승인한 경우에만 분석 결과·주간 리포트의 외부 전달 방식을 검토한다.</x:v>
-      </x:c>
-      <x:c r="F44" s="191" t="str">
-        <x:v>정의·상세: Slack 등 외부 채널 사용 여부와 실제 전달 주체가 정해지지 않았으므로 Baseline에서 외부 전달과 MCP 런타임을 제외한다. 채널·사용 시나리오·보안·승인 흐름이 합의된 뒤 MCP, webhook, API 중 적합한 방식을 비교한다.
-대상 사용자: 관리자, 실무자
-입력→처리→출력: 승인된 리포트·대상 채널·전달 정책 → 선택한 전달 방식과 승인 Gate → 외부 채널 알림
-업무 규칙·예외: 대상 채널 미결정 상태에서는 구현하지 않으며 자동 조치는 금지한다.
-수용 기준: Given 팀이 대상 채널·전달 필요성·승인 흐름을 확정했을 때 / When 방식을 검토하면 / Then MCP를 전제로 하지 않은 대안 비교와 범위 재승인이 기록된다.</x:v>
-      </x:c>
-      <x:c r="G44" s="191" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 확인 필요
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 승인 후
-산출물: 시스템 구성도
-참고: 선행 RPT-001 · 비고: 현재 Baseline 제외</x:v>
+      <x:c r="B44" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C44" s="207" t="str">
+        <x:v>승인</x:v>
+      </x:c>
+      <x:c r="D44" s="209" t="str">
+        <x:v>REQ-RPT-005</x:v>
+      </x:c>
+      <x:c r="E44" s="208" t="str">
+        <x:v>보고서 정의는 권한·계약 검증과 감사 기록 후 DRAFT에서 APPROVED로 전환해야 한다.</x:v>
+      </x:c>
+      <x:c r="F44" s="208" t="str">
+        <x:v>승인 사용자·시각·definition/context/policy version을 저장한다.</x:v>
+      </x:c>
+      <x:c r="G44" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H44" s="2"/>
       <x:c r="I44" s="2"/>
@@ -3241,36 +2927,27 @@
       <x:c r="Y44" s="2"/>
       <x:c r="Z44" s="2"/>
     </x:row>
-    <x:row r="45" ht="112" customHeight="1">
-      <x:c r="A45" s="170" t="str">
+    <x:row r="45" ht="72" customHeight="1">
+      <x:c r="A45" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B45" s="170" t="str">
-        <x:v>화면 요구사항</x:v>
-      </x:c>
-      <x:c r="C45" s="116" t="str">
-        <x:v>운영 홈</x:v>
-      </x:c>
-      <x:c r="D45" s="169" t="str">
-        <x:v>UI-001</x:v>
-      </x:c>
-      <x:c r="E45" s="182" t="str">
-        <x:v>사용자는 권한 범위의 서비스 영역·기간 필터가 있는 운영 홈을 조회할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F45" s="191" t="str">
-        <x:v>정의·상세: 평점 요약과 장소별 매출·운영수익·예약·체크인·체크아웃·운영인력 중 관리자 판단에 필요한 최소 KPI만 권한 범위의 장소·기간 필터와 함께 제공한다. 단일 호텔 전제이므로 호텔 선택 필터를 두지 않는다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 분석 결과 → 필터 조회·시각화(React/Tremor) → 대시보드
-업무 규칙·예외: 기간·단위 표시.
-수용 기준: Given 권한 있는 사용자가 로그인했을 때 / When 서비스 영역·기간 필터를 적용하면 / Then 허용 범위의 KPI·추세·이슈만 표시된다.</x:v>
-      </x:c>
-      <x:c r="G45" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: A 프론트·UX(송민지)
-실행·검증: 5주차
-산출물: 웹 애플리케이션
-참고: 선행 AI-005,AI-006 · 화면: 운영 홈</x:v>
+      <x:c r="B45" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C45" s="207" t="str">
+        <x:v>수동 실행</x:v>
+      </x:c>
+      <x:c r="D45" s="209" t="str">
+        <x:v>REQ-RPT-006</x:v>
+      </x:c>
+      <x:c r="E45" s="208" t="str">
+        <x:v>승인된 정의는 하나의 as_of 기준으로 수동 실행할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F45" s="208" t="str">
+        <x:v>run과 block run 상태, 시작·종료 시각, snapshot, checksum, source를 저장한다.</x:v>
+      </x:c>
+      <x:c r="G45" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H45" s="2"/>
       <x:c r="I45" s="2"/>
@@ -3292,36 +2969,27 @@
       <x:c r="Y45" s="2"/>
       <x:c r="Z45" s="2"/>
     </x:row>
-    <x:row r="46" ht="112" customHeight="1">
-      <x:c r="A46" s="169" t="str">
+    <x:row r="46" ht="72" customHeight="1">
+      <x:c r="A46" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B46" s="169" t="str">
-        <x:v>화면 요구사항</x:v>
-      </x:c>
-      <x:c r="C46" s="116" t="str">
-        <x:v>운영 요약</x:v>
-      </x:c>
-      <x:c r="D46" s="169" t="str">
-        <x:v>UI-002</x:v>
-      </x:c>
-      <x:c r="E46" s="182" t="str">
-        <x:v>관리자·실무자는 주간 요약·위험 이슈·우선 점검 항목을 조회할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F46" s="191" t="str">
-        <x:v>정의·상세: 서비스 영역별 주요 이슈·우선 점검 항목·전주 비교를 운영 홈과 이슈 상세에 표시한다. 데이터만으로 개선 우선순위를 확정하지 않는다.
-대상 사용자: 관리자, 실무자
-입력→처리→출력: 분석 요약 → 중요도·증감 요약 → 요약 화면
-업무 규칙·예외: 실무 상세는 별도 화면.
-수용 기준: Given 관리자 또는 실무자가 로그인했을 때 / When 요약을 열면 / Then 주요 이슈·위험·우선 점검 항목·전주 비교가 표시된다.</x:v>
-      </x:c>
-      <x:c r="G46" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: A 프론트·UX(송민지)
-실행·검증: 5주차 Gate
-산출물: 웹 애플리케이션
-참고: 선행 RPT-001 · 화면: 운영 홈·이슈 상세</x:v>
+      <x:c r="B46" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C46" s="207" t="str">
+        <x:v>부분 실패</x:v>
+      </x:c>
+      <x:c r="D46" s="209" t="str">
+        <x:v>REQ-RPT-007</x:v>
+      </x:c>
+      <x:c r="E46" s="208" t="str">
+        <x:v>보고서 실행은 성공·부분 성공·실패를 구분하고 block별 상태를 제공해야 한다.</x:v>
+      </x:c>
+      <x:c r="F46" s="208" t="str">
+        <x:v>부분 성공 시 실패 block과 마지막 성공 snapshot 사용 여부를 명시한다.</x:v>
+      </x:c>
+      <x:c r="G46" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H46" s="2"/>
       <x:c r="I46" s="2"/>
@@ -3343,36 +3011,27 @@
       <x:c r="Y46" s="2"/>
       <x:c r="Z46" s="2"/>
     </x:row>
-    <x:row r="47" ht="138" customHeight="1">
-      <x:c r="A47" s="169" t="str">
+    <x:row r="47" ht="72" customHeight="1">
+      <x:c r="A47" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B47" s="169" t="str">
-        <x:v>화면 요구사항</x:v>
-      </x:c>
-      <x:c r="C47" s="116" t="str">
-        <x:v>조건부 근거</x:v>
-      </x:c>
-      <x:c r="D47" s="169" t="str">
-        <x:v>UI-003</x:v>
-      </x:c>
-      <x:c r="E47" s="182" t="str">
-        <x:v>사용자는 추가 질의 시 허용된 저점 리뷰와 최소 운영 근거를 확인할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F47" s="191" t="str">
-        <x:v>정의·상세: VOC 최초 질문에는 평점·기간·표본만 표시한다. 사용자가 저점 리뷰를 추가 질의한 경우에만 최근 분기, 확대 시 최대 최근 반기 내 3점 이하 합성 리뷰의 원문·한국어 번역·일자·장소와 최소 운영지표를 표시한다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 분석·근거 → 목록·차트 렌더링 → 근거 목록·차트
-업무 규칙·예외: 실제 개인정보는 생성·수집하지 않으며 적재 전 개인정보성 값 validation을 통과한 합성 원문만 표시한다.
-수용 기준: Given VOC 최초 결과일 때 / When 화면을 열면 / Then 리뷰 원문 없이 평점 요약만 표시된다. Given 저점 근거 추가 질의일 때 / Then 허용 기간·평점 조건을 충족한 리뷰만 표시된다.</x:v>
-      </x:c>
-      <x:c r="G47" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: A 프론트·UX(송민지)
-실행·검증: 5주차 Gate
-산출물: 웹 애플리케이션
-참고: 선행 BIZ-003,AI-008 · 화면: 근거 리뷰</x:v>
+      <x:c r="B47" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C47" s="207" t="str">
+        <x:v>재실행</x:v>
+      </x:c>
+      <x:c r="D47" s="209" t="str">
+        <x:v>REQ-RPT-008</x:v>
+      </x:c>
+      <x:c r="E47" s="208" t="str">
+        <x:v>권한 사용자는 동일 정의와 기준 조건으로 실패 run 또는 block을 재실행할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F47" s="208" t="str">
+        <x:v>idempotency key와 재시도 상한을 적용하고 이전 run 증거를 보존한다.</x:v>
+      </x:c>
+      <x:c r="G47" s="208" t="str">
+        <x:v>P0</x:v>
       </x:c>
       <x:c r="H47" s="2"/>
       <x:c r="I47" s="2"/>
@@ -3394,36 +3053,27 @@
       <x:c r="Y47" s="2"/>
       <x:c r="Z47" s="2"/>
     </x:row>
-    <x:row r="48" ht="125" customHeight="1">
-      <x:c r="A48" s="169" t="str">
+    <x:row r="48" ht="72" customHeight="1">
+      <x:c r="A48" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B48" s="169" t="str">
-        <x:v>화면 요구사항</x:v>
-      </x:c>
-      <x:c r="C48" s="116" t="str">
-        <x:v>접근성</x:v>
-      </x:c>
-      <x:c r="D48" s="169" t="str">
-        <x:v>UI-004</x:v>
-      </x:c>
-      <x:c r="E48" s="182" t="str">
-        <x:v>시스템은 증감·경고 상태를 색상만으로 구분하지 않고 단위·기간을 표시해야 한다.</x:v>
-      </x:c>
-      <x:c r="F48" s="191" t="str">
-        <x:v>정의·상세: 운영 용어 우선, 단위·기간 표기, 색상 외 라벨/아이콘 병행.
-대상 사용자: 전 사용자
-입력→처리→출력: 화면 요소 → 라벨·단위·색상 병행 → 접근성 화면
-업무 규칙·예외: 전문 통계 용어 최소화.
-수용 기준: Given 차트 표시 시 / When 증감·경고 상태를 구분하면 / Then 색상 외 라벨·단위·기간이 함께 표시된다.</x:v>
-      </x:c>
-      <x:c r="G48" s="191" t="str">
-        <x:v>우선순위: 🟡Should | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: A 프론트·UX(송민지)
-실행·검증: 5주차 단위·기간 Gate·7주차 색상 외 구분(비차단)
-산출물: 웹 애플리케이션·서비스 테스트 결과서
-참고: 선행 UI-001 · 화면: 전 화면 · 비고: 사용성</x:v>
+      <x:c r="B48" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C48" s="207" t="str">
+        <x:v>스케줄</x:v>
+      </x:c>
+      <x:c r="D48" s="209" t="str">
+        <x:v>REQ-RPT-009</x:v>
+      </x:c>
+      <x:c r="E48" s="208" t="str">
+        <x:v>일·주·월 스케줄은 수동 실행과 부분 실패 처리가 안정된 승인 정의에만 활성화해야 한다.</x:v>
+      </x:c>
+      <x:c r="F48" s="208" t="str">
+        <x:v>definition·context·policy version 고정, owner, timezone, 중복 방지와 비활성화 절차를 검증한다.</x:v>
+      </x:c>
+      <x:c r="G48" s="208" t="str">
+        <x:v>P1·필수</x:v>
       </x:c>
       <x:c r="H48" s="2"/>
       <x:c r="I48" s="2"/>
@@ -3445,36 +3095,27 @@
       <x:c r="Y48" s="2"/>
       <x:c r="Z48" s="2"/>
     </x:row>
-    <x:row r="49" ht="112" customHeight="1">
-      <x:c r="A49" s="171" t="str">
+    <x:row r="49" ht="72" customHeight="1">
+      <x:c r="A49" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B49" s="171" t="str">
-        <x:v>화면 요구사항</x:v>
-      </x:c>
-      <x:c r="C49" s="116" t="str">
-        <x:v>시각화 연결</x:v>
-      </x:c>
-      <x:c r="D49" s="169" t="str">
-        <x:v>UI-005</x:v>
-      </x:c>
-      <x:c r="E49" s="182" t="str">
-        <x:v>시스템은 text-to-SQL 조회 결과를 자동으로 차트와 표로 시각화해야 한다.</x:v>
-      </x:c>
-      <x:c r="F49" s="191" t="str">
-        <x:v>정의·상세: 결과 유형(시계열·비교·비율)에 따라 관리자 판단에 필요한 차트 1개와 최소 컬럼 표를 병행하고, 불필요한 장소·매출·운영 지표는 숨긴다.
-대상 사용자: 실무자, 관리자
-입력→처리→출력: 쿼리 결과 → 유형 판별·차트 생성 → 차트·표
-업무 규칙·예외: 단위·기간 표기.
-수용 기준: Given 쿼리 결과일 때 / When 표시하면 / Then 결과 유형에 맞는 차트와 표가 함께 표시된다.</x:v>
-      </x:c>
-      <x:c r="G49" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(결과 유형 규칙)
-담당: A 프론트·UX(송민지)
-실행·검증: 5주차 Gate
-산출물: 웹 애플리케이션
-참고: 선행 AI-010 · 화면: 분석 에이전트 · 비고: text-to-SQL→시각화</x:v>
+      <x:c r="B49" s="211" t="str">
+        <x:v>보고서 요구사항</x:v>
+      </x:c>
+      <x:c r="C49" s="207" t="str">
+        <x:v>이력</x:v>
+      </x:c>
+      <x:c r="D49" s="209" t="str">
+        <x:v>REQ-RPT-010</x:v>
+      </x:c>
+      <x:c r="E49" s="208" t="str">
+        <x:v>사용자는 보고서별 definition 이력과 run 이력을 독립적으로 조회해야 한다.</x:v>
+      </x:c>
+      <x:c r="F49" s="208" t="str">
+        <x:v>목록·상세에서 상태, as_of, version, block 결과와 trace link를 제공한다.</x:v>
+      </x:c>
+      <x:c r="G49" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H49" s="2"/>
       <x:c r="I49" s="2"/>
@@ -3496,36 +3137,27 @@
       <x:c r="Y49" s="2"/>
       <x:c r="Z49" s="2"/>
     </x:row>
-    <x:row r="50" ht="177" customHeight="1">
-      <x:c r="A50" s="170" t="str">
+    <x:row r="50" ht="72" customHeight="1">
+      <x:c r="A50" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B50" s="170" t="str">
-        <x:v>리포트 요구사항</x:v>
-      </x:c>
-      <x:c r="C50" s="116" t="str">
-        <x:v>주간 리포트</x:v>
-      </x:c>
-      <x:c r="D50" s="169" t="str">
-        <x:v>RPT-001</x:v>
-      </x:c>
-      <x:c r="E50" s="182" t="str">
-        <x:v>시스템은 근거 기반 주간 HTML DRAFT를 생성·저장·표시하고 생성 시점·생성자를 기록해야 한다.</x:v>
-      </x:c>
-      <x:c r="F50" s="191" t="str">
-        <x:v>정의·상세: 리포트 수치는 voc_review_raw에서 산출하고 감성·모델 평가는 별도 voc_training_dataset을 사용한다. 원본을 학습용 label로 오염시키지 않으며 보고서에는 기간·평점 변화·함께 변한 최소 운영지표·원인 후보·반대 근거·현장 점검 항목·대응 옵션·분석 한계를 포함한다. PDF는 Could이다.
-대상 사용자: 관리자, 실무자
-입력→처리→출력: 분석 결과·evidence → 근거 기반 DRAFT 조립 → 저장·decision 이력 → HTML 표시
-업무 규칙·예외: 생성 시점·생성자·상태를 기록하고 자동 승인·자동 조치를 금지한다. LLM 실패 시 결정론적 수치와 template DRAFT를 유지하고 PARTIAL을 표시한다.
-수용 기준: Given 1주 이상 데이터와 유효 evidence가 있을 때 / When 생성하면 / Then 이슈·변화·후보·반대 근거·점검 항목·옵션·한계를 포함한 DRAFT가 저장·표시되고 생성자/시점/상태가 기록된다. LLM timeout 시에도 수치와 template 본문이 유지된다.</x:v>
-      </x:c>
-      <x:c r="G50" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:초안 서술+비AI 저장·표시
-담당: D AI·Agent(윤대성) / B 백엔드·통합(김재홍) / A 프론트·UX(송민지)
-실행·검증: 5주차 Gate
-산출물: LLM 활용 소프트웨어·웹 애플리케이션
-참고: 선행 AI-008,AI-009 · 화면: 주간 리포트 · 비고: PDF는 Could</x:v>
+      <x:c r="B50" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C50" s="207" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="D50" s="209" t="str">
+        <x:v>REQ-UI-001</x:v>
+      </x:c>
+      <x:c r="E50" s="208" t="str">
+        <x:v>활성 frontend는 React·TypeScript·Vite 기반 단일 애플리케이션이어야 한다.</x:v>
+      </x:c>
+      <x:c r="F50" s="208" t="str">
+        <x:v>I0에서 확정한 frontend만 구현하고 다른 후보를 동시에 개발하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G50" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H50" s="2"/>
       <x:c r="I50" s="2"/>
@@ -3547,36 +3179,27 @@
       <x:c r="Y50" s="2"/>
       <x:c r="Z50" s="2"/>
     </x:row>
-    <x:row r="51" ht="112" customHeight="1">
-      <x:c r="A51" s="171" t="str">
+    <x:row r="51" ht="72" customHeight="1">
+      <x:c r="A51" s="210" t="str">
         <x:v>기능</x:v>
       </x:c>
-      <x:c r="B51" s="171" t="str">
-        <x:v>리포트 요구사항</x:v>
-      </x:c>
-      <x:c r="C51" s="116" t="str">
-        <x:v>분석 한계</x:v>
-      </x:c>
-      <x:c r="D51" s="169" t="str">
-        <x:v>RPT-002</x:v>
-      </x:c>
-      <x:c r="E51" s="182" t="str">
-        <x:v>리포트는 분석 한계와 주의사항을 포함해야 한다.</x:v>
-      </x:c>
-      <x:c r="F51" s="191" t="str">
-        <x:v>정의·상세: 합성 데이터 한계·상관≠인과·표본 제한 명시.
-대상 사용자: 관리자, 실무자
-입력→처리→출력: 분석 메타 → 한계 문구 삽입 → 한계 포함 리포트
-업무 규칙·예외: 확정 원인 표현 금지.
-수용 기준: Given 리포트 생성 시 / When 출력하면 / Then 데이터 한계·인과 아님 안내가 포함된다.</x:v>
-      </x:c>
-      <x:c r="G51" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차 Gate
-산출물: 웹 애플리케이션
-참고: 선행 BIZ-002,BIZ-005 · 화면: 주간 리포트</x:v>
+      <x:c r="B51" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C51" s="207" t="str">
+        <x:v>공통</x:v>
+      </x:c>
+      <x:c r="D51" s="209" t="str">
+        <x:v>REQ-UI-002</x:v>
+      </x:c>
+      <x:c r="E51" s="208" t="str">
+        <x:v>모든 업무 결과 화면은 합성 환경과 데이터 기준 정보를 표시해야 한다.</x:v>
+      </x:c>
+      <x:c r="F51" s="208" t="str">
+        <x:v>SYNTHETIC, seed, schema version, as_of, timezone을 확인할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="G51" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H51" s="2"/>
       <x:c r="I51" s="2"/>
@@ -3598,36 +3221,27 @@
       <x:c r="Y51" s="2"/>
       <x:c r="Z51" s="2"/>
     </x:row>
-    <x:row r="52" ht="164" customHeight="1">
-      <x:c r="A52" s="170" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B52" s="170" t="str">
-        <x:v>보안 요구사항</x:v>
-      </x:c>
-      <x:c r="C52" s="116" t="str">
-        <x:v>개인정보</x:v>
-      </x:c>
-      <x:c r="D52" s="169" t="str">
-        <x:v>SEC-001</x:v>
-      </x:c>
-      <x:c r="E52" s="182" t="str">
-        <x:v>시스템은 실제 개인정보를 생성·수집·저장하지 않고 합성 데이터의 개인정보성 값 포함 여부를 검증해야 한다.</x:v>
-      </x:c>
-      <x:c r="F52" s="191" t="str">
-        <x:v>정의·상세: 고객 이름·전화·이메일·예약번호와 실제 직원 이름·사번·개인 사유를 생성하지 않는다. internal_staff에는 합성 staff_id, 합성 표시명, manager_id, 관리자 구분, 담당 파트·부서 영역·장소, 권한, 알림 여부만 두며 알림 시각·조치 여부·메모는 alert_action에 분리한다.
-대상 사용자: 데이터 담당
-입력→처리→출력: 합성 리뷰·운영 데이터 → 생성 금지 규칙·패턴 검사 → 검증 통과 데이터 또는 적재 거부
-업무 규칙·예외: Baseline은 실제 개인정보 입력을 받지 않으며 개인정보 마스킹 기능 구현을 전제로 하지 않는다.
-수용 기준: Given 개인정보성 패턴을 의도적으로 넣은 합성 테스트 데이터일 때 / When 적재 전 validation을 실행하면 / Then 저장·모델 입력·임베딩 전에 batch가 차단되고 사유가 기록된다.</x:v>
-      </x:c>
-      <x:c r="G52" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 3주차
-산출물: 데이터 전처리 결과서
-참고: 선행 FUN-005,DAT-008 · 비고: 실제 데이터 사용 승인 시 별도 개인정보 처리 기준 필요</x:v>
+    <x:row r="52" ht="72" customHeight="1">
+      <x:c r="A52" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B52" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C52" s="207" t="str">
+        <x:v>분석 챗</x:v>
+      </x:c>
+      <x:c r="D52" s="209" t="str">
+        <x:v>REQ-UI-003</x:v>
+      </x:c>
+      <x:c r="E52" s="208" t="str">
+        <x:v>분석 챗은 질문, 처리 상태, 결과, 근거, 후속 질문과 보고서 전달 동작을 제공해야 한다.</x:v>
+      </x:c>
+      <x:c r="F52" s="208" t="str">
+        <x:v>SCR-CHAT-001 수용 기준과 typed API 상태를 따른다.</x:v>
+      </x:c>
+      <x:c r="G52" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H52" s="2"/>
       <x:c r="I52" s="2"/>
@@ -3649,36 +3263,27 @@
       <x:c r="Y52" s="2"/>
       <x:c r="Z52" s="2"/>
     </x:row>
-    <x:row r="53" ht="112" customHeight="1">
-      <x:c r="A53" s="169" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B53" s="169" t="str">
-        <x:v>보안 요구사항</x:v>
-      </x:c>
-      <x:c r="C53" s="116" t="str">
-        <x:v>접근·비밀</x:v>
-      </x:c>
-      <x:c r="D53" s="169" t="str">
-        <x:v>SEC-002</x:v>
-      </x:c>
-      <x:c r="E53" s="182" t="str">
-        <x:v>시스템은 역할 기반 접근통제와 비밀정보 환경변수 관리를 적용해야 한다.</x:v>
-      </x:c>
-      <x:c r="F53" s="191" t="str">
-        <x:v>정의·상세: Gate 전에는 RBAC 서버 강제, API 키·비밀번호 환경변수 관리와 secret scan을 완료한다. HTTPS·비밀번호 저장 수준 등 시연·배포 환경의 운영 보안 점검은 6~7주차에 보완한다.
-대상 사용자: 백엔드 담당
-입력→처리→출력: 계정·키 → 암호화·환경변수·RBAC → 보안 접근
-업무 규칙·예외: 키의 소스코드 노출 금지.
-수용 기준: Given 커밋 시 / When 점검하면 / Then API 키·비밀번호가 코드에 노출되지 않는다.</x:v>
-      </x:c>
-      <x:c r="G53" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 가정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 3주차 골격·5주차 Gate·6~7주차 운영 점검
-산출물: 시스템 구성도
-참고: 선행 FUN-002 · 비고: 제출 전 점검</x:v>
+    <x:row r="53" ht="72" customHeight="1">
+      <x:c r="A53" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B53" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C53" s="207" t="str">
+        <x:v>보고서</x:v>
+      </x:c>
+      <x:c r="D53" s="209" t="str">
+        <x:v>REQ-UI-004</x:v>
+      </x:c>
+      <x:c r="E53" s="208" t="str">
+        <x:v>보고서 UI는 목록·상세·편집·실행 이력·실행 상세를 구분해야 한다.</x:v>
+      </x:c>
+      <x:c r="F53" s="208" t="str">
+        <x:v>각 상태는 독립 URL로 복원 가능하고 definition/run을 local state 하나로 혼합하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G53" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H53" s="2"/>
       <x:c r="I53" s="2"/>
@@ -3700,36 +3305,27 @@
       <x:c r="Y53" s="2"/>
       <x:c r="Z53" s="2"/>
     </x:row>
-    <x:row r="54" ht="125" customHeight="1">
-      <x:c r="A54" s="171" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B54" s="171" t="str">
-        <x:v>보안 요구사항</x:v>
-      </x:c>
-      <x:c r="C54" s="116" t="str">
-        <x:v>감사 로그</x:v>
-      </x:c>
-      <x:c r="D54" s="169" t="str">
-        <x:v>SEC-003</x:v>
-      </x:c>
-      <x:c r="E54" s="182" t="str">
-        <x:v>시스템은 로그인·분석 조회·리포트 결정 이력을 저장해야 한다.</x:v>
-      </x:c>
-      <x:c r="F54" s="191" t="str">
-        <x:v>정의·상세: Baseline의 로그인·권한 거부·분석 조회·리포트 승인/보류/반려 이력을 논리 entity audit_event에 로깅한다. 비동기 실행 상태는 별도 논리 entity job에서 관리하고 query_run,analysis_run,report_decision과 추적 ID로 연결한다. 다운로드·설정 변경은 해당 확장 기능이 승인될 때 추가한다.
-대상 사용자: 시스템 관리자
-입력→처리→출력: 사용자 행위 → 이벤트 로깅 → 감사 로그
-업무 규칙·예외: 리포트 결정 이력은 덮어쓰지 않는다.
-수용 기준: Given 사용자가 로그인·분석 조회·리포트 결정을 수행할 때 / When 이력을 확인하면 / Then 행위자·시점·대상·결과가 저장되어 있다.</x:v>
-      </x:c>
-      <x:c r="G54" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 3~4주차 저장 골격·5주차 Gate
-산출물: 서비스 테스트 결과서
-참고: 선행 FUN-001,FUN-002,RPT-001</x:v>
+    <x:row r="54" ht="72" customHeight="1">
+      <x:c r="A54" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B54" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C54" s="207" t="str">
+        <x:v>카탈로그</x:v>
+      </x:c>
+      <x:c r="D54" s="209" t="str">
+        <x:v>REQ-UI-005</x:v>
+      </x:c>
+      <x:c r="E54" s="208" t="str">
+        <x:v>카탈로그는 소스 요약, 자산 검색·상세, 연결 상태와 Context 정보를 제공해야 한다.</x:v>
+      </x:c>
+      <x:c r="F54" s="208" t="str">
+        <x:v>DataHub URN·Trino FQN·owner·tag·lineage·ingestion·active release를 표시한다.</x:v>
+      </x:c>
+      <x:c r="G54" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H54" s="2"/>
       <x:c r="I54" s="2"/>
@@ -3751,36 +3347,27 @@
       <x:c r="Y54" s="2"/>
       <x:c r="Z54" s="2"/>
     </x:row>
-    <x:row r="55" ht="99" customHeight="1">
-      <x:c r="A55" s="170" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B55" s="170" t="str">
-        <x:v>비기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C55" s="116" t="str">
-        <x:v>성능</x:v>
-      </x:c>
-      <x:c r="D55" s="169" t="str">
-        <x:v>NFR-001</x:v>
-      </x:c>
-      <x:c r="E55" s="182" t="str">
-        <x:v>주요 대시보드는 5초 이내, 단일 자연어 분석은 30초 이내를 목표로 한다.</x:v>
-      </x:c>
-      <x:c r="F55" s="191" t="str">
-        <x:v>정의·상세: 내부 생성 합성 데이터의 팀 합의 기준량에서 측정하는 성능 목표다. 대용량 사용자 업로드 성능은 포함하지 않는다.
-대상 사용자: 전 사용자
-입력→처리→출력: 조회 요청 → 측정·최적화 → 성능 결과
-업무 규칙·예외: 목표 초과 시 개선 기록.
-수용 기준: Given 일반 범위일 때 / When 대시보드를 조회하면 / Then 5초 이내 렌더링된다(목표, 측정 후 확정).</x:v>
-      </x:c>
-      <x:c r="G55" s="191" t="str">
-        <x:v>우선순위: 🟡Should | 범위: Baseline 필수 | 성격: 가정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 5~7주차 측정(비차단)
-산출물: 서비스 테스트 결과서
-참고: 선행 UI-001 · 비고: 목표값 가정</x:v>
+    <x:row r="55" ht="72" customHeight="1">
+      <x:c r="A55" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B55" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C55" s="207" t="str">
+        <x:v>감사</x:v>
+      </x:c>
+      <x:c r="D55" s="209" t="str">
+        <x:v>REQ-UI-006</x:v>
+      </x:c>
+      <x:c r="E55" s="208" t="str">
+        <x:v>감사 UI는 request→context→SQL/query→artifact/report trace를 검색·조회해야 한다.</x:v>
+      </x:c>
+      <x:c r="F55" s="208" t="str">
+        <x:v>역할에 따라 민감 필드를 redaction하고 읽기 전용으로 제공한다.</x:v>
+      </x:c>
+      <x:c r="G55" s="208" t="str">
+        <x:v>P0 운영·필수</x:v>
       </x:c>
       <x:c r="H55" s="2"/>
       <x:c r="I55" s="2"/>
@@ -3802,36 +3389,27 @@
       <x:c r="Y55" s="2"/>
       <x:c r="Z55" s="2"/>
     </x:row>
-    <x:row r="56" ht="99" customHeight="1">
-      <x:c r="A56" s="169" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B56" s="169" t="str">
-        <x:v>비기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C56" s="116" t="str">
-        <x:v>가용성</x:v>
-      </x:c>
-      <x:c r="D56" s="169" t="str">
-        <x:v>NFR-002</x:v>
-      </x:c>
-      <x:c r="E56" s="182" t="str">
-        <x:v>분석 실패 시 전체 서비스가 중단되지 않아야 한다.</x:v>
-      </x:c>
-      <x:c r="F56" s="191" t="str">
-        <x:v>정의·상세: LLM/외부 API 오류 시 통계 결과 유지·명확한 오류 메시지.
-대상 사용자: 전 사용자
-입력→처리→출력: 분석 요청 → 예외 격리·Fallback → 부분 결과·오류
-업무 규칙·예외: 서비스 전체 중단 금지.
-수용 기준: Given 외부 API 장애 시 / When 분석을 요청하면 / Then 통계는 표시되고 오류가 안내된다.</x:v>
-      </x:c>
-      <x:c r="G56" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 5주차
-산출물: 서비스 테스트 결과서
-참고: 선행 INT-001 · 화면: 전 화면</x:v>
+    <x:row r="56" ht="72" customHeight="1">
+      <x:c r="A56" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B56" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C56" s="207" t="str">
+        <x:v>상태</x:v>
+      </x:c>
+      <x:c r="D56" s="209" t="str">
+        <x:v>REQ-UI-007</x:v>
+      </x:c>
+      <x:c r="E56" s="208" t="str">
+        <x:v>loading·empty·success·partial·failure·forbidden·expired 상태를 구분해 표시해야 한다.</x:v>
+      </x:c>
+      <x:c r="F56" s="208" t="str">
+        <x:v>색상만 사용하지 않고 아이콘·문구·사용자 다음 동작을 함께 제공한다.</x:v>
+      </x:c>
+      <x:c r="G56" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H56" s="2"/>
       <x:c r="I56" s="2"/>
@@ -3853,36 +3431,27 @@
       <x:c r="Y56" s="2"/>
       <x:c r="Z56" s="2"/>
     </x:row>
-    <x:row r="57" ht="99" customHeight="1">
-      <x:c r="A57" s="169" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B57" s="169" t="str">
-        <x:v>비기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C57" s="116" t="str">
-        <x:v>신뢰성</x:v>
-      </x:c>
-      <x:c r="D57" s="169" t="str">
-        <x:v>NFR-003</x:v>
-      </x:c>
-      <x:c r="E57" s="182" t="str">
-        <x:v>시스템은 동일 조건에서 수치 계산을 재현하고 규칙·모델 버전을 기록해야 한다.</x:v>
-      </x:c>
-      <x:c r="F57" s="191" t="str">
-        <x:v>정의·상세: 결정적 계산, 원본 보존, 규칙/모델 버전 기록, 데이터 누락 시 경고.
-대상 사용자: 분석 담당
-입력→처리→출력: 규칙·데이터 → 버전 관리·결정적 계산 → 재현 결과·버전
-업무 규칙·예외: LLM 문장과 계산 결과 구분.
-수용 기준: Given 동일 데이터·규칙일 때 / When 재계산하면 / Then 동일 수치·규칙 버전이 기록된다.</x:v>
-      </x:c>
-      <x:c r="G57" s="191" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 비AI(계산)
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-산출물: 서비스 테스트 결과서
-참고: 선행 AI-009 · 비고: 설명 가능성</x:v>
+    <x:row r="57" ht="72" customHeight="1">
+      <x:c r="A57" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B57" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C57" s="207" t="str">
+        <x:v>접근성</x:v>
+      </x:c>
+      <x:c r="D57" s="209" t="str">
+        <x:v>REQ-UI-008</x:v>
+      </x:c>
+      <x:c r="E57" s="208" t="str">
+        <x:v>핵심 흐름은 키보드, focus, screen reader와 200% 확대에서 사용할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="F57" s="208" t="str">
+        <x:v>status는 적절한 aria-live, chart는 표 또는 텍스트 대안, dialog는 focus 복귀를 제공한다.</x:v>
+      </x:c>
+      <x:c r="G57" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H57" s="2"/>
       <x:c r="I57" s="2"/>
@@ -3904,35 +3473,27 @@
       <x:c r="Y57" s="2"/>
       <x:c r="Z57" s="2"/>
     </x:row>
-    <x:row r="58" ht="138" customHeight="1">
-      <x:c r="A58" s="169" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B58" s="169" t="str">
-        <x:v>비기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C58" s="116" t="str">
-        <x:v>대용량 입력</x:v>
-      </x:c>
-      <x:c r="D58" s="169" t="str">
-        <x:v>NFR-004</x:v>
-      </x:c>
-      <x:c r="E58" s="182" t="str">
-        <x:v>Baseline은 대용량 사용자 업로드를 지원 범위에서 제외하며 실데이터 연동 결정 시에만 재검토한다.</x:v>
-      </x:c>
-      <x:c r="F58" s="191" t="str">
-        <x:v>정의·상세: 데이터는 고정 seed 생성기가 내부 생성·적재하며 사용자가 대용량 파일을 올리는 시나리오가 없다. 실데이터 연동이나 사용자 파일 입력이 승인될 때 예상 용량·빈도·응답 목표를 먼저 정한 뒤 비동기 처리와 페이지네이션 필요성을 판단한다.
-대상 사용자: 데이터·백엔드 담당
-입력→처리→출력: 승인된 실데이터 시나리오·예상 용량 → 용량·빈도·성능 기준 검토 → 처리 방식 결정
-업무 규칙·예외: 현재 Baseline에는 대용량 업로드 UI·비동기 업로드를 구현하지 않는다.
-수용 기준: Given 실데이터 연동 또는 외부 파일 입력이 승인될 때 / When 용량 요구를 정의하면 / Then 측정값에 근거해 동기·비동기·페이지네이션 정책을 다시 승인한다.</x:v>
-      </x:c>
-      <x:c r="G58" s="191" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: C 데이터·DB(정승)
-실행·검증: 승인 후
-참고: 선행 FUN-003 · 비고: 현재 Baseline 제외</x:v>
+    <x:row r="58" ht="72" customHeight="1">
+      <x:c r="A58" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B58" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C58" s="207" t="str">
+        <x:v>반응형</x:v>
+      </x:c>
+      <x:c r="D58" s="209" t="str">
+        <x:v>REQ-UI-009</x:v>
+      </x:c>
+      <x:c r="E58" s="208" t="str">
+        <x:v>화면은 1440·1024·768·360px 기준에서 핵심 정보와 동작을 유지해야 한다.</x:v>
+      </x:c>
+      <x:c r="F58" s="208" t="str">
+        <x:v>작은 화면에서 report block은 y, x 순으로 단일 열 재배치하고 근거·실패 상태를 숨기지 않는다.</x:v>
+      </x:c>
+      <x:c r="G58" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H58" s="2"/>
       <x:c r="I58" s="2"/>
@@ -3954,36 +3515,27 @@
       <x:c r="Y58" s="2"/>
       <x:c r="Z58" s="2"/>
     </x:row>
-    <x:row r="59" ht="125" customHeight="1">
-      <x:c r="A59" s="169" t="str">
-        <x:v>비기능</x:v>
-      </x:c>
-      <x:c r="B59" s="169" t="str">
-        <x:v>비기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C59" s="116" t="str">
-        <x:v>설명·검토</x:v>
-      </x:c>
-      <x:c r="D59" s="169" t="str">
-        <x:v>NFR-005</x:v>
-      </x:c>
-      <x:c r="E59" s="182" t="str">
-        <x:v>시스템은 분석 결과의 근거·산출 방식·규칙 또는 모델 버전을 표시하고 담당자의 검토 상태를 기록해야 한다.</x:v>
-      </x:c>
-      <x:c r="F59" s="191" t="str">
-        <x:v>정의·상세: 근거 문장·산출 방식·규칙 또는 모델 버전·분석 시각을 표시한다. 모델을 사용한 실험 결과에만 신뢰도를 표시하고, Baseline 의사결정은 담당자가 승인·보류·반려한다.
-대상 사용자: 관리자, 분석 담당
-입력→처리→출력: 리뷰·운영 → 분석·근거·버전 연결 → 설명 가능한 결과·검토 상태
-업무 규칙·예외: 중요 결정은 담당자 검토를 거치며 분류값 직접 수정은 FUN-008 승인 시에만 제공한다.
-수용 기준: Given 분석 완료 / When 결과 조회 / Then 근거·산출 방식·버전과 담당자 검토 상태가 제공된다.</x:v>
-      </x:c>
-      <x:c r="G59" s="191" t="str">
-        <x:v>우선순위: 🟡Should | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:설명가능성
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차
-산출물: AI 윤리/편향성 점검 결과서
-참고: 선행 DAT-002,DAT-004 · 화면: 근거 리뷰 · 비고: 중요도 낮음(옵션 산출물)</x:v>
+    <x:row r="59" ht="72" customHeight="1">
+      <x:c r="A59" s="210" t="str">
+        <x:v>기능</x:v>
+      </x:c>
+      <x:c r="B59" s="211" t="str">
+        <x:v>화면 요구사항</x:v>
+      </x:c>
+      <x:c r="C59" s="207" t="str">
+        <x:v>Feature Gate</x:v>
+      </x:c>
+      <x:c r="D59" s="209" t="str">
+        <x:v>REQ-UI-010</x:v>
+      </x:c>
+      <x:c r="E59" s="208" t="str">
+        <x:v>비활성 P2 및 선택 기능은 메뉴와 직접 route 모두에서 접근할 수 없어야 한다.</x:v>
+      </x:c>
+      <x:c r="F59" s="208" t="str">
+        <x:v>feature flag와 server authorization을 함께 적용한다.</x:v>
+      </x:c>
+      <x:c r="G59" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H59" s="2"/>
       <x:c r="I59" s="2"/>
@@ -4005,36 +3557,27 @@
       <x:c r="Y59" s="2"/>
       <x:c r="Z59" s="2"/>
     </x:row>
-    <x:row r="60" ht="125" customHeight="1">
-      <x:c r="A60" s="171" t="str">
+    <x:row r="60" ht="72" customHeight="1">
+      <x:c r="A60" s="210" t="str">
         <x:v>비기능</x:v>
       </x:c>
-      <x:c r="B60" s="171" t="str">
-        <x:v>비기능 요구사항</x:v>
-      </x:c>
-      <x:c r="C60" s="116" t="str">
-        <x:v>AI 윤리 실험</x:v>
-      </x:c>
-      <x:c r="D60" s="169" t="str">
-        <x:v>NFR-006</x:v>
-      </x:c>
-      <x:c r="E60" s="182" t="str">
-        <x:v>팀은 식별정보가 없는 합성 평가셋에서 정의 가능한 데이터 구간별 모델 성능 편차를 독립 점검해야 한다.</x:v>
-      </x:c>
-      <x:c r="F60" s="191" t="str">
-        <x:v>정의·상세: 성별·연령·국적 등 개인 속성은 생성하지 않는다. 합성 시나리오에 실제로 정의한 template family·서비스 영역·문장 길이 등 비식별 구간에서만 모델 성능 편차를 비교하고 한계를 기록한다.
-대상 사용자: AI·데이터 담당
-입력→처리→출력: 평가 데이터·결과 → 집단별 성능 비교 → 편향성 점검
-업무 규칙·예외: 존재하지 않는 개인 집단 속성을 편향성 평가 목적으로 새로 생성하지 않는다.
-수용 기준: Given 합성 데이터에 정의된 평가 구간이 있을 때 / When 모델을 평가하면 / Then 구간별 성능 편차·표본 수·해석 한계가 기록된다.</x:v>
-      </x:c>
-      <x:c r="G60" s="191" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:편향성 점검
-담당: D AI·Agent(윤대성)
-실행·검증: 6주차
-산출물: AI 윤리/편향성 점검 결과서
-참고: 선행 DAT-001,DAT-002 · 비고: 중요도 낮음(허용 편차는 평가 후 확정)</x:v>
+      <x:c r="B60" s="211" t="str">
+        <x:v>보안 요구사항</x:v>
+      </x:c>
+      <x:c r="C60" s="207" t="str">
+        <x:v>입력 검증</x:v>
+      </x:c>
+      <x:c r="D60" s="209" t="str">
+        <x:v>REQ-S-001</x:v>
+      </x:c>
+      <x:c r="E60" s="208" t="str">
+        <x:v>API·Controller·worker는 모든 외부 입력을 schema와 허용 목록으로 검증해야 한다.</x:v>
+      </x:c>
+      <x:c r="F60" s="208" t="str">
+        <x:v>알 수 없는 field, 범위 밖 enum, 과대 payload와 injection 패턴을 정규화 오류로 거부한다.</x:v>
+      </x:c>
+      <x:c r="G60" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H60" s="2"/>
       <x:c r="I60" s="2"/>
@@ -4056,35 +3599,27 @@
       <x:c r="Y60" s="2"/>
       <x:c r="Z60" s="2"/>
     </x:row>
-    <x:row r="61" ht="112" customHeight="1">
-      <x:c r="A61" s="173" t="str">
+    <x:row r="61" ht="72" customHeight="1">
+      <x:c r="A61" s="210" t="str">
         <x:v>비기능</x:v>
       </x:c>
-      <x:c r="B61" s="173" t="str">
-        <x:v>운영·관리 요구사항</x:v>
-      </x:c>
-      <x:c r="C61" s="119" t="str">
-        <x:v>운영 이력</x:v>
-      </x:c>
-      <x:c r="D61" s="171" t="str">
-        <x:v>OPS-001</x:v>
-      </x:c>
-      <x:c r="E61" s="183" t="str">
-        <x:v>시스템 관리자는 Baseline 분석 작업과 오류 이력을 확인할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F61" s="192" t="str">
-        <x:v>정의·상세: 기술 운영자는 분석 작업·오류 이력을 조회하고, 호텔 관리자와 담당자는 hotel_operation_daily, voc_review_raw, alert_action을 읽는 최소 모니터링 화면에서 장소별 상태·평점·운영 KPI·최종 갱신 시각·미조치 알림을 확인한다. 별도 실시간 원천 테이블은 추가하지 않는다.
-대상 사용자: 시스템 관리자
-입력→처리→출력: 작업·오류 로그 → 조회·필터 → 이력·오류 목록
-수용 기준: Given 작업 수행 시 / When 이력을 조회하면 / Then 작업·오류 이력이 표시된다.</x:v>
-      </x:c>
-      <x:c r="G61" s="192" t="str">
-        <x:v>우선순위: 🟡Should | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 3~4주차 최소 조회·7주차 최종(비차단)
-산출물: 서비스 테스트 결과서
-참고: 선행 FUN-002 · 화면: 관리자 설정</x:v>
+      <x:c r="B61" s="211" t="str">
+        <x:v>보안 요구사항</x:v>
+      </x:c>
+      <x:c r="C61" s="207" t="str">
+        <x:v>비밀정보</x:v>
+      </x:c>
+      <x:c r="D61" s="209" t="str">
+        <x:v>REQ-S-002</x:v>
+      </x:c>
+      <x:c r="E61" s="208" t="str">
+        <x:v>credential과 secret은 코드·fixture·로그·오류·화면·Artifact에 저장하거나 노출하지 않아야 한다.</x:v>
+      </x:c>
+      <x:c r="F61" s="208" t="str">
+        <x:v>환경별 secret 주입과 redaction 검증을 적용한다.</x:v>
+      </x:c>
+      <x:c r="G61" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H61" s="2"/>
       <x:c r="I61" s="2"/>
@@ -4106,36 +3641,27 @@
       <x:c r="Y61" s="2"/>
       <x:c r="Z61" s="2"/>
     </x:row>
-    <x:row r="62" ht="99" customHeight="1">
-      <x:c r="A62" s="165" t="str">
+    <x:row r="62" ht="72" customHeight="1">
+      <x:c r="A62" s="210" t="str">
         <x:v>비기능</x:v>
       </x:c>
-      <x:c r="B62" s="165" t="str">
-        <x:v>운영·관리 요구사항</x:v>
-      </x:c>
-      <x:c r="C62" s="140" t="str">
-        <x:v>모니터링</x:v>
-      </x:c>
-      <x:c r="D62" s="174" t="str">
-        <x:v>OPS-002</x:v>
-      </x:c>
-      <x:c r="E62" s="186" t="str">
-        <x:v>팀이 승인한 경우 시스템 관리자는 AI 모델·API 호출 상태를 별도 화면에서 확인할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F62" s="199" t="str">
-        <x:v>정의·상세: LLM/API 성공·실패·지연 모니터링.
-대상 사용자: 시스템 관리자
-입력→처리→출력: 호출 로그 → 상태 집계 → API 상태
-업무 규칙·예외: 장애 시 알림(가정).
-수용 기준: Given API 실패 시 / When 상태를 조회하면 / Then 실패 건수·원인이 표시된다.</x:v>
-      </x:c>
-      <x:c r="G62" s="200" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: B 백엔드·통합(김재홍)
-실행·검증: 승인 후
-산출물: 시스템 구성도
-참고: 선행 INT-001 · 화면: 관리자 설정</x:v>
+      <x:c r="B62" s="211" t="str">
+        <x:v>보안 요구사항</x:v>
+      </x:c>
+      <x:c r="C62" s="207" t="str">
+        <x:v>감사</x:v>
+      </x:c>
+      <x:c r="D62" s="209" t="str">
+        <x:v>REQ-S-003</x:v>
+      </x:c>
+      <x:c r="E62" s="208" t="str">
+        <x:v>권한·Context·Gate·query·Artifact·보고서의 중요 동작은 변경 불가능한 감사 이벤트로 연결해야 한다.</x:v>
+      </x:c>
+      <x:c r="F62" s="208" t="str">
+        <x:v>최소 user, role, entitlement hash, route, request, version, result, timestamp를 포함한다.</x:v>
+      </x:c>
+      <x:c r="G62" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H62" s="2"/>
       <x:c r="I62" s="2"/>
@@ -4157,36 +3683,27 @@
       <x:c r="Y62" s="2"/>
       <x:c r="Z62" s="2"/>
     </x:row>
-    <x:row r="63" ht="112" customHeight="1">
-      <x:c r="A63" s="168" t="str">
+    <x:row r="63" ht="72" customHeight="1">
+      <x:c r="A63" s="210" t="str">
         <x:v>비기능</x:v>
       </x:c>
-      <x:c r="B63" s="168" t="str">
-        <x:v>운영·관리 요구사항</x:v>
-      </x:c>
-      <x:c r="C63" s="140" t="str">
-        <x:v>규칙 관리</x:v>
-      </x:c>
-      <x:c r="D63" s="174" t="str">
-        <x:v>OPS-003</x:v>
-      </x:c>
-      <x:c r="E63" s="186" t="str">
-        <x:v>팀이 승인한 경우 시스템 관리자는 이상징후 임계값과 원인 후보 규칙을 화면에서 관리할 수 있어야 한다.</x:v>
-      </x:c>
-      <x:c r="F63" s="199" t="str">
-        <x:v>정의·상세: Baseline은 팀이 합의한 versioned rule을 고정 설정으로 사용한다. 운영 중 화면에서 임계값·원인 후보 규칙·대응 옵션 template을 바꾸는 기능은 필요성이 승인될 때만 구현한다.
-대상 사용자: 시스템 관리자, 분석 담당
-입력→처리→출력: 임계값·규칙 → CRUD·버전 관리 → 갱신 규칙
-업무 규칙·예외: 규칙 버전 기록(NFR-003).
-수용 기준: Given 관리 기능이 승인되고 관리자 권한일 때 / When 임계값을 변경하면 / Then 변경 전후 값·행위자·버전이 기록되고 승인된 시점부터 탐지에 반영된다.</x:v>
-      </x:c>
-      <x:c r="G63" s="200" t="str">
-        <x:v>우선순위: ⚪Could | 범위: 보류·승인 후 후보 | 성격: 가정
-AI 활용: 해당 없음
-담당: D AI·Agent(윤대성)
-실행·검증: 승인 후
-산출물: 웹 애플리케이션
-참고: 선행 AI-006,AI-009 · 화면: 관리자 설정 · 비고: 현재 Baseline 제외</x:v>
+      <x:c r="B63" s="211" t="str">
+        <x:v>보안 요구사항</x:v>
+      </x:c>
+      <x:c r="C63" s="207" t="str">
+        <x:v>보존</x:v>
+      </x:c>
+      <x:c r="D63" s="209" t="str">
+        <x:v>REQ-S-004</x:v>
+      </x:c>
+      <x:c r="E63" s="208" t="str">
+        <x:v>로그·감사·Artifact·보고서 snapshot은 승인된 보존 및 삭제 정책을 따라야 한다.</x:v>
+      </x:c>
+      <x:c r="F63" s="208" t="str">
+        <x:v>민감정보 최소화, 보존기간, 삭제 주체와 삭제 증거를 명시한다.</x:v>
+      </x:c>
+      <x:c r="G63" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H63" s="2"/>
       <x:c r="I63" s="2"/>
@@ -4208,36 +3725,27 @@
       <x:c r="Y63" s="2"/>
       <x:c r="Z63" s="2"/>
     </x:row>
-    <x:row r="64" ht="138" customHeight="1">
-      <x:c r="A64" s="161" t="str">
-        <x:v>검증</x:v>
-      </x:c>
-      <x:c r="B64" s="161" t="str">
-        <x:v>검증·테스트 요구사항</x:v>
-      </x:c>
-      <x:c r="C64" s="140" t="str">
-        <x:v>통합 테스트</x:v>
-      </x:c>
-      <x:c r="D64" s="174" t="str">
-        <x:v>TST-001</x:v>
-      </x:c>
-      <x:c r="E64" s="186" t="str">
-        <x:v>팀은 8월 13~14일에 반례 세트 v2 21건과 기능 A~D 통합 Gate를 수행해야 한다.</x:v>
-      </x:c>
-      <x:c r="F64" s="199" t="str">
-        <x:v>정의·상세: 기능 A의 로그인·권한·보장 질문·SQL Guard와 기능 B의 적재 전 validation·적재 후 analytical Gate·감지·Incident·보고서·결정을 정상·충돌·결측·권한·timeout·중복·목업 오인 반례 세트 v2 21건으로 검증한다. SQL 공격 suite에는 UNION, 주석, 다중 statement, 금지 함수·catalog 접근, scope 우회를 포함한다.
-대상 사용자: 전원(테스트 리드 백엔드)
-입력→처리→출력: 테스트 케이스 → 시나리오 실행·기록 → 테스트 보고서
-업무 규칙·예외: 발견 버그·조치 기록.
-수용 기준: Given 대표 시나리오일 때 / When 통합 테스트하면 / Then 단계 결과·이슈·조치가 기록된다.</x:v>
-      </x:c>
-      <x:c r="G64" s="200" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: 해당 없음
-담당: PM·A·B·C·D(전원)
-실행·검증: 5주차 Gate
-산출물: Baseline Gate evidence·서비스 테스트 계획 및 결과 보고서
-참고: 5주차 Gate 미통과 시 6주차 Baseline 보완을 우선하고 차단 결함이 남으면 선택 확장을 취소</x:v>
+    <x:row r="64" ht="72" customHeight="1">
+      <x:c r="A64" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B64" s="211" t="str">
+        <x:v>보안 요구사항</x:v>
+      </x:c>
+      <x:c r="C64" s="207" t="str">
+        <x:v>내보내기</x:v>
+      </x:c>
+      <x:c r="D64" s="209" t="str">
+        <x:v>REQ-S-005</x:v>
+      </x:c>
+      <x:c r="E64" s="208" t="str">
+        <x:v>데이터 및 감사 내보내기는 별도 권한·범위 검증과 감사 기록을 요구해야 한다.</x:v>
+      </x:c>
+      <x:c r="F64" s="208" t="str">
+        <x:v>승인 범위를 넘는 컬럼·행·원문 PII를 포함하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G64" s="208" t="str">
+        <x:v>P1</x:v>
       </x:c>
       <x:c r="H64" s="2"/>
       <x:c r="I64" s="2"/>
@@ -4259,36 +3767,27 @@
       <x:c r="Y64" s="2"/>
       <x:c r="Z64" s="2"/>
     </x:row>
-    <x:row r="65" ht="125" customHeight="1">
-      <x:c r="A65" s="165" t="str">
-        <x:v>검증</x:v>
-      </x:c>
-      <x:c r="B65" s="165" t="str">
-        <x:v>검증·테스트 요구사항</x:v>
-      </x:c>
-      <x:c r="C65" s="140" t="str">
-        <x:v>에이전트 테스트</x:v>
-      </x:c>
-      <x:c r="D65" s="174" t="str">
-        <x:v>TST-002</x:v>
-      </x:c>
-      <x:c r="E65" s="186" t="str">
-        <x:v>팀은 멀티 에이전트 라우팅과 실패 대응(Fallback)을 독립 실험해야 한다.</x:v>
-      </x:c>
-      <x:c r="F65" s="199" t="str">
-        <x:v>정의·상세: 기능 B의 단일 Agent와 계획·조사·작성 3역할 구성을 같은 합성 scenario에서 비교한다. Baseline은 논리 Agent 2개 구조를 유지하고 이 실험 결과에 의존하지 않는다.
-대상 사용자: 분석 담당
-입력→처리→출력: 테스트 케이스 → 라우팅·Fallback 검증 → 에이전트 테스트 결과
-업무 규칙·예외: 기대 대비 실제 기록.
-수용 기준: Given 의도별 질문 세트일 때 / When 실행하면 / Then 라우팅·Fallback 동작이 기록된다.</x:v>
-      </x:c>
-      <x:c r="G65" s="200" t="str">
-        <x:v>우선순위: 🟡Should | 범위: 독립 실험 | 성격: 결정
-AI 활용: AI:에이전트 검증
-담당: D AI·Agent(윤대성)
-실행·검증: 6주차
-산출물: 멀티 에이전트 테스트 계획 및 결과 보고서
-참고: 선행 FUN-006 · 화면: 분석 에이전트 · 비고: 🎓 교육 산출물 제약</x:v>
+    <x:row r="65" ht="72" customHeight="1">
+      <x:c r="A65" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B65" s="211" t="str">
+        <x:v>운영 요구사항</x:v>
+      </x:c>
+      <x:c r="C65" s="207" t="str">
+        <x:v>상태 확인</x:v>
+      </x:c>
+      <x:c r="D65" s="209" t="str">
+        <x:v>REQ-O-001</x:v>
+      </x:c>
+      <x:c r="E65" s="208" t="str">
+        <x:v>각 서비스는 기동·준비·의존성 상태를 구분하는 health 정보를 제공해야 한다.</x:v>
+      </x:c>
+      <x:c r="F65" s="208" t="str">
+        <x:v>단순 process 생존과 실제 요청 준비 상태를 구분하고 root 통합 health 계약을 따른다.</x:v>
+      </x:c>
+      <x:c r="G65" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H65" s="2"/>
       <x:c r="I65" s="2"/>
@@ -4310,36 +3809,27 @@
       <x:c r="Y65" s="2"/>
       <x:c r="Z65" s="2"/>
     </x:row>
-    <x:row r="66" ht="125" customHeight="1">
-      <x:c r="A66" s="168" t="str">
-        <x:v>검증</x:v>
-      </x:c>
-      <x:c r="B66" s="168" t="str">
-        <x:v>검증·테스트 요구사항</x:v>
-      </x:c>
-      <x:c r="C66" s="144" t="str">
-        <x:v>eval 정답표</x:v>
-      </x:c>
-      <x:c r="D66" s="176" t="str">
-        <x:v>TST-003</x:v>
-      </x:c>
-      <x:c r="E66" s="189" t="str">
-        <x:v>팀은 합성 데이터 정답표로 분석·에이전트 정확도를 자동 채점(회귀 테스트)해야 한다.</x:v>
-      </x:c>
-      <x:c r="F66" s="201" t="str">
-        <x:v>정의·상세: 합성 정답 manifest로 반례 세트 v2 21건을 자동 채점하고, 8개 intent×3개 역할×검증 발화 3종의 허용·차단 결과와 복수 seed 회귀를 확인한 뒤 최종 안정화에서 Golden Path를 연속 5회 재현한다. 특정 관측성 제품은 Baseline 필수 의존성으로 두지 않는다.
-대상 사용자: 분석 담당
-입력→처리→출력: 정답표·결과 → 자동 채점·추적 → 정확도 리포트
-업무 규칙·예외: 보장 세트는 회귀 테스트 통과 필수.
-수용 기준: Given 정답표가 있을 때 / When 자동 채점하면 / Then 시나리오별 정확도와 회귀 결과가 산출된다.</x:v>
-      </x:c>
-      <x:c r="G66" s="202" t="str">
-        <x:v>우선순위: 🔴Must | 범위: Baseline 필수 | 성격: 결정
-AI 활용: AI:eval/관측성
-담당: D AI·Agent(윤대성)
-실행·검증: 5주차 Gate·6~7주차 회귀·8주차 5회
-산출물: 서비스 테스트 결과서
-참고: 선행 DAT-008 · 비고: 측정 서사</x:v>
+    <x:row r="66" ht="72" customHeight="1">
+      <x:c r="A66" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B66" s="211" t="str">
+        <x:v>운영 요구사항</x:v>
+      </x:c>
+      <x:c r="C66" s="207" t="str">
+        <x:v>관측성</x:v>
+      </x:c>
+      <x:c r="D66" s="209" t="str">
+        <x:v>REQ-O-002</x:v>
+      </x:c>
+      <x:c r="E66" s="208" t="str">
+        <x:v>요청과 비동기 실행은 공통 식별자로 구조화 로그·metric·trace를 연결해야 한다.</x:v>
+      </x:c>
+      <x:c r="F66" s="208" t="str">
+        <x:v>conversation_id, request_id, query/artifact/report/run ID를 사용하고 secret·CoT를 기록하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G66" s="208" t="str">
+        <x:v>P0·필수</x:v>
       </x:c>
       <x:c r="H66" s="2"/>
       <x:c r="I66" s="2"/>
@@ -4361,14 +3851,28 @@
       <x:c r="Y66" s="2"/>
       <x:c r="Z66" s="2"/>
     </x:row>
-    <x:row r="67" ht="15.75" customHeight="1">
-      <x:c r="A67" s="2"/>
-      <x:c r="B67" s="2"/>
-      <x:c r="C67" s="2"/>
-      <x:c r="D67" s="2"/>
-      <x:c r="E67" s="2"/>
-      <x:c r="F67" s="2"/>
-      <x:c r="G67" s="2"/>
+    <x:row r="67" ht="72" customHeight="1">
+      <x:c r="A67" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B67" s="211" t="str">
+        <x:v>운영 요구사항</x:v>
+      </x:c>
+      <x:c r="C67" s="207" t="str">
+        <x:v>Worker</x:v>
+      </x:c>
+      <x:c r="D67" s="209" t="str">
+        <x:v>REQ-O-003</x:v>
+      </x:c>
+      <x:c r="E67" s="208" t="str">
+        <x:v>보고서 실행 worker는 idempotency, 중복 방지, timeout과 안전한 재시도 정책을 적용해야 한다.</x:v>
+      </x:c>
+      <x:c r="F67" s="208" t="str">
+        <x:v>부분 실패와 재시작 후 상태를 재구성할 수 있어야 한다.</x:v>
+      </x:c>
+      <x:c r="G67" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H67" s="2"/>
       <x:c r="I67" s="2"/>
       <x:c r="J67" s="2"/>
@@ -4389,14 +3893,28 @@
       <x:c r="Y67" s="2"/>
       <x:c r="Z67" s="2"/>
     </x:row>
-    <x:row r="68" ht="15.75" customHeight="1">
-      <x:c r="A68" s="2"/>
-      <x:c r="B68" s="2"/>
-      <x:c r="C68" s="2"/>
-      <x:c r="D68" s="2"/>
-      <x:c r="E68" s="2"/>
-      <x:c r="F68" s="2"/>
-      <x:c r="G68" s="2"/>
+    <x:row r="68" ht="72" customHeight="1">
+      <x:c r="A68" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B68" s="211" t="str">
+        <x:v>운영 요구사항</x:v>
+      </x:c>
+      <x:c r="C68" s="207" t="str">
+        <x:v>백업·복구</x:v>
+      </x:c>
+      <x:c r="D68" s="209" t="str">
+        <x:v>REQ-O-004</x:v>
+      </x:c>
+      <x:c r="E68" s="208" t="str">
+        <x:v>애플리케이션 DB, versioned policy와 Artifact metadata는 백업·복구 절차를 가져야 한다.</x:v>
+      </x:c>
+      <x:c r="F68" s="208" t="str">
+        <x:v>승인된 빈 환경에서 restore test를 수행하고 복구 증거와 한계를 기록한다.</x:v>
+      </x:c>
+      <x:c r="G68" s="208" t="str">
+        <x:v>P1·필수</x:v>
+      </x:c>
       <x:c r="H68" s="2"/>
       <x:c r="I68" s="2"/>
       <x:c r="J68" s="2"/>
@@ -4417,14 +3935,28 @@
       <x:c r="Y68" s="2"/>
       <x:c r="Z68" s="2"/>
     </x:row>
-    <x:row r="69" ht="15.75" customHeight="1">
-      <x:c r="A69" s="2"/>
-      <x:c r="B69" s="2"/>
-      <x:c r="C69" s="2"/>
-      <x:c r="D69" s="2"/>
-      <x:c r="E69" s="2"/>
-      <x:c r="F69" s="2"/>
-      <x:c r="G69" s="2"/>
+    <x:row r="69" ht="72" customHeight="1">
+      <x:c r="A69" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B69" s="211" t="str">
+        <x:v>운영 요구사항</x:v>
+      </x:c>
+      <x:c r="C69" s="207" t="str">
+        <x:v>배포</x:v>
+      </x:c>
+      <x:c r="D69" s="209" t="str">
+        <x:v>REQ-O-005</x:v>
+      </x:c>
+      <x:c r="E69" s="208" t="str">
+        <x:v>배포물은 code·data·model·prompt·policy·seed·schema version을 manifest로 고정해야 한다.</x:v>
+      </x:c>
+      <x:c r="F69" s="208" t="str">
+        <x:v>RC2 승인 후 변경을 금지하고 승인 SHA와 고정 fixture로 시연한다.</x:v>
+      </x:c>
+      <x:c r="G69" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H69" s="2"/>
       <x:c r="I69" s="2"/>
       <x:c r="J69" s="2"/>
@@ -4445,14 +3977,28 @@
       <x:c r="Y69" s="2"/>
       <x:c r="Z69" s="2"/>
     </x:row>
-    <x:row r="70" ht="15.75" customHeight="1">
-      <x:c r="A70" s="2"/>
-      <x:c r="B70" s="2"/>
-      <x:c r="C70" s="2"/>
-      <x:c r="D70" s="2"/>
-      <x:c r="E70" s="2"/>
-      <x:c r="F70" s="2"/>
-      <x:c r="G70" s="2"/>
+    <x:row r="70" ht="72" customHeight="1">
+      <x:c r="A70" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B70" s="211" t="str">
+        <x:v>운영 요구사항</x:v>
+      </x:c>
+      <x:c r="C70" s="207" t="str">
+        <x:v>실패 격리</x:v>
+      </x:c>
+      <x:c r="D70" s="209" t="str">
+        <x:v>REQ-O-006</x:v>
+      </x:c>
+      <x:c r="E70" s="208" t="str">
+        <x:v>외부 모델·DataHub·개별 source 장애가 권한·Gate를 우회하는 fallback을 유발하지 않아야 한다.</x:v>
+      </x:c>
+      <x:c r="F70" s="208" t="str">
+        <x:v>degraded 상태와 사용 불가 기능을 표시하고 승인되지 않은 대체 경로를 실행하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G70" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H70" s="2"/>
       <x:c r="I70" s="2"/>
       <x:c r="J70" s="2"/>
@@ -4473,14 +4019,28 @@
       <x:c r="Y70" s="2"/>
       <x:c r="Z70" s="2"/>
     </x:row>
-    <x:row r="71" ht="15.75" customHeight="1">
-      <x:c r="A71" s="2"/>
-      <x:c r="B71" s="2"/>
-      <x:c r="C71" s="2"/>
-      <x:c r="D71" s="2"/>
-      <x:c r="E71" s="2"/>
-      <x:c r="F71" s="2"/>
-      <x:c r="G71" s="2"/>
+    <x:row r="71" ht="72" customHeight="1">
+      <x:c r="A71" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B71" s="211" t="str">
+        <x:v>비기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C71" s="207" t="str">
+        <x:v>성능</x:v>
+      </x:c>
+      <x:c r="D71" s="209" t="str">
+        <x:v>REQ-NFR-001</x:v>
+      </x:c>
+      <x:c r="E71" s="208" t="str">
+        <x:v>대표 질문과 보고서 실행의 p50·p95 지연을 동일 조건에서 측정해야 한다.</x:v>
+      </x:c>
+      <x:c r="F71" s="208" t="str">
+        <x:v>warm/cold, batch size, 입력·출력 상한과 측정 환경을 기록하며 실측 전 임의 SLO를 확정하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G71" s="208" t="str">
+        <x:v>P1</x:v>
+      </x:c>
       <x:c r="H71" s="2"/>
       <x:c r="I71" s="2"/>
       <x:c r="J71" s="2"/>
@@ -4501,14 +4061,28 @@
       <x:c r="Y71" s="2"/>
       <x:c r="Z71" s="2"/>
     </x:row>
-    <x:row r="72" ht="15.75" customHeight="1">
-      <x:c r="A72" s="2"/>
-      <x:c r="B72" s="2"/>
-      <x:c r="C72" s="2"/>
-      <x:c r="D72" s="2"/>
-      <x:c r="E72" s="2"/>
-      <x:c r="F72" s="2"/>
-      <x:c r="G72" s="2"/>
+    <x:row r="72" ht="72" customHeight="1">
+      <x:c r="A72" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B72" s="211" t="str">
+        <x:v>비기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C72" s="207" t="str">
+        <x:v>신뢰성</x:v>
+      </x:c>
+      <x:c r="D72" s="209" t="str">
+        <x:v>REQ-NFR-002</x:v>
+      </x:c>
+      <x:c r="E72" s="208" t="str">
+        <x:v>동일 승인 입력과 version에서 결과 재현성 또는 설명 가능한 차이를 제공해야 한다.</x:v>
+      </x:c>
+      <x:c r="F72" s="208" t="str">
+        <x:v>SQL, as_of, source watermark, checksum과 모델 비결정성 조건을 기록한다.</x:v>
+      </x:c>
+      <x:c r="G72" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H72" s="2"/>
       <x:c r="I72" s="2"/>
       <x:c r="J72" s="2"/>
@@ -4529,14 +4103,28 @@
       <x:c r="Y72" s="2"/>
       <x:c r="Z72" s="2"/>
     </x:row>
-    <x:row r="73" ht="15.75" customHeight="1">
-      <x:c r="A73" s="2"/>
-      <x:c r="B73" s="2"/>
-      <x:c r="C73" s="2"/>
-      <x:c r="D73" s="2"/>
-      <x:c r="E73" s="2"/>
-      <x:c r="F73" s="2"/>
-      <x:c r="G73" s="2"/>
+    <x:row r="73" ht="72" customHeight="1">
+      <x:c r="A73" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B73" s="211" t="str">
+        <x:v>비기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C73" s="207" t="str">
+        <x:v>호환성</x:v>
+      </x:c>
+      <x:c r="D73" s="209" t="str">
+        <x:v>REQ-NFR-003</x:v>
+      </x:c>
+      <x:c r="E73" s="208" t="str">
+        <x:v>OpenAPI·상태·오류·fixture 계약은 version으로 관리하고 생산자·소비자 contract test를 통과해야 한다.</x:v>
+      </x:c>
+      <x:c r="F73" s="208" t="str">
+        <x:v>호환성 파괴 변경은 새 version과 migration·handoff를 요구한다.</x:v>
+      </x:c>
+      <x:c r="G73" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H73" s="2"/>
       <x:c r="I73" s="2"/>
       <x:c r="J73" s="2"/>
@@ -4557,14 +4145,28 @@
       <x:c r="Y73" s="2"/>
       <x:c r="Z73" s="2"/>
     </x:row>
-    <x:row r="74" ht="15.75" customHeight="1">
-      <x:c r="A74" s="2"/>
-      <x:c r="B74" s="2"/>
-      <x:c r="C74" s="2"/>
-      <x:c r="D74" s="2"/>
-      <x:c r="E74" s="2"/>
-      <x:c r="F74" s="2"/>
-      <x:c r="G74" s="2"/>
+    <x:row r="74" ht="72" customHeight="1">
+      <x:c r="A74" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B74" s="211" t="str">
+        <x:v>비기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C74" s="207" t="str">
+        <x:v>유지보수성</x:v>
+      </x:c>
+      <x:c r="D74" s="209" t="str">
+        <x:v>REQ-NFR-004</x:v>
+      </x:c>
+      <x:c r="E74" s="208" t="str">
+        <x:v>backend는 FastAPI, frontend는 활성 React 앱의 기존 구조를 사용해야 한다.</x:v>
+      </x:c>
+      <x:c r="F74" s="208" t="str">
+        <x:v>Django, 자유 ReAct loop, 앱 내부 federation과 요청되지 않은 중복 abstraction을 추가하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G74" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H74" s="2"/>
       <x:c r="I74" s="2"/>
       <x:c r="J74" s="2"/>
@@ -4585,14 +4187,28 @@
       <x:c r="Y74" s="2"/>
       <x:c r="Z74" s="2"/>
     </x:row>
-    <x:row r="75" ht="15.75" customHeight="1">
-      <x:c r="A75" s="2"/>
-      <x:c r="B75" s="2"/>
-      <x:c r="C75" s="2"/>
-      <x:c r="D75" s="2"/>
-      <x:c r="E75" s="2"/>
-      <x:c r="F75" s="2"/>
-      <x:c r="G75" s="2"/>
+    <x:row r="75" ht="72" customHeight="1">
+      <x:c r="A75" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B75" s="211" t="str">
+        <x:v>비기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C75" s="207" t="str">
+        <x:v>테스트</x:v>
+      </x:c>
+      <x:c r="D75" s="209" t="str">
+        <x:v>REQ-NFR-005</x:v>
+      </x:c>
+      <x:c r="E75" s="208" t="str">
+        <x:v>변경 범위에 적용 가능한 formatter·lint·type check·unit·contract·build·E2E를 실행해야 한다.</x:v>
+      </x:c>
+      <x:c r="F75" s="208" t="str">
+        <x:v>실행하지 않은 검증은 Not Run, 외부 환경 부족은 Blocked와 사유로 기록한다.</x:v>
+      </x:c>
+      <x:c r="G75" s="208" t="str">
+        <x:v>P0·필수</x:v>
+      </x:c>
       <x:c r="H75" s="2"/>
       <x:c r="I75" s="2"/>
       <x:c r="J75" s="2"/>
@@ -4613,14 +4229,28 @@
       <x:c r="Y75" s="2"/>
       <x:c r="Z75" s="2"/>
     </x:row>
-    <x:row r="76" ht="15.75" customHeight="1">
-      <x:c r="A76" s="2"/>
-      <x:c r="B76" s="2"/>
-      <x:c r="C76" s="2"/>
-      <x:c r="D76" s="2"/>
-      <x:c r="E76" s="2"/>
-      <x:c r="F76" s="2"/>
-      <x:c r="G76" s="2"/>
+    <x:row r="76" ht="72" customHeight="1">
+      <x:c r="A76" s="210" t="str">
+        <x:v>비기능</x:v>
+      </x:c>
+      <x:c r="B76" s="211" t="str">
+        <x:v>비기능 요구사항</x:v>
+      </x:c>
+      <x:c r="C76" s="207" t="str">
+        <x:v>사용성</x:v>
+      </x:c>
+      <x:c r="D76" s="209" t="str">
+        <x:v>REQ-NFR-006</x:v>
+      </x:c>
+      <x:c r="E76" s="208" t="str">
+        <x:v>오류·빈 값·부분 성공 화면은 사용자가 안전한 다음 행동을 선택할 수 있게 해야 한다.</x:v>
+      </x:c>
+      <x:c r="F76" s="208" t="str">
+        <x:v>수정, 재시도, 이전 화면 이동 또는 관리자 문의 중 허용된 동작을 명확히 제공한다.</x:v>
+      </x:c>
+      <x:c r="G76" s="208" t="str">
+        <x:v>P0</x:v>
+      </x:c>
       <x:c r="H76" s="2"/>
       <x:c r="I76" s="2"/>
       <x:c r="J76" s="2"/>
@@ -4641,14 +4271,28 @@
       <x:c r="Y76" s="2"/>
       <x:c r="Z76" s="2"/>
     </x:row>
-    <x:row r="77" ht="15.75" customHeight="1">
-      <x:c r="A77" s="2"/>
-      <x:c r="B77" s="2"/>
-      <x:c r="C77" s="2"/>
-      <x:c r="D77" s="2"/>
-      <x:c r="E77" s="2"/>
-      <x:c r="F77" s="2"/>
-      <x:c r="G77" s="2"/>
+    <x:row r="77" ht="72" customHeight="1">
+      <x:c r="A77" s="210" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="B77" s="211" t="str">
+        <x:v>범위 요구사항</x:v>
+      </x:c>
+      <x:c r="C77" s="207" t="str">
+        <x:v>P2</x:v>
+      </x:c>
+      <x:c r="D77" s="209" t="str">
+        <x:v>REQ-SCP-001</x:v>
+      </x:c>
+      <x:c r="E77" s="208" t="str">
+        <x:v>MCP·문서 RAG·ML-as-a-Tool은 P0/P1 완료와 R1 편입 승인 전 비활성 상태여야 한다.</x:v>
+      </x:c>
+      <x:c r="F77" s="208" t="str">
+        <x:v>route·메뉴·worker·dependency를 선행 구현하지 않는다.</x:v>
+      </x:c>
+      <x:c r="G77" s="208" t="str">
+        <x:v>P2·기본 제외</x:v>
+      </x:c>
       <x:c r="H77" s="2"/>
       <x:c r="I77" s="2"/>
       <x:c r="J77" s="2"/>
@@ -4669,14 +4313,28 @@
       <x:c r="Y77" s="2"/>
       <x:c r="Z77" s="2"/>
     </x:row>
-    <x:row r="78" ht="15.75" customHeight="1">
-      <x:c r="A78" s="2"/>
-      <x:c r="B78" s="2"/>
-      <x:c r="C78" s="2"/>
-      <x:c r="D78" s="2"/>
-      <x:c r="E78" s="2"/>
-      <x:c r="F78" s="2"/>
-      <x:c r="G78" s="2"/>
+    <x:row r="78" ht="72" customHeight="1">
+      <x:c r="A78" s="210" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="B78" s="211" t="str">
+        <x:v>범위 요구사항</x:v>
+      </x:c>
+      <x:c r="C78" s="207" t="str">
+        <x:v>고객 360</x:v>
+      </x:c>
+      <x:c r="D78" s="209" t="str">
+        <x:v>REQ-SCP-002</x:v>
+      </x:c>
+      <x:c r="E78" s="208" t="str">
+        <x:v>고객 360은 identity mapping·masking·전용 권한과 일정 영향 승인 전 비활성 상태여야 한다.</x:v>
+      </x:c>
+      <x:c r="F78" s="208" t="str">
+        <x:v>승인 전 MVP navigation과 직접 route에서 접근할 수 없다.</x:v>
+      </x:c>
+      <x:c r="G78" s="208" t="str">
+        <x:v>선택·기본 제외</x:v>
+      </x:c>
       <x:c r="H78" s="2"/>
       <x:c r="I78" s="2"/>
       <x:c r="J78" s="2"/>
@@ -4697,14 +4355,28 @@
       <x:c r="Y78" s="2"/>
       <x:c r="Z78" s="2"/>
     </x:row>
-    <x:row r="79" ht="15.75" customHeight="1">
-      <x:c r="A79" s="2"/>
-      <x:c r="B79" s="2"/>
-      <x:c r="C79" s="2"/>
-      <x:c r="D79" s="2"/>
-      <x:c r="E79" s="2"/>
-      <x:c r="F79" s="2"/>
-      <x:c r="G79" s="2"/>
+    <x:row r="79" ht="72" customHeight="1">
+      <x:c r="A79" s="210" t="str">
+        <x:v>범위</x:v>
+      </x:c>
+      <x:c r="B79" s="211" t="str">
+        <x:v>범위 요구사항</x:v>
+      </x:c>
+      <x:c r="C79" s="207" t="str">
+        <x:v>외부 배포</x:v>
+      </x:c>
+      <x:c r="D79" s="209" t="str">
+        <x:v>REQ-SCP-003</x:v>
+      </x:c>
+      <x:c r="E79" s="208" t="str">
+        <x:v>외부 Report 배포와 다단 승인 workflow는 별도 승인 전 구현하지 않아야 한다.</x:v>
+      </x:c>
+      <x:c r="F79" s="208" t="str">
+        <x:v>P0는 내부 정의·승인·수동/스케줄 실행·이력에 한정한다.</x:v>
+      </x:c>
+      <x:c r="G79" s="208" t="str">
+        <x:v>P2·기본 제외</x:v>
+      </x:c>
       <x:c r="H79" s="2"/>
       <x:c r="I79" s="2"/>
       <x:c r="J79" s="2"/>
@@ -4726,13 +4398,13 @@
       <x:c r="Z79" s="2"/>
     </x:row>
     <x:row r="80" ht="15.75" customHeight="1">
-      <x:c r="A80" s="2"/>
-      <x:c r="B80" s="2"/>
-      <x:c r="C80" s="2"/>
-      <x:c r="D80" s="2"/>
-      <x:c r="E80" s="2"/>
-      <x:c r="F80" s="2"/>
-      <x:c r="G80" s="2"/>
+      <x:c r="A80"/>
+      <x:c r="B80"/>
+      <x:c r="C80"/>
+      <x:c r="D80"/>
+      <x:c r="E80"/>
+      <x:c r="F80"/>
+      <x:c r="G80"/>
       <x:c r="H80" s="2"/>
       <x:c r="I80" s="2"/>
       <x:c r="J80" s="2"/>
@@ -4754,13 +4426,13 @@
       <x:c r="Z80" s="2"/>
     </x:row>
     <x:row r="81" ht="15.75" customHeight="1">
-      <x:c r="A81" s="2"/>
-      <x:c r="B81" s="2"/>
-      <x:c r="C81" s="2"/>
-      <x:c r="D81" s="2"/>
-      <x:c r="E81" s="2"/>
-      <x:c r="F81" s="2"/>
-      <x:c r="G81" s="2"/>
+      <x:c r="A81"/>
+      <x:c r="B81"/>
+      <x:c r="C81"/>
+      <x:c r="D81"/>
+      <x:c r="E81"/>
+      <x:c r="F81"/>
+      <x:c r="G81"/>
       <x:c r="H81" s="2"/>
       <x:c r="I81" s="2"/>
       <x:c r="J81" s="2"/>
@@ -4782,13 +4454,13 @@
       <x:c r="Z81" s="2"/>
     </x:row>
     <x:row r="82" ht="15.75" customHeight="1">
-      <x:c r="A82" s="2"/>
-      <x:c r="B82" s="2"/>
-      <x:c r="C82" s="2"/>
-      <x:c r="D82" s="2"/>
-      <x:c r="E82" s="2"/>
-      <x:c r="F82" s="2"/>
-      <x:c r="G82" s="2"/>
+      <x:c r="A82"/>
+      <x:c r="B82"/>
+      <x:c r="C82"/>
+      <x:c r="D82"/>
+      <x:c r="E82"/>
+      <x:c r="F82"/>
+      <x:c r="G82"/>
       <x:c r="H82" s="2"/>
       <x:c r="I82" s="2"/>
       <x:c r="J82" s="2"/>
@@ -4810,13 +4482,13 @@
       <x:c r="Z82" s="2"/>
     </x:row>
     <x:row r="83" ht="15.75" customHeight="1">
-      <x:c r="A83" s="2"/>
-      <x:c r="B83" s="2"/>
-      <x:c r="C83" s="2"/>
-      <x:c r="D83" s="2"/>
-      <x:c r="E83" s="2"/>
-      <x:c r="F83" s="2"/>
-      <x:c r="G83" s="2"/>
+      <x:c r="A83"/>
+      <x:c r="B83"/>
+      <x:c r="C83"/>
+      <x:c r="D83"/>
+      <x:c r="E83"/>
+      <x:c r="F83"/>
+      <x:c r="G83"/>
       <x:c r="H83" s="2"/>
       <x:c r="I83" s="2"/>
       <x:c r="J83" s="2"/>
@@ -4838,13 +4510,13 @@
       <x:c r="Z83" s="2"/>
     </x:row>
     <x:row r="84" ht="15.75" customHeight="1">
-      <x:c r="A84" s="2"/>
-      <x:c r="B84" s="2"/>
-      <x:c r="C84" s="2"/>
-      <x:c r="D84" s="2"/>
-      <x:c r="E84" s="2"/>
-      <x:c r="F84" s="2"/>
-      <x:c r="G84" s="2"/>
+      <x:c r="A84"/>
+      <x:c r="B84"/>
+      <x:c r="C84"/>
+      <x:c r="D84"/>
+      <x:c r="E84"/>
+      <x:c r="F84"/>
+      <x:c r="G84"/>
       <x:c r="H84" s="2"/>
       <x:c r="I84" s="2"/>
       <x:c r="J84" s="2"/>
@@ -4866,13 +4538,13 @@
       <x:c r="Z84" s="2"/>
     </x:row>
     <x:row r="85" ht="15.75" customHeight="1">
-      <x:c r="A85" s="2"/>
-      <x:c r="B85" s="2"/>
-      <x:c r="C85" s="2"/>
-      <x:c r="D85" s="2"/>
-      <x:c r="E85" s="2"/>
-      <x:c r="F85" s="2"/>
-      <x:c r="G85" s="2"/>
+      <x:c r="A85"/>
+      <x:c r="B85"/>
+      <x:c r="C85"/>
+      <x:c r="D85"/>
+      <x:c r="E85"/>
+      <x:c r="F85"/>
+      <x:c r="G85"/>
       <x:c r="H85" s="2"/>
       <x:c r="I85" s="2"/>
       <x:c r="J85" s="2"/>
@@ -4894,13 +4566,13 @@
       <x:c r="Z85" s="2"/>
     </x:row>
     <x:row r="86" ht="15.75" customHeight="1">
-      <x:c r="A86" s="2"/>
-      <x:c r="B86" s="2"/>
-      <x:c r="C86" s="2"/>
-      <x:c r="D86" s="2"/>
-      <x:c r="E86" s="2"/>
-      <x:c r="F86" s="2"/>
-      <x:c r="G86" s="2"/>
+      <x:c r="A86"/>
+      <x:c r="B86"/>
+      <x:c r="C86"/>
+      <x:c r="D86"/>
+      <x:c r="E86"/>
+      <x:c r="F86"/>
+      <x:c r="G86"/>
       <x:c r="H86" s="2"/>
       <x:c r="I86" s="2"/>
       <x:c r="J86" s="2"/>
@@ -4922,13 +4594,13 @@
       <x:c r="Z86" s="2"/>
     </x:row>
     <x:row r="87" ht="15.75" customHeight="1">
-      <x:c r="A87" s="2"/>
-      <x:c r="B87" s="2"/>
-      <x:c r="C87" s="2"/>
-      <x:c r="D87" s="2"/>
-      <x:c r="E87" s="2"/>
-      <x:c r="F87" s="2"/>
-      <x:c r="G87" s="2"/>
+      <x:c r="A87"/>
+      <x:c r="B87"/>
+      <x:c r="C87"/>
+      <x:c r="D87"/>
+      <x:c r="E87"/>
+      <x:c r="F87"/>
+      <x:c r="G87"/>
       <x:c r="H87" s="2"/>
       <x:c r="I87" s="2"/>
       <x:c r="J87" s="2"/>
@@ -4950,13 +4622,13 @@
       <x:c r="Z87" s="2"/>
     </x:row>
     <x:row r="88" ht="15.75" customHeight="1">
-      <x:c r="A88" s="2"/>
-      <x:c r="B88" s="2"/>
-      <x:c r="C88" s="2"/>
-      <x:c r="D88" s="2"/>
-      <x:c r="E88" s="2"/>
-      <x:c r="F88" s="2"/>
-      <x:c r="G88" s="2"/>
+      <x:c r="A88"/>
+      <x:c r="B88"/>
+      <x:c r="C88"/>
+      <x:c r="D88"/>
+      <x:c r="E88"/>
+      <x:c r="F88"/>
+      <x:c r="G88"/>
       <x:c r="H88" s="2"/>
       <x:c r="I88" s="2"/>
       <x:c r="J88" s="2"/>
@@ -4978,13 +4650,13 @@
       <x:c r="Z88" s="2"/>
     </x:row>
     <x:row r="89" ht="15.75" customHeight="1">
-      <x:c r="A89" s="2"/>
-      <x:c r="B89" s="2"/>
-      <x:c r="C89" s="2"/>
-      <x:c r="D89" s="2"/>
-      <x:c r="E89" s="2"/>
-      <x:c r="F89" s="2"/>
-      <x:c r="G89" s="2"/>
+      <x:c r="A89"/>
+      <x:c r="B89"/>
+      <x:c r="C89"/>
+      <x:c r="D89"/>
+      <x:c r="E89"/>
+      <x:c r="F89"/>
+      <x:c r="G89"/>
       <x:c r="H89" s="2"/>
       <x:c r="I89" s="2"/>
       <x:c r="J89" s="2"/>
@@ -5006,13 +4678,13 @@
       <x:c r="Z89" s="2"/>
     </x:row>
     <x:row r="90" ht="15.75" customHeight="1">
-      <x:c r="A90" s="2"/>
-      <x:c r="B90" s="2"/>
-      <x:c r="C90" s="2"/>
-      <x:c r="D90" s="2"/>
-      <x:c r="E90" s="2"/>
-      <x:c r="F90" s="2"/>
-      <x:c r="G90" s="2"/>
+      <x:c r="A90"/>
+      <x:c r="B90"/>
+      <x:c r="C90"/>
+      <x:c r="D90"/>
+      <x:c r="E90"/>
+      <x:c r="F90"/>
+      <x:c r="G90"/>
       <x:c r="H90" s="2"/>
       <x:c r="I90" s="2"/>
       <x:c r="J90" s="2"/>
@@ -5034,13 +4706,13 @@
       <x:c r="Z90" s="2"/>
     </x:row>
     <x:row r="91" ht="15.75" customHeight="1">
-      <x:c r="A91" s="2"/>
-      <x:c r="B91" s="2"/>
-      <x:c r="C91" s="2"/>
-      <x:c r="D91" s="2"/>
-      <x:c r="E91" s="2"/>
-      <x:c r="F91" s="2"/>
-      <x:c r="G91" s="2"/>
+      <x:c r="A91"/>
+      <x:c r="B91"/>
+      <x:c r="C91"/>
+      <x:c r="D91"/>
+      <x:c r="E91"/>
+      <x:c r="F91"/>
+      <x:c r="G91"/>
       <x:c r="H91" s="2"/>
       <x:c r="I91" s="2"/>
       <x:c r="J91" s="2"/>
@@ -5062,13 +4734,13 @@
       <x:c r="Z91" s="2"/>
     </x:row>
     <x:row r="92" ht="15.75" customHeight="1">
-      <x:c r="A92" s="2"/>
-      <x:c r="B92" s="2"/>
-      <x:c r="C92" s="2"/>
-      <x:c r="D92" s="2"/>
-      <x:c r="E92" s="2"/>
-      <x:c r="F92" s="2"/>
-      <x:c r="G92" s="2"/>
+      <x:c r="A92"/>
+      <x:c r="B92"/>
+      <x:c r="C92"/>
+      <x:c r="D92"/>
+      <x:c r="E92"/>
+      <x:c r="F92"/>
+      <x:c r="G92"/>
       <x:c r="H92" s="2"/>
       <x:c r="I92" s="2"/>
       <x:c r="J92" s="2"/>
@@ -5090,13 +4762,13 @@
       <x:c r="Z92" s="2"/>
     </x:row>
     <x:row r="93" ht="15.75" customHeight="1">
-      <x:c r="A93" s="2"/>
-      <x:c r="B93" s="2"/>
-      <x:c r="C93" s="2"/>
-      <x:c r="D93" s="2"/>
-      <x:c r="E93" s="2"/>
-      <x:c r="F93" s="2"/>
-      <x:c r="G93" s="2"/>
+      <x:c r="A93"/>
+      <x:c r="B93"/>
+      <x:c r="C93"/>
+      <x:c r="D93"/>
+      <x:c r="E93"/>
+      <x:c r="F93"/>
+      <x:c r="G93"/>
       <x:c r="H93" s="2"/>
       <x:c r="I93" s="2"/>
       <x:c r="J93" s="2"/>
@@ -5118,13 +4790,13 @@
       <x:c r="Z93" s="2"/>
     </x:row>
     <x:row r="94" ht="15.75" customHeight="1">
-      <x:c r="A94" s="2"/>
-      <x:c r="B94" s="2"/>
-      <x:c r="C94" s="2"/>
-      <x:c r="D94" s="2"/>
-      <x:c r="E94" s="2"/>
-      <x:c r="F94" s="2"/>
-      <x:c r="G94" s="2"/>
+      <x:c r="A94"/>
+      <x:c r="B94"/>
+      <x:c r="C94"/>
+      <x:c r="D94"/>
+      <x:c r="E94"/>
+      <x:c r="F94"/>
+      <x:c r="G94"/>
       <x:c r="H94" s="2"/>
       <x:c r="I94" s="2"/>
       <x:c r="J94" s="2"/>
@@ -5146,13 +4818,13 @@
       <x:c r="Z94" s="2"/>
     </x:row>
     <x:row r="95" ht="15.75" customHeight="1">
-      <x:c r="A95" s="2"/>
-      <x:c r="B95" s="2"/>
-      <x:c r="C95" s="2"/>
-      <x:c r="D95" s="2"/>
-      <x:c r="E95" s="2"/>
-      <x:c r="F95" s="2"/>
-      <x:c r="G95" s="2"/>
+      <x:c r="A95"/>
+      <x:c r="B95"/>
+      <x:c r="C95"/>
+      <x:c r="D95"/>
+      <x:c r="E95"/>
+      <x:c r="F95"/>
+      <x:c r="G95"/>
       <x:c r="H95" s="2"/>
       <x:c r="I95" s="2"/>
       <x:c r="J95" s="2"/>
@@ -5174,13 +4846,13 @@
       <x:c r="Z95" s="2"/>
     </x:row>
     <x:row r="96" ht="15.75" customHeight="1">
-      <x:c r="A96" s="2"/>
-      <x:c r="B96" s="2"/>
-      <x:c r="C96" s="2"/>
-      <x:c r="D96" s="2"/>
-      <x:c r="E96" s="2"/>
-      <x:c r="F96" s="2"/>
-      <x:c r="G96" s="2"/>
+      <x:c r="A96"/>
+      <x:c r="B96"/>
+      <x:c r="C96"/>
+      <x:c r="D96"/>
+      <x:c r="E96"/>
+      <x:c r="F96"/>
+      <x:c r="G96"/>
       <x:c r="H96" s="2"/>
       <x:c r="I96" s="2"/>
       <x:c r="J96" s="2"/>
@@ -5202,13 +4874,13 @@
       <x:c r="Z96" s="2"/>
     </x:row>
     <x:row r="97" ht="15.75" customHeight="1">
-      <x:c r="A97" s="2"/>
-      <x:c r="B97" s="2"/>
-      <x:c r="C97" s="2"/>
-      <x:c r="D97" s="2"/>
-      <x:c r="E97" s="2"/>
-      <x:c r="F97" s="2"/>
-      <x:c r="G97" s="2"/>
+      <x:c r="A97"/>
+      <x:c r="B97"/>
+      <x:c r="C97"/>
+      <x:c r="D97"/>
+      <x:c r="E97"/>
+      <x:c r="F97"/>
+      <x:c r="G97"/>
       <x:c r="H97" s="2"/>
       <x:c r="I97" s="2"/>
       <x:c r="J97" s="2"/>
@@ -5230,13 +4902,13 @@
       <x:c r="Z97" s="2"/>
     </x:row>
     <x:row r="98" ht="15.75" customHeight="1">
-      <x:c r="A98" s="2"/>
-      <x:c r="B98" s="2"/>
-      <x:c r="C98" s="2"/>
-      <x:c r="D98" s="2"/>
-      <x:c r="E98" s="2"/>
-      <x:c r="F98" s="2"/>
-      <x:c r="G98" s="2"/>
+      <x:c r="A98"/>
+      <x:c r="B98"/>
+      <x:c r="C98"/>
+      <x:c r="D98"/>
+      <x:c r="E98"/>
+      <x:c r="F98"/>
+      <x:c r="G98"/>
       <x:c r="H98" s="2"/>
       <x:c r="I98" s="2"/>
       <x:c r="J98" s="2"/>
@@ -5258,13 +4930,13 @@
       <x:c r="Z98" s="2"/>
     </x:row>
     <x:row r="99" ht="15.75" customHeight="1">
-      <x:c r="A99" s="2"/>
-      <x:c r="B99" s="2"/>
-      <x:c r="C99" s="2"/>
-      <x:c r="D99" s="2"/>
-      <x:c r="E99" s="2"/>
-      <x:c r="F99" s="2"/>
-      <x:c r="G99" s="2"/>
+      <x:c r="A99"/>
+      <x:c r="B99"/>
+      <x:c r="C99"/>
+      <x:c r="D99"/>
+      <x:c r="E99"/>
+      <x:c r="F99"/>
+      <x:c r="G99"/>
       <x:c r="H99" s="2"/>
       <x:c r="I99" s="2"/>
       <x:c r="J99" s="2"/>
@@ -5286,13 +4958,13 @@
       <x:c r="Z99" s="2"/>
     </x:row>
     <x:row r="100" ht="15.75" customHeight="1">
-      <x:c r="A100" s="2"/>
-      <x:c r="B100" s="2"/>
-      <x:c r="C100" s="2"/>
-      <x:c r="D100" s="2"/>
-      <x:c r="E100" s="2"/>
-      <x:c r="F100" s="2"/>
-      <x:c r="G100" s="2"/>
+      <x:c r="A100"/>
+      <x:c r="B100"/>
+      <x:c r="C100"/>
+      <x:c r="D100"/>
+      <x:c r="E100"/>
+      <x:c r="F100"/>
+      <x:c r="G100"/>
       <x:c r="H100" s="2"/>
       <x:c r="I100" s="2"/>
       <x:c r="J100" s="2"/>
@@ -5314,13 +4986,13 @@
       <x:c r="Z100" s="2"/>
     </x:row>
     <x:row r="101" ht="15.75" customHeight="1">
-      <x:c r="A101" s="2"/>
-      <x:c r="B101" s="2"/>
-      <x:c r="C101" s="2"/>
-      <x:c r="D101" s="2"/>
-      <x:c r="E101" s="2"/>
-      <x:c r="F101" s="2"/>
-      <x:c r="G101" s="2"/>
+      <x:c r="A101"/>
+      <x:c r="B101"/>
+      <x:c r="C101"/>
+      <x:c r="D101"/>
+      <x:c r="E101"/>
+      <x:c r="F101"/>
+      <x:c r="G101"/>
       <x:c r="H101" s="2"/>
       <x:c r="I101" s="2"/>
       <x:c r="J101" s="2"/>
@@ -5342,13 +5014,13 @@
       <x:c r="Z101" s="2"/>
     </x:row>
     <x:row r="102" ht="15.75" customHeight="1">
-      <x:c r="A102" s="2"/>
-      <x:c r="B102" s="2"/>
-      <x:c r="C102" s="2"/>
-      <x:c r="D102" s="2"/>
-      <x:c r="E102" s="2"/>
-      <x:c r="F102" s="2"/>
-      <x:c r="G102" s="2"/>
+      <x:c r="A102"/>
+      <x:c r="B102"/>
+      <x:c r="C102"/>
+      <x:c r="D102"/>
+      <x:c r="E102"/>
+      <x:c r="F102"/>
+      <x:c r="G102"/>
       <x:c r="H102" s="2"/>
       <x:c r="I102" s="2"/>
       <x:c r="J102" s="2"/>
@@ -5370,13 +5042,13 @@
       <x:c r="Z102" s="2"/>
     </x:row>
     <x:row r="103" ht="15.75" customHeight="1">
-      <x:c r="A103" s="2"/>
-      <x:c r="B103" s="2"/>
-      <x:c r="C103" s="2"/>
-      <x:c r="D103" s="2"/>
-      <x:c r="E103" s="2"/>
-      <x:c r="F103" s="2"/>
-      <x:c r="G103" s="2"/>
+      <x:c r="A103"/>
+      <x:c r="B103"/>
+      <x:c r="C103"/>
+      <x:c r="D103"/>
+      <x:c r="E103"/>
+      <x:c r="F103"/>
+      <x:c r="G103"/>
       <x:c r="H103" s="2"/>
       <x:c r="I103" s="2"/>
       <x:c r="J103" s="2"/>
@@ -5398,13 +5070,13 @@
       <x:c r="Z103" s="2"/>
     </x:row>
     <x:row r="104" ht="15.75" customHeight="1">
-      <x:c r="A104" s="2"/>
-      <x:c r="B104" s="2"/>
-      <x:c r="C104" s="2"/>
-      <x:c r="D104" s="2"/>
-      <x:c r="E104" s="2"/>
-      <x:c r="F104" s="2"/>
-      <x:c r="G104" s="2"/>
+      <x:c r="A104"/>
+      <x:c r="B104"/>
+      <x:c r="C104"/>
+      <x:c r="D104"/>
+      <x:c r="E104"/>
+      <x:c r="F104"/>
+      <x:c r="G104"/>
       <x:c r="H104" s="2"/>
       <x:c r="I104" s="2"/>
       <x:c r="J104" s="2"/>
@@ -5426,13 +5098,13 @@
       <x:c r="Z104" s="2"/>
     </x:row>
     <x:row r="105" ht="15.75" customHeight="1">
-      <x:c r="A105" s="2"/>
-      <x:c r="B105" s="2"/>
-      <x:c r="C105" s="2"/>
-      <x:c r="D105" s="2"/>
-      <x:c r="E105" s="2"/>
-      <x:c r="F105" s="2"/>
-      <x:c r="G105" s="2"/>
+      <x:c r="A105"/>
+      <x:c r="B105"/>
+      <x:c r="C105"/>
+      <x:c r="D105"/>
+      <x:c r="E105"/>
+      <x:c r="F105"/>
+      <x:c r="G105"/>
       <x:c r="H105" s="2"/>
       <x:c r="I105" s="2"/>
       <x:c r="J105" s="2"/>
@@ -5454,13 +5126,13 @@
       <x:c r="Z105" s="2"/>
     </x:row>
     <x:row r="106" ht="15.75" customHeight="1">
-      <x:c r="A106" s="2"/>
-      <x:c r="B106" s="2"/>
-      <x:c r="C106" s="2"/>
-      <x:c r="D106" s="2"/>
-      <x:c r="E106" s="2"/>
-      <x:c r="F106" s="2"/>
-      <x:c r="G106" s="2"/>
+      <x:c r="A106"/>
+      <x:c r="B106"/>
+      <x:c r="C106"/>
+      <x:c r="D106"/>
+      <x:c r="E106"/>
+      <x:c r="F106"/>
+      <x:c r="G106"/>
       <x:c r="H106" s="2"/>
       <x:c r="I106" s="2"/>
       <x:c r="J106" s="2"/>
@@ -5482,13 +5154,13 @@
       <x:c r="Z106" s="2"/>
     </x:row>
     <x:row r="107" ht="15.75" customHeight="1">
-      <x:c r="A107" s="2"/>
-      <x:c r="B107" s="2"/>
-      <x:c r="C107" s="2"/>
-      <x:c r="D107" s="2"/>
-      <x:c r="E107" s="2"/>
-      <x:c r="F107" s="2"/>
-      <x:c r="G107" s="2"/>
+      <x:c r="A107"/>
+      <x:c r="B107"/>
+      <x:c r="C107"/>
+      <x:c r="D107"/>
+      <x:c r="E107"/>
+      <x:c r="F107"/>
+      <x:c r="G107"/>
       <x:c r="H107" s="2"/>
       <x:c r="I107" s="2"/>
       <x:c r="J107" s="2"/>
@@ -5510,13 +5182,13 @@
       <x:c r="Z107" s="2"/>
     </x:row>
     <x:row r="108" ht="15.75" customHeight="1">
-      <x:c r="A108" s="2"/>
-      <x:c r="B108" s="2"/>
-      <x:c r="C108" s="2"/>
-      <x:c r="D108" s="2"/>
-      <x:c r="E108" s="2"/>
-      <x:c r="F108" s="2"/>
-      <x:c r="G108" s="2"/>
+      <x:c r="A108"/>
+      <x:c r="B108"/>
+      <x:c r="C108"/>
+      <x:c r="D108"/>
+      <x:c r="E108"/>
+      <x:c r="F108"/>
+      <x:c r="G108"/>
       <x:c r="H108" s="2"/>
       <x:c r="I108" s="2"/>
       <x:c r="J108" s="2"/>
@@ -5538,13 +5210,13 @@
       <x:c r="Z108" s="2"/>
     </x:row>
     <x:row r="109" ht="15.75" customHeight="1">
-      <x:c r="A109" s="2"/>
-      <x:c r="B109" s="2"/>
-      <x:c r="C109" s="2"/>
-      <x:c r="D109" s="2"/>
-      <x:c r="E109" s="2"/>
-      <x:c r="F109" s="2"/>
-      <x:c r="G109" s="2"/>
+      <x:c r="A109"/>
+      <x:c r="B109"/>
+      <x:c r="C109"/>
+      <x:c r="D109"/>
+      <x:c r="E109"/>
+      <x:c r="F109"/>
+      <x:c r="G109"/>
       <x:c r="H109" s="2"/>
       <x:c r="I109" s="2"/>
       <x:c r="J109" s="2"/>
@@ -5566,13 +5238,13 @@
       <x:c r="Z109" s="2"/>
     </x:row>
     <x:row r="110" ht="15.75" customHeight="1">
-      <x:c r="A110" s="2"/>
-      <x:c r="B110" s="2"/>
-      <x:c r="C110" s="2"/>
-      <x:c r="D110" s="2"/>
-      <x:c r="E110" s="2"/>
-      <x:c r="F110" s="2"/>
-      <x:c r="G110" s="2"/>
+      <x:c r="A110"/>
+      <x:c r="B110"/>
+      <x:c r="C110"/>
+      <x:c r="D110"/>
+      <x:c r="E110"/>
+      <x:c r="F110"/>
+      <x:c r="G110"/>
       <x:c r="H110" s="2"/>
       <x:c r="I110" s="2"/>
       <x:c r="J110" s="2"/>
@@ -5594,13 +5266,13 @@
       <x:c r="Z110" s="2"/>
     </x:row>
     <x:row r="111" ht="15.75" customHeight="1">
-      <x:c r="A111" s="2"/>
-      <x:c r="B111" s="2"/>
-      <x:c r="C111" s="2"/>
-      <x:c r="D111" s="2"/>
-      <x:c r="E111" s="2"/>
-      <x:c r="F111" s="2"/>
-      <x:c r="G111" s="2"/>
+      <x:c r="A111"/>
+      <x:c r="B111"/>
+      <x:c r="C111"/>
+      <x:c r="D111"/>
+      <x:c r="E111"/>
+      <x:c r="F111"/>
+      <x:c r="G111"/>
       <x:c r="H111" s="2"/>
       <x:c r="I111" s="2"/>
       <x:c r="J111" s="2"/>
@@ -5622,13 +5294,13 @@
       <x:c r="Z111" s="2"/>
     </x:row>
     <x:row r="112" ht="15.75" customHeight="1">
-      <x:c r="A112" s="2"/>
-      <x:c r="B112" s="2"/>
-      <x:c r="C112" s="2"/>
-      <x:c r="D112" s="2"/>
-      <x:c r="E112" s="2"/>
-      <x:c r="F112" s="2"/>
-      <x:c r="G112" s="2"/>
+      <x:c r="A112"/>
+      <x:c r="B112"/>
+      <x:c r="C112"/>
+      <x:c r="D112"/>
+      <x:c r="E112"/>
+      <x:c r="F112"/>
+      <x:c r="G112"/>
       <x:c r="H112" s="2"/>
       <x:c r="I112" s="2"/>
       <x:c r="J112" s="2"/>
@@ -5650,13 +5322,13 @@
       <x:c r="Z112" s="2"/>
     </x:row>
     <x:row r="113" ht="15.75" customHeight="1">
-      <x:c r="A113" s="2"/>
-      <x:c r="B113" s="2"/>
-      <x:c r="C113" s="2"/>
-      <x:c r="D113" s="2"/>
-      <x:c r="E113" s="2"/>
-      <x:c r="F113" s="2"/>
-      <x:c r="G113" s="2"/>
+      <x:c r="A113"/>
+      <x:c r="B113"/>
+      <x:c r="C113"/>
+      <x:c r="D113"/>
+      <x:c r="E113"/>
+      <x:c r="F113"/>
+      <x:c r="G113"/>
       <x:c r="H113" s="2"/>
       <x:c r="I113" s="2"/>
       <x:c r="J113" s="2"/>
@@ -5678,13 +5350,13 @@
       <x:c r="Z113" s="2"/>
     </x:row>
     <x:row r="114" ht="15.75" customHeight="1">
-      <x:c r="A114" s="2"/>
-      <x:c r="B114" s="2"/>
-      <x:c r="C114" s="2"/>
-      <x:c r="D114" s="2"/>
-      <x:c r="E114" s="2"/>
-      <x:c r="F114" s="2"/>
-      <x:c r="G114" s="2"/>
+      <x:c r="A114"/>
+      <x:c r="B114"/>
+      <x:c r="C114"/>
+      <x:c r="D114"/>
+      <x:c r="E114"/>
+      <x:c r="F114"/>
+      <x:c r="G114"/>
       <x:c r="H114" s="2"/>
       <x:c r="I114" s="2"/>
       <x:c r="J114" s="2"/>
@@ -5706,13 +5378,13 @@
       <x:c r="Z114" s="2"/>
     </x:row>
     <x:row r="115" ht="15.75" customHeight="1">
-      <x:c r="A115" s="2"/>
-      <x:c r="B115" s="2"/>
-      <x:c r="C115" s="2"/>
-      <x:c r="D115" s="2"/>
-      <x:c r="E115" s="2"/>
-      <x:c r="F115" s="2"/>
-      <x:c r="G115" s="2"/>
+      <x:c r="A115"/>
+      <x:c r="B115"/>
+      <x:c r="C115"/>
+      <x:c r="D115"/>
+      <x:c r="E115"/>
+      <x:c r="F115"/>
+      <x:c r="G115"/>
       <x:c r="H115" s="2"/>
       <x:c r="I115" s="2"/>
       <x:c r="J115" s="2"/>
@@ -5734,13 +5406,13 @@
       <x:c r="Z115" s="2"/>
     </x:row>
     <x:row r="116" ht="15.75" customHeight="1">
-      <x:c r="A116" s="2"/>
-      <x:c r="B116" s="2"/>
-      <x:c r="C116" s="2"/>
-      <x:c r="D116" s="2"/>
-      <x:c r="E116" s="2"/>
-      <x:c r="F116" s="2"/>
-      <x:c r="G116" s="2"/>
+      <x:c r="A116"/>
+      <x:c r="B116"/>
+      <x:c r="C116"/>
+      <x:c r="D116"/>
+      <x:c r="E116"/>
+      <x:c r="F116"/>
+      <x:c r="G116"/>
       <x:c r="H116" s="2"/>
       <x:c r="I116" s="2"/>
       <x:c r="J116" s="2"/>
@@ -5762,13 +5434,13 @@
       <x:c r="Z116" s="2"/>
     </x:row>
     <x:row r="117" ht="15.75" customHeight="1">
-      <x:c r="A117" s="2"/>
-      <x:c r="B117" s="2"/>
-      <x:c r="C117" s="2"/>
-      <x:c r="D117" s="2"/>
-      <x:c r="E117" s="2"/>
-      <x:c r="F117" s="2"/>
-      <x:c r="G117" s="2"/>
+      <x:c r="A117"/>
+      <x:c r="B117"/>
+      <x:c r="C117"/>
+      <x:c r="D117"/>
+      <x:c r="E117"/>
+      <x:c r="F117"/>
+      <x:c r="G117"/>
       <x:c r="H117" s="2"/>
       <x:c r="I117" s="2"/>
       <x:c r="J117" s="2"/>
@@ -5790,13 +5462,13 @@
       <x:c r="Z117" s="2"/>
     </x:row>
     <x:row r="118" ht="15.75" customHeight="1">
-      <x:c r="A118" s="2"/>
-      <x:c r="B118" s="2"/>
-      <x:c r="C118" s="2"/>
-      <x:c r="D118" s="2"/>
-      <x:c r="E118" s="2"/>
-      <x:c r="F118" s="2"/>
-      <x:c r="G118" s="2"/>
+      <x:c r="A118"/>
+      <x:c r="B118"/>
+      <x:c r="C118"/>
+      <x:c r="D118"/>
+      <x:c r="E118"/>
+      <x:c r="F118"/>
+      <x:c r="G118"/>
       <x:c r="H118" s="2"/>
       <x:c r="I118" s="2"/>
       <x:c r="J118" s="2"/>
@@ -5818,13 +5490,13 @@
       <x:c r="Z118" s="2"/>
     </x:row>
     <x:row r="119" ht="15.75" customHeight="1">
-      <x:c r="A119" s="2"/>
-      <x:c r="B119" s="2"/>
-      <x:c r="C119" s="2"/>
-      <x:c r="D119" s="2"/>
-      <x:c r="E119" s="2"/>
-      <x:c r="F119" s="2"/>
-      <x:c r="G119" s="2"/>
+      <x:c r="A119"/>
+      <x:c r="B119"/>
+      <x:c r="C119"/>
+      <x:c r="D119"/>
+      <x:c r="E119"/>
+      <x:c r="F119"/>
+      <x:c r="G119"/>
       <x:c r="H119" s="2"/>
       <x:c r="I119" s="2"/>
       <x:c r="J119" s="2"/>
@@ -5846,13 +5518,13 @@
       <x:c r="Z119" s="2"/>
     </x:row>
     <x:row r="120" ht="15.75" customHeight="1">
-      <x:c r="A120" s="2"/>
-      <x:c r="B120" s="2"/>
-      <x:c r="C120" s="2"/>
-      <x:c r="D120" s="2"/>
-      <x:c r="E120" s="2"/>
-      <x:c r="F120" s="2"/>
-      <x:c r="G120" s="2"/>
+      <x:c r="A120"/>
+      <x:c r="B120"/>
+      <x:c r="C120"/>
+      <x:c r="D120"/>
+      <x:c r="E120"/>
+      <x:c r="F120"/>
+      <x:c r="G120"/>
       <x:c r="H120" s="2"/>
       <x:c r="I120" s="2"/>
       <x:c r="J120" s="2"/>
@@ -5874,13 +5546,13 @@
       <x:c r="Z120" s="2"/>
     </x:row>
     <x:row r="121" ht="15.75" customHeight="1">
-      <x:c r="A121" s="2"/>
-      <x:c r="B121" s="2"/>
-      <x:c r="C121" s="2"/>
-      <x:c r="D121" s="2"/>
-      <x:c r="E121" s="2"/>
-      <x:c r="F121" s="2"/>
-      <x:c r="G121" s="2"/>
+      <x:c r="A121"/>
+      <x:c r="B121"/>
+      <x:c r="C121"/>
+      <x:c r="D121"/>
+      <x:c r="E121"/>
+      <x:c r="F121"/>
+      <x:c r="G121"/>
       <x:c r="H121" s="2"/>
       <x:c r="I121" s="2"/>
       <x:c r="J121" s="2"/>
@@ -5902,13 +5574,13 @@
       <x:c r="Z121" s="2"/>
     </x:row>
     <x:row r="122" ht="15.75" customHeight="1">
-      <x:c r="A122" s="2"/>
-      <x:c r="B122" s="2"/>
-      <x:c r="C122" s="2"/>
-      <x:c r="D122" s="2"/>
-      <x:c r="E122" s="2"/>
-      <x:c r="F122" s="2"/>
-      <x:c r="G122" s="2"/>
+      <x:c r="A122"/>
+      <x:c r="B122"/>
+      <x:c r="C122"/>
+      <x:c r="D122"/>
+      <x:c r="E122"/>
+      <x:c r="F122"/>
+      <x:c r="G122"/>
       <x:c r="H122" s="2"/>
       <x:c r="I122" s="2"/>
       <x:c r="J122" s="2"/>
@@ -5930,13 +5602,13 @@
       <x:c r="Z122" s="2"/>
     </x:row>
     <x:row r="123" ht="15.75" customHeight="1">
-      <x:c r="A123" s="2"/>
-      <x:c r="B123" s="2"/>
-      <x:c r="C123" s="2"/>
-      <x:c r="D123" s="2"/>
-      <x:c r="E123" s="2"/>
-      <x:c r="F123" s="2"/>
-      <x:c r="G123" s="2"/>
+      <x:c r="A123"/>
+      <x:c r="B123"/>
+      <x:c r="C123"/>
+      <x:c r="D123"/>
+      <x:c r="E123"/>
+      <x:c r="F123"/>
+      <x:c r="G123"/>
       <x:c r="H123" s="2"/>
       <x:c r="I123" s="2"/>
       <x:c r="J123" s="2"/>
@@ -5958,13 +5630,13 @@
       <x:c r="Z123" s="2"/>
     </x:row>
     <x:row r="124" ht="15.75" customHeight="1">
-      <x:c r="A124" s="2"/>
-      <x:c r="B124" s="2"/>
-      <x:c r="C124" s="2"/>
-      <x:c r="D124" s="2"/>
-      <x:c r="E124" s="2"/>
-      <x:c r="F124" s="2"/>
-      <x:c r="G124" s="2"/>
+      <x:c r="A124"/>
+      <x:c r="B124"/>
+      <x:c r="C124"/>
+      <x:c r="D124"/>
+      <x:c r="E124"/>
+      <x:c r="F124"/>
+      <x:c r="G124"/>
       <x:c r="H124" s="2"/>
       <x:c r="I124" s="2"/>
       <x:c r="J124" s="2"/>
@@ -5986,13 +5658,13 @@
       <x:c r="Z124" s="2"/>
     </x:row>
     <x:row r="125" ht="15.75" customHeight="1">
-      <x:c r="A125" s="2"/>
-      <x:c r="B125" s="2"/>
-      <x:c r="C125" s="2"/>
-      <x:c r="D125" s="2"/>
-      <x:c r="E125" s="2"/>
-      <x:c r="F125" s="2"/>
-      <x:c r="G125" s="2"/>
+      <x:c r="A125"/>
+      <x:c r="B125"/>
+      <x:c r="C125"/>
+      <x:c r="D125"/>
+      <x:c r="E125"/>
+      <x:c r="F125"/>
+      <x:c r="G125"/>
       <x:c r="H125" s="2"/>
       <x:c r="I125" s="2"/>
       <x:c r="J125" s="2"/>
@@ -6014,13 +5686,13 @@
       <x:c r="Z125" s="2"/>
     </x:row>
     <x:row r="126" ht="15.75" customHeight="1">
-      <x:c r="A126" s="2"/>
-      <x:c r="B126" s="2"/>
-      <x:c r="C126" s="2"/>
-      <x:c r="D126" s="2"/>
-      <x:c r="E126" s="2"/>
-      <x:c r="F126" s="2"/>
-      <x:c r="G126" s="2"/>
+      <x:c r="A126"/>
+      <x:c r="B126"/>
+      <x:c r="C126"/>
+      <x:c r="D126"/>
+      <x:c r="E126"/>
+      <x:c r="F126"/>
+      <x:c r="G126"/>
       <x:c r="H126" s="2"/>
       <x:c r="I126" s="2"/>
       <x:c r="J126" s="2"/>
@@ -6042,13 +5714,13 @@
       <x:c r="Z126" s="2"/>
     </x:row>
     <x:row r="127" ht="15.75" customHeight="1">
-      <x:c r="A127" s="2"/>
-      <x:c r="B127" s="2"/>
-      <x:c r="C127" s="2"/>
-      <x:c r="D127" s="2"/>
-      <x:c r="E127" s="2"/>
-      <x:c r="F127" s="2"/>
-      <x:c r="G127" s="2"/>
+      <x:c r="A127"/>
+      <x:c r="B127"/>
+      <x:c r="C127"/>
+      <x:c r="D127"/>
+      <x:c r="E127"/>
+      <x:c r="F127"/>
+      <x:c r="G127"/>
       <x:c r="H127" s="2"/>
       <x:c r="I127" s="2"/>
       <x:c r="J127" s="2"/>
@@ -6070,13 +5742,13 @@
       <x:c r="Z127" s="2"/>
     </x:row>
     <x:row r="128" ht="15.75" customHeight="1">
-      <x:c r="A128" s="2"/>
-      <x:c r="B128" s="2"/>
-      <x:c r="C128" s="2"/>
-      <x:c r="D128" s="2"/>
-      <x:c r="E128" s="2"/>
-      <x:c r="F128" s="2"/>
-      <x:c r="G128" s="2"/>
+      <x:c r="A128"/>
+      <x:c r="B128"/>
+      <x:c r="C128"/>
+      <x:c r="D128"/>
+      <x:c r="E128"/>
+      <x:c r="F128"/>
+      <x:c r="G128"/>
       <x:c r="H128" s="2"/>
       <x:c r="I128" s="2"/>
       <x:c r="J128" s="2"/>
@@ -6098,13 +5770,13 @@
       <x:c r="Z128" s="2"/>
     </x:row>
     <x:row r="129" ht="15.75" customHeight="1">
-      <x:c r="A129" s="2"/>
-      <x:c r="B129" s="2"/>
-      <x:c r="C129" s="2"/>
-      <x:c r="D129" s="2"/>
-      <x:c r="E129" s="2"/>
-      <x:c r="F129" s="2"/>
-      <x:c r="G129" s="2"/>
+      <x:c r="A129"/>
+      <x:c r="B129"/>
+      <x:c r="C129"/>
+      <x:c r="D129"/>
+      <x:c r="E129"/>
+      <x:c r="F129"/>
+      <x:c r="G129"/>
       <x:c r="H129" s="2"/>
       <x:c r="I129" s="2"/>
       <x:c r="J129" s="2"/>
@@ -6126,13 +5798,13 @@
       <x:c r="Z129" s="2"/>
     </x:row>
     <x:row r="130" ht="15.75" customHeight="1">
-      <x:c r="A130" s="2"/>
-      <x:c r="B130" s="2"/>
-      <x:c r="C130" s="2"/>
-      <x:c r="D130" s="2"/>
-      <x:c r="E130" s="2"/>
-      <x:c r="F130" s="2"/>
-      <x:c r="G130" s="2"/>
+      <x:c r="A130"/>
+      <x:c r="B130"/>
+      <x:c r="C130"/>
+      <x:c r="D130"/>
+      <x:c r="E130"/>
+      <x:c r="F130"/>
+      <x:c r="G130"/>
       <x:c r="H130" s="2"/>
       <x:c r="I130" s="2"/>
       <x:c r="J130" s="2"/>
@@ -6154,13 +5826,13 @@
       <x:c r="Z130" s="2"/>
     </x:row>
     <x:row r="131" ht="15.75" customHeight="1">
-      <x:c r="A131" s="2"/>
-      <x:c r="B131" s="2"/>
-      <x:c r="C131" s="2"/>
-      <x:c r="D131" s="2"/>
-      <x:c r="E131" s="2"/>
-      <x:c r="F131" s="2"/>
-      <x:c r="G131" s="2"/>
+      <x:c r="A131"/>
+      <x:c r="B131"/>
+      <x:c r="C131"/>
+      <x:c r="D131"/>
+      <x:c r="E131"/>
+      <x:c r="F131"/>
+      <x:c r="G131"/>
       <x:c r="H131" s="2"/>
       <x:c r="I131" s="2"/>
       <x:c r="J131" s="2"/>
@@ -6182,13 +5854,13 @@
       <x:c r="Z131" s="2"/>
     </x:row>
     <x:row r="132" ht="15.75" customHeight="1">
-      <x:c r="A132" s="2"/>
-      <x:c r="B132" s="2"/>
-      <x:c r="C132" s="2"/>
-      <x:c r="D132" s="2"/>
-      <x:c r="E132" s="2"/>
-      <x:c r="F132" s="2"/>
-      <x:c r="G132" s="2"/>
+      <x:c r="A132"/>
+      <x:c r="B132"/>
+      <x:c r="C132"/>
+      <x:c r="D132"/>
+      <x:c r="E132"/>
+      <x:c r="F132"/>
+      <x:c r="G132"/>
       <x:c r="H132" s="2"/>
       <x:c r="I132" s="2"/>
       <x:c r="J132" s="2"/>
@@ -6210,13 +5882,13 @@
       <x:c r="Z132" s="2"/>
     </x:row>
     <x:row r="133" ht="15.75" customHeight="1">
-      <x:c r="A133" s="2"/>
-      <x:c r="B133" s="2"/>
-      <x:c r="C133" s="2"/>
-      <x:c r="D133" s="2"/>
-      <x:c r="E133" s="2"/>
-      <x:c r="F133" s="2"/>
-      <x:c r="G133" s="2"/>
+      <x:c r="A133"/>
+      <x:c r="B133"/>
+      <x:c r="C133"/>
+      <x:c r="D133"/>
+      <x:c r="E133"/>
+      <x:c r="F133"/>
+      <x:c r="G133"/>
       <x:c r="H133" s="2"/>
       <x:c r="I133" s="2"/>
       <x:c r="J133" s="2"/>
@@ -6238,13 +5910,13 @@
       <x:c r="Z133" s="2"/>
     </x:row>
     <x:row r="134" ht="15.75" customHeight="1">
-      <x:c r="A134" s="2"/>
-      <x:c r="B134" s="2"/>
-      <x:c r="C134" s="2"/>
-      <x:c r="D134" s="2"/>
-      <x:c r="E134" s="2"/>
-      <x:c r="F134" s="2"/>
-      <x:c r="G134" s="2"/>
+      <x:c r="A134"/>
+      <x:c r="B134"/>
+      <x:c r="C134"/>
+      <x:c r="D134"/>
+      <x:c r="E134"/>
+      <x:c r="F134"/>
+      <x:c r="G134"/>
       <x:c r="H134" s="2"/>
       <x:c r="I134" s="2"/>
       <x:c r="J134" s="2"/>
@@ -6266,13 +5938,13 @@
       <x:c r="Z134" s="2"/>
     </x:row>
     <x:row r="135" ht="15.75" customHeight="1">
-      <x:c r="A135" s="2"/>
-      <x:c r="B135" s="2"/>
-      <x:c r="C135" s="2"/>
-      <x:c r="D135" s="2"/>
-      <x:c r="E135" s="2"/>
-      <x:c r="F135" s="2"/>
-      <x:c r="G135" s="2"/>
+      <x:c r="A135"/>
+      <x:c r="B135"/>
+      <x:c r="C135"/>
+      <x:c r="D135"/>
+      <x:c r="E135"/>
+      <x:c r="F135"/>
+      <x:c r="G135"/>
       <x:c r="H135" s="2"/>
       <x:c r="I135" s="2"/>
       <x:c r="J135" s="2"/>
@@ -6294,13 +5966,13 @@
       <x:c r="Z135" s="2"/>
     </x:row>
     <x:row r="136" ht="15.75" customHeight="1">
-      <x:c r="A136" s="2"/>
-      <x:c r="B136" s="2"/>
-      <x:c r="C136" s="2"/>
-      <x:c r="D136" s="2"/>
-      <x:c r="E136" s="2"/>
-      <x:c r="F136" s="2"/>
-      <x:c r="G136" s="2"/>
+      <x:c r="A136"/>
+      <x:c r="B136"/>
+      <x:c r="C136"/>
+      <x:c r="D136"/>
+      <x:c r="E136"/>
+      <x:c r="F136"/>
+      <x:c r="G136"/>
       <x:c r="H136" s="2"/>
       <x:c r="I136" s="2"/>
       <x:c r="J136" s="2"/>
@@ -6322,13 +5994,13 @@
       <x:c r="Z136" s="2"/>
     </x:row>
     <x:row r="137" ht="15.75" customHeight="1">
-      <x:c r="A137" s="2"/>
-      <x:c r="B137" s="2"/>
-      <x:c r="C137" s="2"/>
-      <x:c r="D137" s="2"/>
-      <x:c r="E137" s="2"/>
-      <x:c r="F137" s="2"/>
-      <x:c r="G137" s="2"/>
+      <x:c r="A137"/>
+      <x:c r="B137"/>
+      <x:c r="C137"/>
+      <x:c r="D137"/>
+      <x:c r="E137"/>
+      <x:c r="F137"/>
+      <x:c r="G137"/>
       <x:c r="H137" s="2"/>
       <x:c r="I137" s="2"/>
       <x:c r="J137" s="2"/>
@@ -6350,13 +6022,13 @@
       <x:c r="Z137" s="2"/>
     </x:row>
     <x:row r="138" ht="15.75" customHeight="1">
-      <x:c r="A138" s="2"/>
-      <x:c r="B138" s="2"/>
-      <x:c r="C138" s="2"/>
-      <x:c r="D138" s="2"/>
-      <x:c r="E138" s="2"/>
-      <x:c r="F138" s="2"/>
-      <x:c r="G138" s="2"/>
+      <x:c r="A138"/>
+      <x:c r="B138"/>
+      <x:c r="C138"/>
+      <x:c r="D138"/>
+      <x:c r="E138"/>
+      <x:c r="F138"/>
+      <x:c r="G138"/>
       <x:c r="H138" s="2"/>
       <x:c r="I138" s="2"/>
       <x:c r="J138" s="2"/>
@@ -6378,13 +6050,13 @@
       <x:c r="Z138" s="2"/>
     </x:row>
     <x:row r="139" ht="15.75" customHeight="1">
-      <x:c r="A139" s="2"/>
-      <x:c r="B139" s="2"/>
-      <x:c r="C139" s="2"/>
-      <x:c r="D139" s="2"/>
-      <x:c r="E139" s="2"/>
-      <x:c r="F139" s="2"/>
-      <x:c r="G139" s="2"/>
+      <x:c r="A139"/>
+      <x:c r="B139"/>
+      <x:c r="C139"/>
+      <x:c r="D139"/>
+      <x:c r="E139"/>
+      <x:c r="F139"/>
+      <x:c r="G139"/>
       <x:c r="H139" s="2"/>
       <x:c r="I139" s="2"/>
       <x:c r="J139" s="2"/>
@@ -6406,13 +6078,13 @@
       <x:c r="Z139" s="2"/>
     </x:row>
     <x:row r="140" ht="15.75" customHeight="1">
-      <x:c r="A140" s="2"/>
-      <x:c r="B140" s="2"/>
-      <x:c r="C140" s="2"/>
-      <x:c r="D140" s="2"/>
-      <x:c r="E140" s="2"/>
-      <x:c r="F140" s="2"/>
-      <x:c r="G140" s="2"/>
+      <x:c r="A140"/>
+      <x:c r="B140"/>
+      <x:c r="C140"/>
+      <x:c r="D140"/>
+      <x:c r="E140"/>
+      <x:c r="F140"/>
+      <x:c r="G140"/>
       <x:c r="H140" s="2"/>
       <x:c r="I140" s="2"/>
       <x:c r="J140" s="2"/>
@@ -6434,13 +6106,13 @@
       <x:c r="Z140" s="2"/>
     </x:row>
     <x:row r="141" ht="15.75" customHeight="1">
-      <x:c r="A141" s="2"/>
-      <x:c r="B141" s="2"/>
-      <x:c r="C141" s="2"/>
-      <x:c r="D141" s="2"/>
-      <x:c r="E141" s="2"/>
-      <x:c r="F141" s="2"/>
-      <x:c r="G141" s="2"/>
+      <x:c r="A141"/>
+      <x:c r="B141"/>
+      <x:c r="C141"/>
+      <x:c r="D141"/>
+      <x:c r="E141"/>
+      <x:c r="F141"/>
+      <x:c r="G141"/>
       <x:c r="H141" s="2"/>
       <x:c r="I141" s="2"/>
       <x:c r="J141" s="2"/>
@@ -6462,13 +6134,13 @@
       <x:c r="Z141" s="2"/>
     </x:row>
     <x:row r="142" ht="15.75" customHeight="1">
-      <x:c r="A142" s="2"/>
-      <x:c r="B142" s="2"/>
-      <x:c r="C142" s="2"/>
-      <x:c r="D142" s="2"/>
-      <x:c r="E142" s="2"/>
-      <x:c r="F142" s="2"/>
-      <x:c r="G142" s="2"/>
+      <x:c r="A142"/>
+      <x:c r="B142"/>
+      <x:c r="C142"/>
+      <x:c r="D142"/>
+      <x:c r="E142"/>
+      <x:c r="F142"/>
+      <x:c r="G142"/>
       <x:c r="H142" s="2"/>
       <x:c r="I142" s="2"/>
       <x:c r="J142" s="2"/>
@@ -6490,13 +6162,13 @@
       <x:c r="Z142" s="2"/>
     </x:row>
     <x:row r="143" ht="15.75" customHeight="1">
-      <x:c r="A143" s="2"/>
-      <x:c r="B143" s="2"/>
-      <x:c r="C143" s="2"/>
-      <x:c r="D143" s="2"/>
-      <x:c r="E143" s="2"/>
-      <x:c r="F143" s="2"/>
-      <x:c r="G143" s="2"/>
+      <x:c r="A143"/>
+      <x:c r="B143"/>
+      <x:c r="C143"/>
+      <x:c r="D143"/>
+      <x:c r="E143"/>
+      <x:c r="F143"/>
+      <x:c r="G143"/>
       <x:c r="H143" s="2"/>
       <x:c r="I143" s="2"/>
       <x:c r="J143" s="2"/>
@@ -6518,13 +6190,13 @@
       <x:c r="Z143" s="2"/>
     </x:row>
     <x:row r="144" ht="15.75" customHeight="1">
-      <x:c r="A144" s="2"/>
-      <x:c r="B144" s="2"/>
-      <x:c r="C144" s="2"/>
-      <x:c r="D144" s="2"/>
-      <x:c r="E144" s="2"/>
-      <x:c r="F144" s="2"/>
-      <x:c r="G144" s="2"/>
+      <x:c r="A144"/>
+      <x:c r="B144"/>
+      <x:c r="C144"/>
+      <x:c r="D144"/>
+      <x:c r="E144"/>
+      <x:c r="F144"/>
+      <x:c r="G144"/>
       <x:c r="H144" s="2"/>
       <x:c r="I144" s="2"/>
       <x:c r="J144" s="2"/>
@@ -6546,13 +6218,13 @@
       <x:c r="Z144" s="2"/>
     </x:row>
     <x:row r="145" ht="15.75" customHeight="1">
-      <x:c r="A145" s="2"/>
-      <x:c r="B145" s="2"/>
-      <x:c r="C145" s="2"/>
-      <x:c r="D145" s="2"/>
-      <x:c r="E145" s="2"/>
-      <x:c r="F145" s="2"/>
-      <x:c r="G145" s="2"/>
+      <x:c r="A145"/>
+      <x:c r="B145"/>
+      <x:c r="C145"/>
+      <x:c r="D145"/>
+      <x:c r="E145"/>
+      <x:c r="F145"/>
+      <x:c r="G145"/>
       <x:c r="H145" s="2"/>
       <x:c r="I145" s="2"/>
       <x:c r="J145" s="2"/>
@@ -6574,13 +6246,13 @@
       <x:c r="Z145" s="2"/>
     </x:row>
     <x:row r="146" ht="15.75" customHeight="1">
-      <x:c r="A146" s="2"/>
-      <x:c r="B146" s="2"/>
-      <x:c r="C146" s="2"/>
-      <x:c r="D146" s="2"/>
-      <x:c r="E146" s="2"/>
-      <x:c r="F146" s="2"/>
-      <x:c r="G146" s="2"/>
+      <x:c r="A146"/>
+      <x:c r="B146"/>
+      <x:c r="C146"/>
+      <x:c r="D146"/>
+      <x:c r="E146"/>
+      <x:c r="F146"/>
+      <x:c r="G146"/>
       <x:c r="H146" s="2"/>
       <x:c r="I146" s="2"/>
       <x:c r="J146" s="2"/>
@@ -6602,13 +6274,13 @@
       <x:c r="Z146" s="2"/>
     </x:row>
     <x:row r="147" ht="15.75" customHeight="1">
-      <x:c r="A147" s="2"/>
-      <x:c r="B147" s="2"/>
-      <x:c r="C147" s="2"/>
-      <x:c r="D147" s="2"/>
-      <x:c r="E147" s="2"/>
-      <x:c r="F147" s="2"/>
-      <x:c r="G147" s="2"/>
+      <x:c r="A147"/>
+      <x:c r="B147"/>
+      <x:c r="C147"/>
+      <x:c r="D147"/>
+      <x:c r="E147"/>
+      <x:c r="F147"/>
+      <x:c r="G147"/>
       <x:c r="H147" s="2"/>
       <x:c r="I147" s="2"/>
       <x:c r="J147" s="2"/>
@@ -6630,13 +6302,13 @@
       <x:c r="Z147" s="2"/>
     </x:row>
     <x:row r="148" ht="15.75" customHeight="1">
-      <x:c r="A148" s="2"/>
-      <x:c r="B148" s="2"/>
-      <x:c r="C148" s="2"/>
-      <x:c r="D148" s="2"/>
-      <x:c r="E148" s="2"/>
-      <x:c r="F148" s="2"/>
-      <x:c r="G148" s="2"/>
+      <x:c r="A148"/>
+      <x:c r="B148"/>
+      <x:c r="C148"/>
+      <x:c r="D148"/>
+      <x:c r="E148"/>
+      <x:c r="F148"/>
+      <x:c r="G148"/>
       <x:c r="H148" s="2"/>
       <x:c r="I148" s="2"/>
       <x:c r="J148" s="2"/>
@@ -6658,13 +6330,13 @@
       <x:c r="Z148" s="2"/>
     </x:row>
     <x:row r="149" ht="15.75" customHeight="1">
-      <x:c r="A149" s="2"/>
-      <x:c r="B149" s="2"/>
-      <x:c r="C149" s="2"/>
-      <x:c r="D149" s="2"/>
-      <x:c r="E149" s="2"/>
-      <x:c r="F149" s="2"/>
-      <x:c r="G149" s="2"/>
+      <x:c r="A149"/>
+      <x:c r="B149"/>
+      <x:c r="C149"/>
+      <x:c r="D149"/>
+      <x:c r="E149"/>
+      <x:c r="F149"/>
+      <x:c r="G149"/>
       <x:c r="H149" s="2"/>
       <x:c r="I149" s="2"/>
       <x:c r="J149" s="2"/>
@@ -6686,13 +6358,13 @@
       <x:c r="Z149" s="2"/>
     </x:row>
     <x:row r="150" ht="15.75" customHeight="1">
-      <x:c r="A150" s="2"/>
-      <x:c r="B150" s="2"/>
-      <x:c r="C150" s="2"/>
-      <x:c r="D150" s="2"/>
-      <x:c r="E150" s="2"/>
-      <x:c r="F150" s="2"/>
-      <x:c r="G150" s="2"/>
+      <x:c r="A150"/>
+      <x:c r="B150"/>
+      <x:c r="C150"/>
+      <x:c r="D150"/>
+      <x:c r="E150"/>
+      <x:c r="F150"/>
+      <x:c r="G150"/>
       <x:c r="H150" s="2"/>
       <x:c r="I150" s="2"/>
       <x:c r="J150" s="2"/>
@@ -6714,13 +6386,13 @@
       <x:c r="Z150" s="2"/>
     </x:row>
     <x:row r="151" ht="15.75" customHeight="1">
-      <x:c r="A151" s="2"/>
-      <x:c r="B151" s="2"/>
-      <x:c r="C151" s="2"/>
-      <x:c r="D151" s="2"/>
-      <x:c r="E151" s="2"/>
-      <x:c r="F151" s="2"/>
-      <x:c r="G151" s="2"/>
+      <x:c r="A151"/>
+      <x:c r="B151"/>
+      <x:c r="C151"/>
+      <x:c r="D151"/>
+      <x:c r="E151"/>
+      <x:c r="F151"/>
+      <x:c r="G151"/>
       <x:c r="H151" s="2"/>
       <x:c r="I151" s="2"/>
       <x:c r="J151" s="2"/>
@@ -6742,13 +6414,13 @@
       <x:c r="Z151" s="2"/>
     </x:row>
     <x:row r="152" ht="15.75" customHeight="1">
-      <x:c r="A152" s="2"/>
-      <x:c r="B152" s="2"/>
-      <x:c r="C152" s="2"/>
-      <x:c r="D152" s="2"/>
-      <x:c r="E152" s="2"/>
-      <x:c r="F152" s="2"/>
-      <x:c r="G152" s="2"/>
+      <x:c r="A152"/>
+      <x:c r="B152"/>
+      <x:c r="C152"/>
+      <x:c r="D152"/>
+      <x:c r="E152"/>
+      <x:c r="F152"/>
+      <x:c r="G152"/>
       <x:c r="H152" s="2"/>
       <x:c r="I152" s="2"/>
       <x:c r="J152" s="2"/>
@@ -6770,13 +6442,13 @@
       <x:c r="Z152" s="2"/>
     </x:row>
     <x:row r="153" ht="15.75" customHeight="1">
-      <x:c r="A153" s="2"/>
-      <x:c r="B153" s="2"/>
-      <x:c r="C153" s="2"/>
-      <x:c r="D153" s="2"/>
-      <x:c r="E153" s="2"/>
-      <x:c r="F153" s="2"/>
-      <x:c r="G153" s="2"/>
+      <x:c r="A153"/>
+      <x:c r="B153"/>
+      <x:c r="C153"/>
+      <x:c r="D153"/>
+      <x:c r="E153"/>
+      <x:c r="F153"/>
+      <x:c r="G153"/>
       <x:c r="H153" s="2"/>
       <x:c r="I153" s="2"/>
       <x:c r="J153" s="2"/>
@@ -6798,13 +6470,13 @@
       <x:c r="Z153" s="2"/>
     </x:row>
     <x:row r="154" ht="15.75" customHeight="1">
-      <x:c r="A154" s="2"/>
-      <x:c r="B154" s="2"/>
-      <x:c r="C154" s="2"/>
-      <x:c r="D154" s="2"/>
-      <x:c r="E154" s="2"/>
-      <x:c r="F154" s="2"/>
-      <x:c r="G154" s="2"/>
+      <x:c r="A154"/>
+      <x:c r="B154"/>
+      <x:c r="C154"/>
+      <x:c r="D154"/>
+      <x:c r="E154"/>
+      <x:c r="F154"/>
+      <x:c r="G154"/>
       <x:c r="H154" s="2"/>
       <x:c r="I154" s="2"/>
       <x:c r="J154" s="2"/>
@@ -6826,13 +6498,13 @@
       <x:c r="Z154" s="2"/>
     </x:row>
     <x:row r="155" ht="15.75" customHeight="1">
-      <x:c r="A155" s="2"/>
-      <x:c r="B155" s="2"/>
-      <x:c r="C155" s="2"/>
-      <x:c r="D155" s="2"/>
-      <x:c r="E155" s="2"/>
-      <x:c r="F155" s="2"/>
-      <x:c r="G155" s="2"/>
+      <x:c r="A155"/>
+      <x:c r="B155"/>
+      <x:c r="C155"/>
+      <x:c r="D155"/>
+      <x:c r="E155"/>
+      <x:c r="F155"/>
+      <x:c r="G155"/>
       <x:c r="H155" s="2"/>
       <x:c r="I155" s="2"/>
       <x:c r="J155" s="2"/>
@@ -6854,13 +6526,13 @@
       <x:c r="Z155" s="2"/>
     </x:row>
     <x:row r="156" ht="15.75" customHeight="1">
-      <x:c r="A156" s="2"/>
-      <x:c r="B156" s="2"/>
-      <x:c r="C156" s="2"/>
-      <x:c r="D156" s="2"/>
-      <x:c r="E156" s="2"/>
-      <x:c r="F156" s="2"/>
-      <x:c r="G156" s="2"/>
+      <x:c r="A156"/>
+      <x:c r="B156"/>
+      <x:c r="C156"/>
+      <x:c r="D156"/>
+      <x:c r="E156"/>
+      <x:c r="F156"/>
+      <x:c r="G156"/>
       <x:c r="H156" s="2"/>
       <x:c r="I156" s="2"/>
       <x:c r="J156" s="2"/>
@@ -6882,13 +6554,13 @@
       <x:c r="Z156" s="2"/>
     </x:row>
     <x:row r="157" ht="15.75" customHeight="1">
-      <x:c r="A157" s="2"/>
-      <x:c r="B157" s="2"/>
-      <x:c r="C157" s="2"/>
-      <x:c r="D157" s="2"/>
-      <x:c r="E157" s="2"/>
-      <x:c r="F157" s="2"/>
-      <x:c r="G157" s="2"/>
+      <x:c r="A157"/>
+      <x:c r="B157"/>
+      <x:c r="C157"/>
+      <x:c r="D157"/>
+      <x:c r="E157"/>
+      <x:c r="F157"/>
+      <x:c r="G157"/>
       <x:c r="H157" s="2"/>
       <x:c r="I157" s="2"/>
       <x:c r="J157" s="2"/>
@@ -6910,13 +6582,13 @@
       <x:c r="Z157" s="2"/>
     </x:row>
     <x:row r="158" ht="15.75" customHeight="1">
-      <x:c r="A158" s="2"/>
-      <x:c r="B158" s="2"/>
-      <x:c r="C158" s="2"/>
-      <x:c r="D158" s="2"/>
-      <x:c r="E158" s="2"/>
-      <x:c r="F158" s="2"/>
-      <x:c r="G158" s="2"/>
+      <x:c r="A158"/>
+      <x:c r="B158"/>
+      <x:c r="C158"/>
+      <x:c r="D158"/>
+      <x:c r="E158"/>
+      <x:c r="F158"/>
+      <x:c r="G158"/>
       <x:c r="H158" s="2"/>
       <x:c r="I158" s="2"/>
       <x:c r="J158" s="2"/>
@@ -6938,13 +6610,13 @@
       <x:c r="Z158" s="2"/>
     </x:row>
     <x:row r="159" ht="15.75" customHeight="1">
-      <x:c r="A159" s="2"/>
-      <x:c r="B159" s="2"/>
-      <x:c r="C159" s="2"/>
-      <x:c r="D159" s="2"/>
-      <x:c r="E159" s="2"/>
-      <x:c r="F159" s="2"/>
-      <x:c r="G159" s="2"/>
+      <x:c r="A159"/>
+      <x:c r="B159"/>
+      <x:c r="C159"/>
+      <x:c r="D159"/>
+      <x:c r="E159"/>
+      <x:c r="F159"/>
+      <x:c r="G159"/>
       <x:c r="H159" s="2"/>
       <x:c r="I159" s="2"/>
       <x:c r="J159" s="2"/>
@@ -6966,13 +6638,13 @@
       <x:c r="Z159" s="2"/>
     </x:row>
     <x:row r="160" ht="15.75" customHeight="1">
-      <x:c r="A160" s="2"/>
-      <x:c r="B160" s="2"/>
-      <x:c r="C160" s="2"/>
-      <x:c r="D160" s="2"/>
-      <x:c r="E160" s="2"/>
-      <x:c r="F160" s="2"/>
-      <x:c r="G160" s="2"/>
+      <x:c r="A160"/>
+      <x:c r="B160"/>
+      <x:c r="C160"/>
+      <x:c r="D160"/>
+      <x:c r="E160"/>
+      <x:c r="F160"/>
+      <x:c r="G160"/>
       <x:c r="H160" s="2"/>
       <x:c r="I160" s="2"/>
       <x:c r="J160" s="2"/>
@@ -6994,13 +6666,13 @@
       <x:c r="Z160" s="2"/>
     </x:row>
     <x:row r="161" ht="15.75" customHeight="1">
-      <x:c r="A161" s="2"/>
-      <x:c r="B161" s="2"/>
-      <x:c r="C161" s="2"/>
-      <x:c r="D161" s="2"/>
-      <x:c r="E161" s="2"/>
-      <x:c r="F161" s="2"/>
-      <x:c r="G161" s="2"/>
+      <x:c r="A161"/>
+      <x:c r="B161"/>
+      <x:c r="C161"/>
+      <x:c r="D161"/>
+      <x:c r="E161"/>
+      <x:c r="F161"/>
+      <x:c r="G161"/>
       <x:c r="H161" s="2"/>
       <x:c r="I161" s="2"/>
       <x:c r="J161" s="2"/>
@@ -7022,13 +6694,13 @@
       <x:c r="Z161" s="2"/>
     </x:row>
     <x:row r="162" ht="15.75" customHeight="1">
-      <x:c r="A162" s="2"/>
-      <x:c r="B162" s="2"/>
-      <x:c r="C162" s="2"/>
-      <x:c r="D162" s="2"/>
-      <x:c r="E162" s="2"/>
-      <x:c r="F162" s="2"/>
-      <x:c r="G162" s="2"/>
+      <x:c r="A162"/>
+      <x:c r="B162"/>
+      <x:c r="C162"/>
+      <x:c r="D162"/>
+      <x:c r="E162"/>
+      <x:c r="F162"/>
+      <x:c r="G162"/>
       <x:c r="H162" s="2"/>
       <x:c r="I162" s="2"/>
       <x:c r="J162" s="2"/>
@@ -7050,13 +6722,13 @@
       <x:c r="Z162" s="2"/>
     </x:row>
     <x:row r="163" ht="15.75" customHeight="1">
-      <x:c r="A163" s="2"/>
-      <x:c r="B163" s="2"/>
-      <x:c r="C163" s="2"/>
-      <x:c r="D163" s="2"/>
-      <x:c r="E163" s="2"/>
-      <x:c r="F163" s="2"/>
-      <x:c r="G163" s="2"/>
+      <x:c r="A163"/>
+      <x:c r="B163"/>
+      <x:c r="C163"/>
+      <x:c r="D163"/>
+      <x:c r="E163"/>
+      <x:c r="F163"/>
+      <x:c r="G163"/>
       <x:c r="H163" s="2"/>
       <x:c r="I163" s="2"/>
       <x:c r="J163" s="2"/>
@@ -7078,13 +6750,13 @@
       <x:c r="Z163" s="2"/>
     </x:row>
     <x:row r="164" ht="15.75" customHeight="1">
-      <x:c r="A164" s="2"/>
-      <x:c r="B164" s="2"/>
-      <x:c r="C164" s="2"/>
-      <x:c r="D164" s="2"/>
-      <x:c r="E164" s="2"/>
-      <x:c r="F164" s="2"/>
-      <x:c r="G164" s="2"/>
+      <x:c r="A164"/>
+      <x:c r="B164"/>
+      <x:c r="C164"/>
+      <x:c r="D164"/>
+      <x:c r="E164"/>
+      <x:c r="F164"/>
+      <x:c r="G164"/>
       <x:c r="H164" s="2"/>
       <x:c r="I164" s="2"/>
       <x:c r="J164" s="2"/>
@@ -7106,13 +6778,13 @@
       <x:c r="Z164" s="2"/>
     </x:row>
     <x:row r="165" ht="15.75" customHeight="1">
-      <x:c r="A165" s="2"/>
-      <x:c r="B165" s="2"/>
-      <x:c r="C165" s="2"/>
-      <x:c r="D165" s="2"/>
-      <x:c r="E165" s="2"/>
-      <x:c r="F165" s="2"/>
-      <x:c r="G165" s="2"/>
+      <x:c r="A165"/>
+      <x:c r="B165"/>
+      <x:c r="C165"/>
+      <x:c r="D165"/>
+      <x:c r="E165"/>
+      <x:c r="F165"/>
+      <x:c r="G165"/>
       <x:c r="H165" s="2"/>
       <x:c r="I165" s="2"/>
       <x:c r="J165" s="2"/>
@@ -7134,13 +6806,13 @@
       <x:c r="Z165" s="2"/>
     </x:row>
     <x:row r="166" ht="15.75" customHeight="1">
-      <x:c r="A166" s="2"/>
-      <x:c r="B166" s="2"/>
-      <x:c r="C166" s="2"/>
-      <x:c r="D166" s="2"/>
-      <x:c r="E166" s="2"/>
-      <x:c r="F166" s="2"/>
-      <x:c r="G166" s="2"/>
+      <x:c r="A166"/>
+      <x:c r="B166"/>
+      <x:c r="C166"/>
+      <x:c r="D166"/>
+      <x:c r="E166"/>
+      <x:c r="F166"/>
+      <x:c r="G166"/>
       <x:c r="H166" s="2"/>
       <x:c r="I166" s="2"/>
       <x:c r="J166" s="2"/>
@@ -7162,13 +6834,13 @@
       <x:c r="Z166" s="2"/>
     </x:row>
     <x:row r="167" ht="15.75" customHeight="1">
-      <x:c r="A167" s="2"/>
-      <x:c r="B167" s="2"/>
-      <x:c r="C167" s="2"/>
-      <x:c r="D167" s="2"/>
-      <x:c r="E167" s="2"/>
-      <x:c r="F167" s="2"/>
-      <x:c r="G167" s="2"/>
+      <x:c r="A167"/>
+      <x:c r="B167"/>
+      <x:c r="C167"/>
+      <x:c r="D167"/>
+      <x:c r="E167"/>
+      <x:c r="F167"/>
+      <x:c r="G167"/>
       <x:c r="H167" s="2"/>
       <x:c r="I167" s="2"/>
       <x:c r="J167" s="2"/>
@@ -7190,13 +6862,13 @@
       <x:c r="Z167" s="2"/>
     </x:row>
     <x:row r="168" ht="15.75" customHeight="1">
-      <x:c r="A168" s="2"/>
-      <x:c r="B168" s="2"/>
-      <x:c r="C168" s="2"/>
-      <x:c r="D168" s="2"/>
-      <x:c r="E168" s="2"/>
-      <x:c r="F168" s="2"/>
-      <x:c r="G168" s="2"/>
+      <x:c r="A168"/>
+      <x:c r="B168"/>
+      <x:c r="C168"/>
+      <x:c r="D168"/>
+      <x:c r="E168"/>
+      <x:c r="F168"/>
+      <x:c r="G168"/>
       <x:c r="H168" s="2"/>
       <x:c r="I168" s="2"/>
       <x:c r="J168" s="2"/>
@@ -7218,13 +6890,13 @@
       <x:c r="Z168" s="2"/>
     </x:row>
     <x:row r="169" ht="15.75" customHeight="1">
-      <x:c r="A169" s="2"/>
-      <x:c r="B169" s="2"/>
-      <x:c r="C169" s="2"/>
-      <x:c r="D169" s="2"/>
-      <x:c r="E169" s="2"/>
-      <x:c r="F169" s="2"/>
-      <x:c r="G169" s="2"/>
+      <x:c r="A169"/>
+      <x:c r="B169"/>
+      <x:c r="C169"/>
+      <x:c r="D169"/>
+      <x:c r="E169"/>
+      <x:c r="F169"/>
+      <x:c r="G169"/>
       <x:c r="H169" s="2"/>
       <x:c r="I169" s="2"/>
       <x:c r="J169" s="2"/>
@@ -7246,13 +6918,13 @@
       <x:c r="Z169" s="2"/>
     </x:row>
     <x:row r="170" ht="15.75" customHeight="1">
-      <x:c r="A170" s="2"/>
-      <x:c r="B170" s="2"/>
-      <x:c r="C170" s="2"/>
-      <x:c r="D170" s="2"/>
-      <x:c r="E170" s="2"/>
-      <x:c r="F170" s="2"/>
-      <x:c r="G170" s="2"/>
+      <x:c r="A170"/>
+      <x:c r="B170"/>
+      <x:c r="C170"/>
+      <x:c r="D170"/>
+      <x:c r="E170"/>
+      <x:c r="F170"/>
+      <x:c r="G170"/>
       <x:c r="H170" s="2"/>
       <x:c r="I170" s="2"/>
       <x:c r="J170" s="2"/>
@@ -7274,13 +6946,13 @@
       <x:c r="Z170" s="2"/>
     </x:row>
     <x:row r="171" ht="15.75" customHeight="1">
-      <x:c r="A171" s="2"/>
-      <x:c r="B171" s="2"/>
-      <x:c r="C171" s="2"/>
-      <x:c r="D171" s="2"/>
-      <x:c r="E171" s="2"/>
-      <x:c r="F171" s="2"/>
-      <x:c r="G171" s="2"/>
+      <x:c r="A171"/>
+      <x:c r="B171"/>
+      <x:c r="C171"/>
+      <x:c r="D171"/>
+      <x:c r="E171"/>
+      <x:c r="F171"/>
+      <x:c r="G171"/>
       <x:c r="H171" s="2"/>
       <x:c r="I171" s="2"/>
       <x:c r="J171" s="2"/>
@@ -7302,13 +6974,13 @@
       <x:c r="Z171" s="2"/>
     </x:row>
     <x:row r="172" ht="15.75" customHeight="1">
-      <x:c r="A172" s="2"/>
-      <x:c r="B172" s="2"/>
-      <x:c r="C172" s="2"/>
-      <x:c r="D172" s="2"/>
-      <x:c r="E172" s="2"/>
-      <x:c r="F172" s="2"/>
-      <x:c r="G172" s="2"/>
+      <x:c r="A172"/>
+      <x:c r="B172"/>
+      <x:c r="C172"/>
+      <x:c r="D172"/>
+      <x:c r="E172"/>
+      <x:c r="F172"/>
+      <x:c r="G172"/>
       <x:c r="H172" s="2"/>
       <x:c r="I172" s="2"/>
       <x:c r="J172" s="2"/>
@@ -7330,13 +7002,13 @@
       <x:c r="Z172" s="2"/>
     </x:row>
     <x:row r="173" ht="15.75" customHeight="1">
-      <x:c r="A173" s="2"/>
-      <x:c r="B173" s="2"/>
-      <x:c r="C173" s="2"/>
-      <x:c r="D173" s="2"/>
-      <x:c r="E173" s="2"/>
-      <x:c r="F173" s="2"/>
-      <x:c r="G173" s="2"/>
+      <x:c r="A173"/>
+      <x:c r="B173"/>
+      <x:c r="C173"/>
+      <x:c r="D173"/>
+      <x:c r="E173"/>
+      <x:c r="F173"/>
+      <x:c r="G173"/>
       <x:c r="H173" s="2"/>
       <x:c r="I173" s="2"/>
       <x:c r="J173" s="2"/>
@@ -7358,13 +7030,13 @@
       <x:c r="Z173" s="2"/>
     </x:row>
     <x:row r="174" ht="15.75" customHeight="1">
-      <x:c r="A174" s="2"/>
-      <x:c r="B174" s="2"/>
-      <x:c r="C174" s="2"/>
-      <x:c r="D174" s="2"/>
-      <x:c r="E174" s="2"/>
-      <x:c r="F174" s="2"/>
-      <x:c r="G174" s="2"/>
+      <x:c r="A174"/>
+      <x:c r="B174"/>
+      <x:c r="C174"/>
+      <x:c r="D174"/>
+      <x:c r="E174"/>
+      <x:c r="F174"/>
+      <x:c r="G174"/>
       <x:c r="H174" s="2"/>
       <x:c r="I174" s="2"/>
       <x:c r="J174" s="2"/>
@@ -7386,13 +7058,13 @@
       <x:c r="Z174" s="2"/>
     </x:row>
     <x:row r="175" ht="15.75" customHeight="1">
-      <x:c r="A175" s="2"/>
-      <x:c r="B175" s="2"/>
-      <x:c r="C175" s="2"/>
-      <x:c r="D175" s="2"/>
-      <x:c r="E175" s="2"/>
-      <x:c r="F175" s="2"/>
-      <x:c r="G175" s="2"/>
+      <x:c r="A175"/>
+      <x:c r="B175"/>
+      <x:c r="C175"/>
+      <x:c r="D175"/>
+      <x:c r="E175"/>
+      <x:c r="F175"/>
+      <x:c r="G175"/>
       <x:c r="H175" s="2"/>
       <x:c r="I175" s="2"/>
       <x:c r="J175" s="2"/>
@@ -7414,13 +7086,13 @@
       <x:c r="Z175" s="2"/>
     </x:row>
     <x:row r="176" ht="15.75" customHeight="1">
-      <x:c r="A176" s="2"/>
-      <x:c r="B176" s="2"/>
-      <x:c r="C176" s="2"/>
-      <x:c r="D176" s="2"/>
-      <x:c r="E176" s="2"/>
-      <x:c r="F176" s="2"/>
-      <x:c r="G176" s="2"/>
+      <x:c r="A176"/>
+      <x:c r="B176"/>
+      <x:c r="C176"/>
+      <x:c r="D176"/>
+      <x:c r="E176"/>
+      <x:c r="F176"/>
+      <x:c r="G176"/>
       <x:c r="H176" s="2"/>
       <x:c r="I176" s="2"/>
       <x:c r="J176" s="2"/>
@@ -7442,13 +7114,13 @@
       <x:c r="Z176" s="2"/>
     </x:row>
     <x:row r="177" ht="15.75" customHeight="1">
-      <x:c r="A177" s="2"/>
-      <x:c r="B177" s="2"/>
-      <x:c r="C177" s="2"/>
-      <x:c r="D177" s="2"/>
-      <x:c r="E177" s="2"/>
-      <x:c r="F177" s="2"/>
-      <x:c r="G177" s="2"/>
+      <x:c r="A177"/>
+      <x:c r="B177"/>
+      <x:c r="C177"/>
+      <x:c r="D177"/>
+      <x:c r="E177"/>
+      <x:c r="F177"/>
+      <x:c r="G177"/>
       <x:c r="H177" s="2"/>
       <x:c r="I177" s="2"/>
       <x:c r="J177" s="2"/>
@@ -7470,13 +7142,13 @@
       <x:c r="Z177" s="2"/>
     </x:row>
     <x:row r="178" ht="15.75" customHeight="1">
-      <x:c r="A178" s="2"/>
-      <x:c r="B178" s="2"/>
-      <x:c r="C178" s="2"/>
-      <x:c r="D178" s="2"/>
-      <x:c r="E178" s="2"/>
-      <x:c r="F178" s="2"/>
-      <x:c r="G178" s="2"/>
+      <x:c r="A178"/>
+      <x:c r="B178"/>
+      <x:c r="C178"/>
+      <x:c r="D178"/>
+      <x:c r="E178"/>
+      <x:c r="F178"/>
+      <x:c r="G178"/>
       <x:c r="H178" s="2"/>
       <x:c r="I178" s="2"/>
       <x:c r="J178" s="2"/>
@@ -7498,13 +7170,13 @@
       <x:c r="Z178" s="2"/>
     </x:row>
     <x:row r="179" ht="15.75" customHeight="1">
-      <x:c r="A179" s="2"/>
-      <x:c r="B179" s="2"/>
-      <x:c r="C179" s="2"/>
-      <x:c r="D179" s="2"/>
-      <x:c r="E179" s="2"/>
-      <x:c r="F179" s="2"/>
-      <x:c r="G179" s="2"/>
+      <x:c r="A179"/>
+      <x:c r="B179"/>
+      <x:c r="C179"/>
+      <x:c r="D179"/>
+      <x:c r="E179"/>
+      <x:c r="F179"/>
+      <x:c r="G179"/>
       <x:c r="H179" s="2"/>
       <x:c r="I179" s="2"/>
       <x:c r="J179" s="2"/>
@@ -7526,13 +7198,13 @@
       <x:c r="Z179" s="2"/>
     </x:row>
     <x:row r="180" ht="15.75" customHeight="1">
-      <x:c r="A180" s="2"/>
-      <x:c r="B180" s="2"/>
-      <x:c r="C180" s="2"/>
-      <x:c r="D180" s="2"/>
-      <x:c r="E180" s="2"/>
-      <x:c r="F180" s="2"/>
-      <x:c r="G180" s="2"/>
+      <x:c r="A180"/>
+      <x:c r="B180"/>
+      <x:c r="C180"/>
+      <x:c r="D180"/>
+      <x:c r="E180"/>
+      <x:c r="F180"/>
+      <x:c r="G180"/>
       <x:c r="H180" s="2"/>
       <x:c r="I180" s="2"/>
       <x:c r="J180" s="2"/>
@@ -7554,13 +7226,13 @@
       <x:c r="Z180" s="2"/>
     </x:row>
     <x:row r="181" ht="15.75" customHeight="1">
-      <x:c r="A181" s="2"/>
-      <x:c r="B181" s="2"/>
-      <x:c r="C181" s="2"/>
-      <x:c r="D181" s="2"/>
-      <x:c r="E181" s="2"/>
-      <x:c r="F181" s="2"/>
-      <x:c r="G181" s="2"/>
+      <x:c r="A181"/>
+      <x:c r="B181"/>
+      <x:c r="C181"/>
+      <x:c r="D181"/>
+      <x:c r="E181"/>
+      <x:c r="F181"/>
+      <x:c r="G181"/>
       <x:c r="H181" s="2"/>
       <x:c r="I181" s="2"/>
       <x:c r="J181" s="2"/>
@@ -7582,13 +7254,13 @@
       <x:c r="Z181" s="2"/>
     </x:row>
     <x:row r="182" ht="15.75" customHeight="1">
-      <x:c r="A182" s="2"/>
-      <x:c r="B182" s="2"/>
-      <x:c r="C182" s="2"/>
-      <x:c r="D182" s="2"/>
-      <x:c r="E182" s="2"/>
-      <x:c r="F182" s="2"/>
-      <x:c r="G182" s="2"/>
+      <x:c r="A182"/>
+      <x:c r="B182"/>
+      <x:c r="C182"/>
+      <x:c r="D182"/>
+      <x:c r="E182"/>
+      <x:c r="F182"/>
+      <x:c r="G182"/>
       <x:c r="H182" s="2"/>
       <x:c r="I182" s="2"/>
       <x:c r="J182" s="2"/>
@@ -7610,13 +7282,13 @@
       <x:c r="Z182" s="2"/>
     </x:row>
     <x:row r="183" ht="15.75" customHeight="1">
-      <x:c r="A183" s="2"/>
-      <x:c r="B183" s="2"/>
-      <x:c r="C183" s="2"/>
-      <x:c r="D183" s="2"/>
-      <x:c r="E183" s="2"/>
-      <x:c r="F183" s="2"/>
-      <x:c r="G183" s="2"/>
+      <x:c r="A183"/>
+      <x:c r="B183"/>
+      <x:c r="C183"/>
+      <x:c r="D183"/>
+      <x:c r="E183"/>
+      <x:c r="F183"/>
+      <x:c r="G183"/>
       <x:c r="H183" s="2"/>
       <x:c r="I183" s="2"/>
       <x:c r="J183" s="2"/>
@@ -7638,13 +7310,13 @@
       <x:c r="Z183" s="2"/>
     </x:row>
     <x:row r="184" ht="15.75" customHeight="1">
-      <x:c r="A184" s="2"/>
-      <x:c r="B184" s="2"/>
-      <x:c r="C184" s="2"/>
-      <x:c r="D184" s="2"/>
-      <x:c r="E184" s="2"/>
-      <x:c r="F184" s="2"/>
-      <x:c r="G184" s="2"/>
+      <x:c r="A184"/>
+      <x:c r="B184"/>
+      <x:c r="C184"/>
+      <x:c r="D184"/>
+      <x:c r="E184"/>
+      <x:c r="F184"/>
+      <x:c r="G184"/>
       <x:c r="H184" s="2"/>
       <x:c r="I184" s="2"/>
       <x:c r="J184" s="2"/>
@@ -7666,13 +7338,13 @@
       <x:c r="Z184" s="2"/>
     </x:row>
     <x:row r="185" ht="15.75" customHeight="1">
-      <x:c r="A185" s="2"/>
-      <x:c r="B185" s="2"/>
-      <x:c r="C185" s="2"/>
-      <x:c r="D185" s="2"/>
-      <x:c r="E185" s="2"/>
-      <x:c r="F185" s="2"/>
-      <x:c r="G185" s="2"/>
+      <x:c r="A185"/>
+      <x:c r="B185"/>
+      <x:c r="C185"/>
+      <x:c r="D185"/>
+      <x:c r="E185"/>
+      <x:c r="F185"/>
+      <x:c r="G185"/>
       <x:c r="H185" s="2"/>
       <x:c r="I185" s="2"/>
       <x:c r="J185" s="2"/>
@@ -7694,13 +7366,13 @@
       <x:c r="Z185" s="2"/>
     </x:row>
     <x:row r="186" ht="15.75" customHeight="1">
-      <x:c r="A186" s="2"/>
-      <x:c r="B186" s="2"/>
-      <x:c r="C186" s="2"/>
-      <x:c r="D186" s="2"/>
-      <x:c r="E186" s="2"/>
-      <x:c r="F186" s="2"/>
-      <x:c r="G186" s="2"/>
+      <x:c r="A186"/>
+      <x:c r="B186"/>
+      <x:c r="C186"/>
+      <x:c r="D186"/>
+      <x:c r="E186"/>
+      <x:c r="F186"/>
+      <x:c r="G186"/>
       <x:c r="H186" s="2"/>
       <x:c r="I186" s="2"/>
       <x:c r="J186" s="2"/>
@@ -7722,13 +7394,13 @@
       <x:c r="Z186" s="2"/>
     </x:row>
     <x:row r="187" ht="15.75" customHeight="1">
-      <x:c r="A187" s="2"/>
-      <x:c r="B187" s="2"/>
-      <x:c r="C187" s="2"/>
-      <x:c r="D187" s="2"/>
-      <x:c r="E187" s="2"/>
-      <x:c r="F187" s="2"/>
-      <x:c r="G187" s="2"/>
+      <x:c r="A187"/>
+      <x:c r="B187"/>
+      <x:c r="C187"/>
+      <x:c r="D187"/>
+      <x:c r="E187"/>
+      <x:c r="F187"/>
+      <x:c r="G187"/>
       <x:c r="H187" s="2"/>
       <x:c r="I187" s="2"/>
       <x:c r="J187" s="2"/>
@@ -7750,13 +7422,13 @@
       <x:c r="Z187" s="2"/>
     </x:row>
     <x:row r="188" ht="15.75" customHeight="1">
-      <x:c r="A188" s="2"/>
-      <x:c r="B188" s="2"/>
-      <x:c r="C188" s="2"/>
-      <x:c r="D188" s="2"/>
-      <x:c r="E188" s="2"/>
-      <x:c r="F188" s="2"/>
-      <x:c r="G188" s="2"/>
+      <x:c r="A188"/>
+      <x:c r="B188"/>
+      <x:c r="C188"/>
+      <x:c r="D188"/>
+      <x:c r="E188"/>
+      <x:c r="F188"/>
+      <x:c r="G188"/>
       <x:c r="H188" s="2"/>
       <x:c r="I188" s="2"/>
       <x:c r="J188" s="2"/>
@@ -7778,13 +7450,13 @@
       <x:c r="Z188" s="2"/>
     </x:row>
     <x:row r="189" ht="15.75" customHeight="1">
-      <x:c r="A189" s="2"/>
-      <x:c r="B189" s="2"/>
-      <x:c r="C189" s="2"/>
-      <x:c r="D189" s="2"/>
-      <x:c r="E189" s="2"/>
-      <x:c r="F189" s="2"/>
-      <x:c r="G189" s="2"/>
+      <x:c r="A189"/>
+      <x:c r="B189"/>
+      <x:c r="C189"/>
+      <x:c r="D189"/>
+      <x:c r="E189"/>
+      <x:c r="F189"/>
+      <x:c r="G189"/>
       <x:c r="H189" s="2"/>
       <x:c r="I189" s="2"/>
       <x:c r="J189" s="2"/>
@@ -7806,13 +7478,13 @@
       <x:c r="Z189" s="2"/>
     </x:row>
     <x:row r="190" ht="15.75" customHeight="1">
-      <x:c r="A190" s="2"/>
-      <x:c r="B190" s="2"/>
-      <x:c r="C190" s="2"/>
-      <x:c r="D190" s="2"/>
-      <x:c r="E190" s="2"/>
-      <x:c r="F190" s="2"/>
-      <x:c r="G190" s="2"/>
+      <x:c r="A190"/>
+      <x:c r="B190"/>
+      <x:c r="C190"/>
+      <x:c r="D190"/>
+      <x:c r="E190"/>
+      <x:c r="F190"/>
+      <x:c r="G190"/>
       <x:c r="H190" s="2"/>
       <x:c r="I190" s="2"/>
       <x:c r="J190" s="2"/>
@@ -7834,13 +7506,13 @@
       <x:c r="Z190" s="2"/>
     </x:row>
     <x:row r="191" ht="15.75" customHeight="1">
-      <x:c r="A191" s="2"/>
-      <x:c r="B191" s="2"/>
-      <x:c r="C191" s="2"/>
-      <x:c r="D191" s="2"/>
-      <x:c r="E191" s="2"/>
-      <x:c r="F191" s="2"/>
-      <x:c r="G191" s="2"/>
+      <x:c r="A191"/>
+      <x:c r="B191"/>
+      <x:c r="C191"/>
+      <x:c r="D191"/>
+      <x:c r="E191"/>
+      <x:c r="F191"/>
+      <x:c r="G191"/>
       <x:c r="H191" s="2"/>
       <x:c r="I191" s="2"/>
       <x:c r="J191" s="2"/>
@@ -7862,13 +7534,13 @@
       <x:c r="Z191" s="2"/>
     </x:row>
     <x:row r="192" ht="15.75" customHeight="1">
-      <x:c r="A192" s="2"/>
-      <x:c r="B192" s="2"/>
-      <x:c r="C192" s="2"/>
-      <x:c r="D192" s="2"/>
-      <x:c r="E192" s="2"/>
-      <x:c r="F192" s="2"/>
-      <x:c r="G192" s="2"/>
+      <x:c r="A192"/>
+      <x:c r="B192"/>
+      <x:c r="C192"/>
+      <x:c r="D192"/>
+      <x:c r="E192"/>
+      <x:c r="F192"/>
+      <x:c r="G192"/>
       <x:c r="H192" s="2"/>
       <x:c r="I192" s="2"/>
       <x:c r="J192" s="2"/>
@@ -7890,13 +7562,13 @@
       <x:c r="Z192" s="2"/>
     </x:row>
     <x:row r="193" ht="15.75" customHeight="1">
-      <x:c r="A193" s="2"/>
-      <x:c r="B193" s="2"/>
-      <x:c r="C193" s="2"/>
-      <x:c r="D193" s="2"/>
-      <x:c r="E193" s="2"/>
-      <x:c r="F193" s="2"/>
-      <x:c r="G193" s="2"/>
+      <x:c r="A193"/>
+      <x:c r="B193"/>
+      <x:c r="C193"/>
+      <x:c r="D193"/>
+      <x:c r="E193"/>
+      <x:c r="F193"/>
+      <x:c r="G193"/>
       <x:c r="H193" s="2"/>
       <x:c r="I193" s="2"/>
       <x:c r="J193" s="2"/>
@@ -7918,13 +7590,13 @@
       <x:c r="Z193" s="2"/>
     </x:row>
     <x:row r="194" ht="15.75" customHeight="1">
-      <x:c r="A194" s="2"/>
-      <x:c r="B194" s="2"/>
-      <x:c r="C194" s="2"/>
-      <x:c r="D194" s="2"/>
-      <x:c r="E194" s="2"/>
-      <x:c r="F194" s="2"/>
-      <x:c r="G194" s="2"/>
+      <x:c r="A194"/>
+      <x:c r="B194"/>
+      <x:c r="C194"/>
+      <x:c r="D194"/>
+      <x:c r="E194"/>
+      <x:c r="F194"/>
+      <x:c r="G194"/>
       <x:c r="H194" s="2"/>
       <x:c r="I194" s="2"/>
       <x:c r="J194" s="2"/>
@@ -7946,13 +7618,13 @@
       <x:c r="Z194" s="2"/>
     </x:row>
     <x:row r="195" ht="15.75" customHeight="1">
-      <x:c r="A195" s="2"/>
-      <x:c r="B195" s="2"/>
-      <x:c r="C195" s="2"/>
-      <x:c r="D195" s="2"/>
-      <x:c r="E195" s="2"/>
-      <x:c r="F195" s="2"/>
-      <x:c r="G195" s="2"/>
+      <x:c r="A195"/>
+      <x:c r="B195"/>
+      <x:c r="C195"/>
+      <x:c r="D195"/>
+      <x:c r="E195"/>
+      <x:c r="F195"/>
+      <x:c r="G195"/>
       <x:c r="H195" s="2"/>
       <x:c r="I195" s="2"/>
       <x:c r="J195" s="2"/>
@@ -7974,13 +7646,13 @@
       <x:c r="Z195" s="2"/>
     </x:row>
     <x:row r="196" ht="15.75" customHeight="1">
-      <x:c r="A196" s="2"/>
-      <x:c r="B196" s="2"/>
-      <x:c r="C196" s="2"/>
-      <x:c r="D196" s="2"/>
-      <x:c r="E196" s="2"/>
-      <x:c r="F196" s="2"/>
-      <x:c r="G196" s="2"/>
+      <x:c r="A196"/>
+      <x:c r="B196"/>
+      <x:c r="C196"/>
+      <x:c r="D196"/>
+      <x:c r="E196"/>
+      <x:c r="F196"/>
+      <x:c r="G196"/>
       <x:c r="H196" s="2"/>
       <x:c r="I196" s="2"/>
       <x:c r="J196" s="2"/>
@@ -8002,13 +7674,13 @@
       <x:c r="Z196" s="2"/>
     </x:row>
     <x:row r="197" ht="15.75" customHeight="1">
-      <x:c r="A197" s="2"/>
-      <x:c r="B197" s="2"/>
-      <x:c r="C197" s="2"/>
-      <x:c r="D197" s="2"/>
-      <x:c r="E197" s="2"/>
-      <x:c r="F197" s="2"/>
-      <x:c r="G197" s="2"/>
+      <x:c r="A197"/>
+      <x:c r="B197"/>
+      <x:c r="C197"/>
+      <x:c r="D197"/>
+      <x:c r="E197"/>
+      <x:c r="F197"/>
+      <x:c r="G197"/>
       <x:c r="H197" s="2"/>
       <x:c r="I197" s="2"/>
       <x:c r="J197" s="2"/>
@@ -8030,13 +7702,13 @@
       <x:c r="Z197" s="2"/>
     </x:row>
     <x:row r="198" ht="15.75" customHeight="1">
-      <x:c r="A198" s="2"/>
-      <x:c r="B198" s="2"/>
-      <x:c r="C198" s="2"/>
-      <x:c r="D198" s="2"/>
-      <x:c r="E198" s="2"/>
-      <x:c r="F198" s="2"/>
-      <x:c r="G198" s="2"/>
+      <x:c r="A198"/>
+      <x:c r="B198"/>
+      <x:c r="C198"/>
+      <x:c r="D198"/>
+      <x:c r="E198"/>
+      <x:c r="F198"/>
+      <x:c r="G198"/>
       <x:c r="H198" s="2"/>
       <x:c r="I198" s="2"/>
       <x:c r="J198" s="2"/>
@@ -8058,13 +7730,13 @@
       <x:c r="Z198" s="2"/>
     </x:row>
     <x:row r="199" ht="15.75" customHeight="1">
-      <x:c r="A199" s="2"/>
-      <x:c r="B199" s="2"/>
-      <x:c r="C199" s="2"/>
-      <x:c r="D199" s="2"/>
-      <x:c r="E199" s="2"/>
-      <x:c r="F199" s="2"/>
-      <x:c r="G199" s="2"/>
+      <x:c r="A199"/>
+      <x:c r="B199"/>
+      <x:c r="C199"/>
+      <x:c r="D199"/>
+      <x:c r="E199"/>
+      <x:c r="F199"/>
+      <x:c r="G199"/>
       <x:c r="H199" s="2"/>
       <x:c r="I199" s="2"/>
       <x:c r="J199" s="2"/>
@@ -8086,13 +7758,13 @@
       <x:c r="Z199" s="2"/>
     </x:row>
     <x:row r="200" ht="15.75" customHeight="1">
-      <x:c r="A200" s="2"/>
-      <x:c r="B200" s="2"/>
-      <x:c r="C200" s="2"/>
-      <x:c r="D200" s="2"/>
-      <x:c r="E200" s="2"/>
-      <x:c r="F200" s="2"/>
-      <x:c r="G200" s="2"/>
+      <x:c r="A200"/>
+      <x:c r="B200"/>
+      <x:c r="C200"/>
+      <x:c r="D200"/>
+      <x:c r="E200"/>
+      <x:c r="F200"/>
+      <x:c r="G200"/>
       <x:c r="H200" s="2"/>
       <x:c r="I200" s="2"/>
       <x:c r="J200" s="2"/>
@@ -9461,28 +9133,18 @@
     <x:mergeCell ref="F3:F4"/>
     <x:mergeCell ref="G3:G4"/>
     <x:mergeCell ref="A2:G2"/>
-    <x:mergeCell ref="A5:A9"/>
-    <x:mergeCell ref="B5:B9"/>
-    <x:mergeCell ref="A10:A17"/>
-    <x:mergeCell ref="B10:B17"/>
-    <x:mergeCell ref="A18:A30"/>
-    <x:mergeCell ref="B18:B30"/>
-    <x:mergeCell ref="A31:A41"/>
-    <x:mergeCell ref="B31:B41"/>
-    <x:mergeCell ref="A42:A44"/>
-    <x:mergeCell ref="B42:B44"/>
-    <x:mergeCell ref="A45:A49"/>
-    <x:mergeCell ref="B45:B49"/>
-    <x:mergeCell ref="A50:A51"/>
-    <x:mergeCell ref="B50:B51"/>
-    <x:mergeCell ref="A52:A54"/>
-    <x:mergeCell ref="B52:B54"/>
-    <x:mergeCell ref="A55:A60"/>
-    <x:mergeCell ref="B55:B60"/>
-    <x:mergeCell ref="A61:A63"/>
-    <x:mergeCell ref="B61:B63"/>
-    <x:mergeCell ref="A64:A66"/>
-    <x:mergeCell ref="B64:B66"/>
+    <x:mergeCell ref="A5:A59"/>
+    <x:mergeCell ref="A60:A76"/>
+    <x:mergeCell ref="A77:A79"/>
+    <x:mergeCell ref="B5:B16"/>
+    <x:mergeCell ref="B17:B28"/>
+    <x:mergeCell ref="B29:B39"/>
+    <x:mergeCell ref="B40:B49"/>
+    <x:mergeCell ref="B50:B59"/>
+    <x:mergeCell ref="B60:B64"/>
+    <x:mergeCell ref="B65:B70"/>
+    <x:mergeCell ref="B71:B76"/>
+    <x:mergeCell ref="B77:B79"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>

--- a/docs/deliverables/01_요구사항정의서_29기_3팀.xlsx
+++ b/docs/deliverables/01_요구사항정의서_29기_3팀.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" r:id="Rfc4eef8ee5ff4c8b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="시트1" sheetId="1" r:id="R0f79ae1ef5684242"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1147,7 +1147,7 @@
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
       <x:c r="A2" s="160" t="str">
-        <x:v>DataHub Core 기반 대화형 데이터 분석·자동 리포팅 서비스 | SK네트웍스 Family AI 캠프 29기 3팀 | v1.2 | 기준일 2026-07-30 | 추적 요구사항 75개</x:v>
+        <x:v>DataHub Core 기반 대화형 데이터 분석·자동 리포팅 서비스 | SK네트웍스 Family AI 캠프 29기 3팀 | v1.1 | 기준일 2026-07-30 | 추적 요구사항 75개</x:v>
       </x:c>
       <x:c r="B2" s="160"/>
       <x:c r="C2" s="160"/>
@@ -4285,13 +4285,13 @@
         <x:v>REQ-SCP-001</x:v>
       </x:c>
       <x:c r="E77" s="208" t="str">
-        <x:v>MCP·문서 RAG·ML-as-a-Tool은 I5 이후 R1의 별도 일정·계약·비용·보안 Gate 승인 전 비활성 상태여야 한다.</x:v>
+        <x:v>MCP·문서 RAG·ML-as-a-Tool은 P0/P1 완료와 R1 편입 승인 전 비활성 상태여야 한다.</x:v>
       </x:c>
       <x:c r="F77" s="208" t="str">
-        <x:v>route·메뉴·worker·dependency를 선행 구현하지 않고 현재 P0/P1·I5 완료율을 차단하지 않는다.</x:v>
+        <x:v>route·메뉴·worker·dependency를 선행 구현하지 않는다.</x:v>
       </x:c>
       <x:c r="G77" s="208" t="str">
-        <x:v>P2·후속 대기</x:v>
+        <x:v>P2·기본 제외</x:v>
       </x:c>
       <x:c r="H77"/>
       <x:c r="I77"/>
@@ -4327,13 +4327,13 @@
         <x:v>REQ-SCP-002</x:v>
       </x:c>
       <x:c r="E78" s="208" t="str">
-        <x:v>고객 360은 I5 이후 identity mapping·masking·전용 권한·감사·별도 수용 기준 승인 전 비활성 상태여야 한다.</x:v>
+        <x:v>고객 360은 identity mapping·masking·전용 권한과 일정 영향 승인 전 비활성 상태여야 한다.</x:v>
       </x:c>
       <x:c r="F78" s="208" t="str">
-        <x:v>승인 전 MVP navigation과 직접 route에서 접근할 수 없고 현재 P0/P1·I5 완료율을 차단하지 않는다.</x:v>
+        <x:v>승인 전 MVP navigation과 직접 route에서 접근할 수 없다.</x:v>
       </x:c>
       <x:c r="G78" s="208" t="str">
-        <x:v>후속 대기</x:v>
+        <x:v>선택·기본 제외</x:v>
       </x:c>
       <x:c r="H78"/>
       <x:c r="I78"/>
@@ -4369,13 +4369,13 @@
         <x:v>REQ-SCP-003</x:v>
       </x:c>
       <x:c r="E79" s="208" t="str">
-        <x:v>외부 Report 배포와 다단 승인 workflow는 I5 이후 별도 Gate 승인 전 구현하지 않아야 한다.</x:v>
+        <x:v>외부 Report 배포와 다단 승인 workflow는 별도 승인 전 구현하지 않아야 한다.</x:v>
       </x:c>
       <x:c r="F79" s="208" t="str">
         <x:v>P0는 내부 정의·승인·수동/스케줄 실행·이력에 한정한다.</x:v>
       </x:c>
       <x:c r="G79" s="208" t="str">
-        <x:v>P2·후속 대기</x:v>
+        <x:v>P2·기본 제외</x:v>
       </x:c>
       <x:c r="H79"/>
       <x:c r="I79"/>
